--- a/model results/2025 Results.xlsx
+++ b/model results/2025 Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jmiller/Documents/Fun/nfl/model results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241D04A0-070B-AA44-B82F-226740C18F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D507C1B3-7F17-EC45-8EC8-643C03DA8679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="2" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="Week 14" sheetId="11" r:id="rId11"/>
     <sheet name="Week 15" sheetId="12" r:id="rId12"/>
     <sheet name="Week 16" sheetId="14" r:id="rId13"/>
+    <sheet name="Week 17" sheetId="15" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -67,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2863" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3162" uniqueCount="225">
   <si>
     <t>season</t>
   </si>
@@ -855,7 +856,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -907,6 +908,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1210,7 +1212,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E32420-1D15-E549-AAF4-FB71DE782F62}">
-  <dimension ref="B2:AH170"/>
+  <dimension ref="B2:AH186"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.1640625" customWidth="1"/>
@@ -1266,19 +1268,19 @@
       </c>
       <c r="C3" s="13">
         <f>COUNTA(N9:N1000)</f>
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="D3" s="13">
         <f>SUM(N9:N1000)</f>
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="E3" s="13">
         <f>C3-D3</f>
-        <v>59</v>
-      </c>
-      <c r="F3" s="14">
+        <v>65</v>
+      </c>
+      <c r="F3" s="23">
         <f>D3/C3</f>
-        <v>0.63580246913580252</v>
+        <v>0.6348314606741573</v>
       </c>
       <c r="G3" s="6"/>
     </row>
@@ -1288,19 +1290,19 @@
       </c>
       <c r="C4" s="13">
         <f>COUNTA(V9:V1000)</f>
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D4" s="13">
         <f>SUM(V9:V1000)</f>
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E4" s="13">
         <f>C4-D4</f>
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F4" s="14">
         <f>D4/C4</f>
-        <v>0.50549450549450547</v>
+        <v>0.52336448598130836</v>
       </c>
       <c r="G4" s="6"/>
     </row>
@@ -1310,19 +1312,19 @@
       </c>
       <c r="C5" s="13">
         <f>COUNTA(AB9:AB1000)</f>
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D5" s="13">
         <f>SUM(AB9:AB1000)</f>
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E5" s="13">
         <f>C5-D5</f>
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F5" s="14">
         <f>D5/C5</f>
-        <v>0.43956043956043955</v>
+        <v>0.43925233644859812</v>
       </c>
       <c r="G5" s="6"/>
     </row>
@@ -15517,6 +15519,1622 @@
         <v>0.13118640838130829</v>
       </c>
     </row>
+    <row r="171" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B171" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C171" s="4">
+        <v>17</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E171" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F171" s="4">
+        <v>23</v>
+      </c>
+      <c r="G171" s="4">
+        <v>30</v>
+      </c>
+      <c r="H171" s="8">
+        <v>0.41282143019888617</v>
+      </c>
+      <c r="I171" s="4">
+        <v>142</v>
+      </c>
+      <c r="J171" s="8">
+        <v>0.58717856980111383</v>
+      </c>
+      <c r="K171" s="4">
+        <v>-142</v>
+      </c>
+      <c r="L171" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M171" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N171" s="4">
+        <v>1</v>
+      </c>
+      <c r="O171" s="15">
+        <v>21.332065901802299</v>
+      </c>
+      <c r="P171" s="15">
+        <v>24.126748990821628</v>
+      </c>
+      <c r="Q171" s="4">
+        <v>-8.5</v>
+      </c>
+      <c r="R171" s="15">
+        <v>-2.7946830890193302</v>
+      </c>
+      <c r="S171" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T171" s="4">
+        <v>-7</v>
+      </c>
+      <c r="U171" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V171" s="4">
+        <v>1</v>
+      </c>
+      <c r="W171" s="4">
+        <v>50.5</v>
+      </c>
+      <c r="X171" s="9">
+        <v>45.458814892623927</v>
+      </c>
+      <c r="Y171" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z171" s="4">
+        <v>53</v>
+      </c>
+      <c r="AA171" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB171" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC171" s="5">
+        <v>0.2319403360056323</v>
+      </c>
+      <c r="AD171" s="5">
+        <v>-0.22120343083920679</v>
+      </c>
+      <c r="AE171" s="5">
+        <v>9.9053645956105205E-2</v>
+      </c>
+      <c r="AF171" s="5">
+        <v>0.22120343083920679</v>
+      </c>
+      <c r="AG171" s="5">
+        <v>-0.2319403360056323</v>
+      </c>
+      <c r="AH171" s="5">
+        <v>-9.9053645956105205E-2</v>
+      </c>
+    </row>
+    <row r="172" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B172" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C172" s="4">
+        <v>17</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E172" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F172" s="4">
+        <v>23</v>
+      </c>
+      <c r="G172" s="4">
+        <v>10</v>
+      </c>
+      <c r="H172" s="8">
+        <v>0.42549773720014372</v>
+      </c>
+      <c r="I172" s="4">
+        <v>135</v>
+      </c>
+      <c r="J172" s="8">
+        <v>0.57450226279985628</v>
+      </c>
+      <c r="K172" s="4">
+        <v>-135</v>
+      </c>
+      <c r="L172" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M172" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="N172" s="4">
+        <v>0</v>
+      </c>
+      <c r="O172" s="15">
+        <v>20.706238304403229</v>
+      </c>
+      <c r="P172" s="15">
+        <v>24.307338431866409</v>
+      </c>
+      <c r="Q172" s="4">
+        <v>-7.5</v>
+      </c>
+      <c r="R172" s="15">
+        <v>-3.6011001274631802</v>
+      </c>
+      <c r="S172" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T172" s="4">
+        <v>13</v>
+      </c>
+      <c r="U172" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V172" s="4">
+        <v>1</v>
+      </c>
+      <c r="W172" s="4">
+        <v>43.5</v>
+      </c>
+      <c r="X172" s="9">
+        <v>45.013576736269641</v>
+      </c>
+      <c r="Y172" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z172" s="4">
+        <v>33</v>
+      </c>
+      <c r="AA172" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB172" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC172" s="5">
+        <v>-0.25252072016398108</v>
+      </c>
+      <c r="AD172" s="5">
+        <v>0.46371796727180481</v>
+      </c>
+      <c r="AE172" s="5">
+        <v>-2.5729133532597471E-2</v>
+      </c>
+      <c r="AF172" s="5">
+        <v>-0.46371796727180481</v>
+      </c>
+      <c r="AG172" s="5">
+        <v>0.25252072016398108</v>
+      </c>
+      <c r="AH172" s="5">
+        <v>2.5729133532597471E-2</v>
+      </c>
+    </row>
+    <row r="173" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B173" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C173" s="4">
+        <v>17</v>
+      </c>
+      <c r="D173" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E173" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F173" s="4">
+        <v>13</v>
+      </c>
+      <c r="G173" s="4">
+        <v>20</v>
+      </c>
+      <c r="H173" s="8">
+        <v>0.43793113003547351</v>
+      </c>
+      <c r="I173" s="4">
+        <v>128</v>
+      </c>
+      <c r="J173" s="8">
+        <v>0.56206886996452643</v>
+      </c>
+      <c r="K173" s="4">
+        <v>-128</v>
+      </c>
+      <c r="L173" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M173" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N173" s="4">
+        <v>1</v>
+      </c>
+      <c r="O173" s="15">
+        <v>22.35682837886436</v>
+      </c>
+      <c r="P173" s="15">
+        <v>23.84626020725829</v>
+      </c>
+      <c r="Q173" s="4">
+        <v>-13.5</v>
+      </c>
+      <c r="R173" s="9">
+        <v>-1.489431828393929</v>
+      </c>
+      <c r="S173" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T173" s="4">
+        <v>-7</v>
+      </c>
+      <c r="U173" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V173" s="4">
+        <v>1</v>
+      </c>
+      <c r="W173" s="4">
+        <v>36.5</v>
+      </c>
+      <c r="X173" s="9">
+        <v>46.203088586122647</v>
+      </c>
+      <c r="Y173" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z173" s="4">
+        <v>33</v>
+      </c>
+      <c r="AA173" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB173" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC173" s="5">
+        <v>-0.15266824903942289</v>
+      </c>
+      <c r="AD173" s="5">
+        <v>-8.4641396159857094E-2</v>
+      </c>
+      <c r="AE173" s="5">
+        <v>0.28701658937193097</v>
+      </c>
+      <c r="AF173" s="5">
+        <v>8.4641396159857094E-2</v>
+      </c>
+      <c r="AG173" s="5">
+        <v>0.15266824903942289</v>
+      </c>
+      <c r="AH173" s="5">
+        <v>-0.28701658937193097</v>
+      </c>
+    </row>
+    <row r="174" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B174" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C174" s="4">
+        <v>17</v>
+      </c>
+      <c r="D174" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E174" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F174" s="4">
+        <v>16</v>
+      </c>
+      <c r="G174" s="4">
+        <v>20</v>
+      </c>
+      <c r="H174" s="8">
+        <v>0.53751412059105863</v>
+      </c>
+      <c r="I174" s="4">
+        <v>-116</v>
+      </c>
+      <c r="J174" s="8">
+        <v>0.46248587940894142</v>
+      </c>
+      <c r="K174" s="4">
+        <v>116</v>
+      </c>
+      <c r="L174" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M174" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="N174" s="4">
+        <v>0</v>
+      </c>
+      <c r="O174" s="15">
+        <v>22.239051791293011</v>
+      </c>
+      <c r="P174" s="15">
+        <v>22.121618389548519</v>
+      </c>
+      <c r="Q174" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="R174" s="9">
+        <v>0.11743340174448851</v>
+      </c>
+      <c r="S174" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T174" s="4">
+        <v>-4</v>
+      </c>
+      <c r="U174" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V174" s="4">
+        <v>1</v>
+      </c>
+      <c r="W174" s="4">
+        <v>39.5</v>
+      </c>
+      <c r="X174" s="9">
+        <v>44.360670180841517</v>
+      </c>
+      <c r="Y174" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z174" s="4">
+        <v>36</v>
+      </c>
+      <c r="AA174" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB174" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC174" s="5">
+        <v>-0.14214936513749379</v>
+      </c>
+      <c r="AD174" s="5">
+        <v>7.9646910390546249E-2</v>
+      </c>
+      <c r="AE174" s="5">
+        <v>-0.21228645587789599</v>
+      </c>
+      <c r="AF174" s="5">
+        <v>-7.9646910390546249E-2</v>
+      </c>
+      <c r="AG174" s="5">
+        <v>0.14214936513749379</v>
+      </c>
+      <c r="AH174" s="5">
+        <v>0.21228645587789599</v>
+      </c>
+    </row>
+    <row r="175" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B175" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C175" s="4">
+        <v>17</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E175" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F175" s="4">
+        <v>24</v>
+      </c>
+      <c r="G175" s="4">
+        <v>41</v>
+      </c>
+      <c r="H175" s="8">
+        <v>0.63540445235652621</v>
+      </c>
+      <c r="I175" s="4">
+        <v>-174</v>
+      </c>
+      <c r="J175" s="8">
+        <v>0.36459554764347379</v>
+      </c>
+      <c r="K175" s="4">
+        <v>174</v>
+      </c>
+      <c r="L175" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M175" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N175" s="4">
+        <v>0</v>
+      </c>
+      <c r="O175" s="15">
+        <v>25.37538507781553</v>
+      </c>
+      <c r="P175" s="15">
+        <v>25.26811681177249</v>
+      </c>
+      <c r="Q175" s="4">
+        <v>3</v>
+      </c>
+      <c r="R175" s="9">
+        <v>0.1072682660430466</v>
+      </c>
+      <c r="S175" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T175" s="4">
+        <v>-17</v>
+      </c>
+      <c r="U175" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V175" s="4">
+        <v>1</v>
+      </c>
+      <c r="W175" s="4">
+        <v>40.5</v>
+      </c>
+      <c r="X175" s="9">
+        <v>50.643501889588023</v>
+      </c>
+      <c r="Y175" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z175" s="4">
+        <v>65</v>
+      </c>
+      <c r="AA175" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB175" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC175" s="5">
+        <v>0.117405456966824</v>
+      </c>
+      <c r="AD175" s="5">
+        <v>-0.33768915812174483</v>
+      </c>
+      <c r="AE175" s="5">
+        <v>-4.0311717987060536E-3</v>
+      </c>
+      <c r="AF175" s="5">
+        <v>0.33768915812174483</v>
+      </c>
+      <c r="AG175" s="5">
+        <v>-0.117405456966824</v>
+      </c>
+      <c r="AH175" s="5">
+        <v>4.0311717987060536E-3</v>
+      </c>
+    </row>
+    <row r="176" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B176" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C176" s="4">
+        <v>17</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E176" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F176" s="4">
+        <v>10</v>
+      </c>
+      <c r="G176" s="4">
+        <v>27</v>
+      </c>
+      <c r="H176" s="8">
+        <v>0.35131865483870311</v>
+      </c>
+      <c r="I176" s="4">
+        <v>184</v>
+      </c>
+      <c r="J176" s="8">
+        <v>0.64868134516129694</v>
+      </c>
+      <c r="K176" s="4">
+        <v>-184</v>
+      </c>
+      <c r="L176" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M176" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N176" s="4">
+        <v>1</v>
+      </c>
+      <c r="O176" s="15">
+        <v>18.598230455760248</v>
+      </c>
+      <c r="P176" s="15">
+        <v>28.40619118159827</v>
+      </c>
+      <c r="Q176" s="4">
+        <v>-7</v>
+      </c>
+      <c r="R176" s="15">
+        <v>-9.807960725838015</v>
+      </c>
+      <c r="S176" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T176" s="4">
+        <v>-17</v>
+      </c>
+      <c r="U176" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V176" s="4">
+        <v>1</v>
+      </c>
+      <c r="W176" s="4">
+        <v>42.5</v>
+      </c>
+      <c r="X176" s="9">
+        <v>47.004421637358519</v>
+      </c>
+      <c r="Y176" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z176" s="4">
+        <v>37</v>
+      </c>
+      <c r="AA176" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB176" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC176" s="5">
+        <v>-0.47411228179931642</v>
+      </c>
+      <c r="AD176" s="5">
+        <v>5.35889038672814E-2</v>
+      </c>
+      <c r="AE176" s="5">
+        <v>-9.2909699394589373E-2</v>
+      </c>
+      <c r="AF176" s="5">
+        <v>-5.35889038672814E-2</v>
+      </c>
+      <c r="AG176" s="5">
+        <v>0.47411228179931642</v>
+      </c>
+      <c r="AH176" s="5">
+        <v>9.2909699394589373E-2</v>
+      </c>
+    </row>
+    <row r="177" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B177" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C177" s="4">
+        <v>17</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E177" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F177" s="4">
+        <v>37</v>
+      </c>
+      <c r="G177" s="4">
+        <v>14</v>
+      </c>
+      <c r="H177" s="8">
+        <v>0.61258942461821686</v>
+      </c>
+      <c r="I177" s="4">
+        <v>-158</v>
+      </c>
+      <c r="J177" s="8">
+        <v>0.38741057538178308</v>
+      </c>
+      <c r="K177" s="4">
+        <v>158</v>
+      </c>
+      <c r="L177" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M177" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="N177" s="4">
+        <v>1</v>
+      </c>
+      <c r="O177" s="15">
+        <v>26.148549655458758</v>
+      </c>
+      <c r="P177" s="15">
+        <v>24.94756395998073</v>
+      </c>
+      <c r="Q177" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="R177" s="9">
+        <v>1.200985695478028</v>
+      </c>
+      <c r="S177" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T177" s="4">
+        <v>23</v>
+      </c>
+      <c r="U177" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V177" s="4">
+        <v>0</v>
+      </c>
+      <c r="W177" s="4">
+        <v>52.5</v>
+      </c>
+      <c r="X177" s="9">
+        <v>51.096113615439492</v>
+      </c>
+      <c r="Y177" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z177" s="4">
+        <v>51</v>
+      </c>
+      <c r="AA177" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB177" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC177" s="5">
+        <v>0.33032649837128097</v>
+      </c>
+      <c r="AD177" s="5">
+        <v>2.2704843889202991E-2</v>
+      </c>
+      <c r="AE177" s="5">
+        <v>-5.1734850956843451E-2</v>
+      </c>
+      <c r="AF177" s="5">
+        <v>-2.2704843889202991E-2</v>
+      </c>
+      <c r="AG177" s="5">
+        <v>-0.33032649837128097</v>
+      </c>
+      <c r="AH177" s="5">
+        <v>5.1734850956843451E-2</v>
+      </c>
+    </row>
+    <row r="178" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B178" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C178" s="4">
+        <v>17</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E178" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F178" s="4">
+        <v>13</v>
+      </c>
+      <c r="G178" s="4">
+        <v>6</v>
+      </c>
+      <c r="H178" s="8">
+        <v>0.30626109673214358</v>
+      </c>
+      <c r="I178" s="4">
+        <v>226</v>
+      </c>
+      <c r="J178" s="8">
+        <v>0.69373890326785637</v>
+      </c>
+      <c r="K178" s="4">
+        <v>-226</v>
+      </c>
+      <c r="L178" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M178" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="N178" s="4">
+        <v>0</v>
+      </c>
+      <c r="O178" s="15">
+        <v>19.07209487906913</v>
+      </c>
+      <c r="P178" s="15">
+        <v>22.81096650874672</v>
+      </c>
+      <c r="Q178" s="4">
+        <v>-3</v>
+      </c>
+      <c r="R178" s="15">
+        <v>-3.7388716296775901</v>
+      </c>
+      <c r="S178" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T178" s="4">
+        <v>7</v>
+      </c>
+      <c r="U178" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V178" s="4">
+        <v>0</v>
+      </c>
+      <c r="W178" s="4">
+        <v>33.5</v>
+      </c>
+      <c r="X178" s="9">
+        <v>41.883061387815857</v>
+      </c>
+      <c r="Y178" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z178" s="4">
+        <v>19</v>
+      </c>
+      <c r="AA178" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB178" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC178" s="5">
+        <v>-0.20642806034462119</v>
+      </c>
+      <c r="AD178" s="5">
+        <v>0.21981136500835419</v>
+      </c>
+      <c r="AE178" s="5">
+        <v>0.23588852655319939</v>
+      </c>
+      <c r="AF178" s="5">
+        <v>-0.21981136500835419</v>
+      </c>
+      <c r="AG178" s="5">
+        <v>0.20642806034462119</v>
+      </c>
+      <c r="AH178" s="5">
+        <v>-0.23588852655319939</v>
+      </c>
+    </row>
+    <row r="179" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B179" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C179" s="4">
+        <v>17</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E179" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F179" s="4">
+        <v>17</v>
+      </c>
+      <c r="G179" s="4">
+        <v>23</v>
+      </c>
+      <c r="H179" s="8">
+        <v>0.41131428422671379</v>
+      </c>
+      <c r="I179" s="4">
+        <v>143</v>
+      </c>
+      <c r="J179" s="8">
+        <v>0.58868571577328621</v>
+      </c>
+      <c r="K179" s="4">
+        <v>-143</v>
+      </c>
+      <c r="L179" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M179" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N179" s="4">
+        <v>1</v>
+      </c>
+      <c r="O179" s="15">
+        <v>20.869518837182529</v>
+      </c>
+      <c r="P179" s="15">
+        <v>24.152507244820601</v>
+      </c>
+      <c r="Q179" s="4">
+        <v>-6.5</v>
+      </c>
+      <c r="R179" s="9">
+        <v>-3.2829884076380789</v>
+      </c>
+      <c r="S179" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T179" s="4">
+        <v>-6</v>
+      </c>
+      <c r="U179" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V179" s="4">
+        <v>1</v>
+      </c>
+      <c r="W179" s="4">
+        <v>48.5</v>
+      </c>
+      <c r="X179" s="9">
+        <v>45.02202608200313</v>
+      </c>
+      <c r="Y179" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z179" s="4">
+        <v>40</v>
+      </c>
+      <c r="AA179" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB179" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC179" s="5">
+        <v>-0.17091699232134899</v>
+      </c>
+      <c r="AD179" s="5">
+        <v>4.0298069732776576E-3</v>
+      </c>
+      <c r="AE179" s="5">
+        <v>1.0396182537078859E-2</v>
+      </c>
+      <c r="AF179" s="5">
+        <v>-4.0298069732776576E-3</v>
+      </c>
+      <c r="AG179" s="5">
+        <v>0.17091699232134899</v>
+      </c>
+      <c r="AH179" s="5">
+        <v>-1.0396182537078859E-2</v>
+      </c>
+    </row>
+    <row r="180" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B180" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C180" s="4">
+        <v>17</v>
+      </c>
+      <c r="D180" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E180" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F180" s="4">
+        <v>20</v>
+      </c>
+      <c r="G180" s="4">
+        <v>17</v>
+      </c>
+      <c r="H180" s="8">
+        <v>0.54252769259493627</v>
+      </c>
+      <c r="I180" s="4">
+        <v>-118</v>
+      </c>
+      <c r="J180" s="8">
+        <v>0.45747230740506373</v>
+      </c>
+      <c r="K180" s="4">
+        <v>118</v>
+      </c>
+      <c r="L180" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M180" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N180" s="4">
+        <v>1</v>
+      </c>
+      <c r="O180" s="15">
+        <v>25.357523161176289</v>
+      </c>
+      <c r="P180" s="15">
+        <v>24.216388890297029</v>
+      </c>
+      <c r="Q180" s="4">
+        <v>-5.5</v>
+      </c>
+      <c r="R180" s="9">
+        <v>1.141134270879256</v>
+      </c>
+      <c r="S180" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T180" s="4">
+        <v>3</v>
+      </c>
+      <c r="U180" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V180" s="4">
+        <v>1</v>
+      </c>
+      <c r="W180" s="4">
+        <v>45.5</v>
+      </c>
+      <c r="X180" s="9">
+        <v>49.573912051473307</v>
+      </c>
+      <c r="Y180" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z180" s="4">
+        <v>37</v>
+      </c>
+      <c r="AA180" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB180" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC180" s="5">
+        <v>6.0104476081000432E-2</v>
+      </c>
+      <c r="AD180" s="5">
+        <v>-3.7184526671224558E-2</v>
+      </c>
+      <c r="AE180" s="5">
+        <v>0.20254220247268681</v>
+      </c>
+      <c r="AF180" s="5">
+        <v>3.7184526671224558E-2</v>
+      </c>
+      <c r="AG180" s="5">
+        <v>-6.0104476081000432E-2</v>
+      </c>
+      <c r="AH180" s="5">
+        <v>-0.20254220247268681</v>
+      </c>
+    </row>
+    <row r="181" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B181" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C181" s="4">
+        <v>17</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E181" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F181" s="4">
+        <v>10</v>
+      </c>
+      <c r="G181" s="4">
+        <v>42</v>
+      </c>
+      <c r="H181" s="8">
+        <v>0.233976447694279</v>
+      </c>
+      <c r="I181" s="4">
+        <v>327</v>
+      </c>
+      <c r="J181" s="8">
+        <v>0.76602355230572095</v>
+      </c>
+      <c r="K181" s="4">
+        <v>-327</v>
+      </c>
+      <c r="L181" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M181" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N181" s="4">
+        <v>1</v>
+      </c>
+      <c r="O181" s="15">
+        <v>18.15545795202846</v>
+      </c>
+      <c r="P181" s="15">
+        <v>27.46140112404218</v>
+      </c>
+      <c r="Q181" s="4">
+        <v>-13.5</v>
+      </c>
+      <c r="R181" s="15">
+        <v>-9.3059431720137198</v>
+      </c>
+      <c r="S181" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T181" s="4">
+        <v>-32</v>
+      </c>
+      <c r="U181" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V181" s="4">
+        <v>0</v>
+      </c>
+      <c r="W181" s="4">
+        <v>42.5</v>
+      </c>
+      <c r="X181" s="9">
+        <v>45.616859076070639</v>
+      </c>
+      <c r="Y181" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z181" s="4">
+        <v>52</v>
+      </c>
+      <c r="AA181" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB181" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC181" s="5">
+        <v>-0.17908743023872381</v>
+      </c>
+      <c r="AD181" s="5">
+        <v>-0.50469183921813965</v>
+      </c>
+      <c r="AE181" s="5">
+        <v>0.27865218079608423</v>
+      </c>
+      <c r="AF181" s="5">
+        <v>0.50469183921813965</v>
+      </c>
+      <c r="AG181" s="5">
+        <v>0.17908743023872381</v>
+      </c>
+      <c r="AH181" s="5">
+        <v>-0.27865218079608423</v>
+      </c>
+    </row>
+    <row r="182" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B182" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C182" s="4">
+        <v>17</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E182" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F182" s="4">
+        <v>26</v>
+      </c>
+      <c r="G182" s="4">
+        <v>34</v>
+      </c>
+      <c r="H182" s="8">
+        <v>0.44607944474533329</v>
+      </c>
+      <c r="I182" s="4">
+        <v>124</v>
+      </c>
+      <c r="J182" s="8">
+        <v>0.55392055525466666</v>
+      </c>
+      <c r="K182" s="4">
+        <v>-124</v>
+      </c>
+      <c r="L182" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M182" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N182" s="4">
+        <v>1</v>
+      </c>
+      <c r="O182" s="15">
+        <v>22.906844836940341</v>
+      </c>
+      <c r="P182" s="15">
+        <v>21.82991600578422</v>
+      </c>
+      <c r="Q182" s="4">
+        <v>-2.5</v>
+      </c>
+      <c r="R182" s="9">
+        <v>1.07692883115612</v>
+      </c>
+      <c r="S182" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T182" s="4">
+        <v>-8</v>
+      </c>
+      <c r="U182" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V182" s="4">
+        <v>0</v>
+      </c>
+      <c r="W182" s="4">
+        <v>39.5</v>
+      </c>
+      <c r="X182" s="9">
+        <v>44.736760842724557</v>
+      </c>
+      <c r="Y182" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z182" s="4">
+        <v>60</v>
+      </c>
+      <c r="AA182" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB182" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC182" s="5">
+        <v>-0.13270121651726799</v>
+      </c>
+      <c r="AD182" s="5">
+        <v>-0.1991390912037975</v>
+      </c>
+      <c r="AE182" s="5">
+        <v>0.2469404177232222</v>
+      </c>
+      <c r="AF182" s="5">
+        <v>0.1991390912037975</v>
+      </c>
+      <c r="AG182" s="5">
+        <v>0.13270121651726799</v>
+      </c>
+      <c r="AH182" s="5">
+        <v>-0.2469404177232222</v>
+      </c>
+    </row>
+    <row r="183" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B183" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C183" s="4">
+        <v>17</v>
+      </c>
+      <c r="D183" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E183" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F183" s="4">
+        <v>10</v>
+      </c>
+      <c r="G183" s="4">
+        <v>34</v>
+      </c>
+      <c r="H183" s="8">
+        <v>0.33366036237169933</v>
+      </c>
+      <c r="I183" s="4">
+        <v>199</v>
+      </c>
+      <c r="J183" s="8">
+        <v>0.66633963762830062</v>
+      </c>
+      <c r="K183" s="4">
+        <v>-199</v>
+      </c>
+      <c r="L183" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M183" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="N183" s="4">
+        <v>1</v>
+      </c>
+      <c r="O183" s="15">
+        <v>18.502818792130569</v>
+      </c>
+      <c r="P183" s="15">
+        <v>22.57260962654793</v>
+      </c>
+      <c r="Q183" s="4">
+        <v>-1.5</v>
+      </c>
+      <c r="R183" s="9">
+        <v>-4.0697908344173648</v>
+      </c>
+      <c r="S183" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T183" s="4">
+        <v>-24</v>
+      </c>
+      <c r="U183" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V183" s="4">
+        <v>1</v>
+      </c>
+      <c r="W183" s="4">
+        <v>41.5</v>
+      </c>
+      <c r="X183" s="9">
+        <v>41.075428418678499</v>
+      </c>
+      <c r="Y183" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z183" s="4">
+        <v>44</v>
+      </c>
+      <c r="AA183" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB183" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC183" s="5">
+        <v>-0.22700842495622309</v>
+      </c>
+      <c r="AD183" s="5">
+        <v>-0.2351310761248479</v>
+      </c>
+      <c r="AE183" s="5">
+        <v>-9.7053625366904525E-2</v>
+      </c>
+      <c r="AF183" s="5">
+        <v>0.2351310761248479</v>
+      </c>
+      <c r="AG183" s="5">
+        <v>0.22700842495622309</v>
+      </c>
+      <c r="AH183" s="5">
+        <v>9.7053625366904525E-2</v>
+      </c>
+    </row>
+    <row r="184" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B184" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C184" s="4">
+        <v>17</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E184" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F184" s="4">
+        <v>12</v>
+      </c>
+      <c r="G184" s="4">
+        <v>13</v>
+      </c>
+      <c r="H184" s="8">
+        <v>0.57234845190812011</v>
+      </c>
+      <c r="I184" s="4">
+        <v>-133</v>
+      </c>
+      <c r="J184" s="8">
+        <v>0.42765154809187989</v>
+      </c>
+      <c r="K184" s="4">
+        <v>133</v>
+      </c>
+      <c r="L184" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="M184" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="N184" s="4">
+        <v>0</v>
+      </c>
+      <c r="O184" s="9">
+        <v>26.037626997972321</v>
+      </c>
+      <c r="P184" s="15">
+        <v>22.915419244049261</v>
+      </c>
+      <c r="Q184" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="R184" s="9">
+        <v>3.1222077539230599</v>
+      </c>
+      <c r="S184" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T184" s="4">
+        <v>-1</v>
+      </c>
+      <c r="U184" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V184" s="4">
+        <v>0</v>
+      </c>
+      <c r="W184" s="4">
+        <v>43.5</v>
+      </c>
+      <c r="X184" s="9">
+        <v>48.953046242021593</v>
+      </c>
+      <c r="Y184" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z184" s="4">
+        <v>25</v>
+      </c>
+      <c r="AA184" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB184" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC184" s="5">
+        <v>-5.0502319593687318E-2</v>
+      </c>
+      <c r="AD184" s="5">
+        <v>0.1195927835860342</v>
+      </c>
+      <c r="AE184" s="5">
+        <v>-0.25014792442321782</v>
+      </c>
+      <c r="AF184" s="5">
+        <v>-0.1195927835860342</v>
+      </c>
+      <c r="AG184" s="5">
+        <v>5.0502319593687318E-2</v>
+      </c>
+      <c r="AH184" s="5">
+        <v>0.25014792442321782</v>
+      </c>
+    </row>
+    <row r="185" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B185" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C185" s="4">
+        <v>17</v>
+      </c>
+      <c r="D185" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E185" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F185" s="4">
+        <v>42</v>
+      </c>
+      <c r="G185" s="4">
+        <v>38</v>
+      </c>
+      <c r="H185" s="8">
+        <v>0.63055471279437458</v>
+      </c>
+      <c r="I185" s="4">
+        <v>-170</v>
+      </c>
+      <c r="J185" s="8">
+        <v>0.36944528720562542</v>
+      </c>
+      <c r="K185" s="4">
+        <v>170</v>
+      </c>
+      <c r="L185" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M185" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="N185" s="4">
+        <v>1</v>
+      </c>
+      <c r="O185" s="9">
+        <v>28.48497409018092</v>
+      </c>
+      <c r="P185" s="15">
+        <v>24.427110672654521</v>
+      </c>
+      <c r="Q185" s="4">
+        <v>3</v>
+      </c>
+      <c r="R185" s="9">
+        <v>4.057863417526395</v>
+      </c>
+      <c r="S185" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T185" s="4">
+        <v>4</v>
+      </c>
+      <c r="U185" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V185" s="4">
+        <v>1</v>
+      </c>
+      <c r="W185" s="4">
+        <v>52.5</v>
+      </c>
+      <c r="X185" s="9">
+        <v>52.912084762835427</v>
+      </c>
+      <c r="Y185" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z185" s="4">
+        <v>80</v>
+      </c>
+      <c r="AA185" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB185" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC185" s="5">
+        <v>0.29294983545939129</v>
+      </c>
+      <c r="AD185" s="5">
+        <v>-0.32815566429725063</v>
+      </c>
+      <c r="AE185" s="5">
+        <v>1.3250324033921771E-2</v>
+      </c>
+      <c r="AF185" s="5">
+        <v>0.32815566429725063</v>
+      </c>
+      <c r="AG185" s="5">
+        <v>-0.29294983545939129</v>
+      </c>
+      <c r="AH185" s="5">
+        <v>-1.3250324033921771E-2</v>
+      </c>
+    </row>
+    <row r="186" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B186" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C186" s="4">
+        <v>17</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E186" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F186" s="4">
+        <v>27</v>
+      </c>
+      <c r="G186" s="4">
+        <v>24</v>
+      </c>
+      <c r="H186" s="8">
+        <v>0.29752007082527432</v>
+      </c>
+      <c r="I186" s="4">
+        <v>236</v>
+      </c>
+      <c r="J186" s="8">
+        <v>0.70247992917472568</v>
+      </c>
+      <c r="K186" s="4">
+        <v>-236</v>
+      </c>
+      <c r="L186" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M186" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="N186" s="4">
+        <v>0</v>
+      </c>
+      <c r="O186" s="9">
+        <v>21.72428470641804</v>
+      </c>
+      <c r="P186" s="15">
+        <v>30.27893969611544</v>
+      </c>
+      <c r="Q186" s="4">
+        <v>-7.5</v>
+      </c>
+      <c r="R186" s="9">
+        <v>-8.5546549896974042</v>
+      </c>
+      <c r="S186" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T186" s="4">
+        <v>3</v>
+      </c>
+      <c r="U186" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V186" s="4">
+        <v>0</v>
+      </c>
+      <c r="W186" s="4">
+        <v>49.5</v>
+      </c>
+      <c r="X186" s="9">
+        <v>52.003224402533483</v>
+      </c>
+      <c r="Y186" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z186" s="4">
+        <v>51</v>
+      </c>
+      <c r="AA186" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB186" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC186" s="5">
+        <v>0.11564381617420121</v>
+      </c>
+      <c r="AD186" s="5">
+        <v>0.1016359402583196</v>
+      </c>
+      <c r="AE186" s="5">
+        <v>-0.3074916090284075</v>
+      </c>
+      <c r="AF186" s="5">
+        <v>-0.1016359402583196</v>
+      </c>
+      <c r="AG186" s="5">
+        <v>-0.11564381617420121</v>
+      </c>
+      <c r="AH186" s="5">
+        <v>0.3074916090284075</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="AF7:AH7"/>
@@ -15527,7 +17145,7 @@
     <mergeCell ref="AC7:AE7"/>
   </mergeCells>
   <conditionalFormatting sqref="AC9:AC23">
-    <cfRule type="colorScale" priority="89">
+    <cfRule type="colorScale" priority="98">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15539,7 +17157,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC24:AC38">
-    <cfRule type="colorScale" priority="82">
+    <cfRule type="colorScale" priority="91">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15551,7 +17169,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC39:AC51">
-    <cfRule type="colorScale" priority="70">
+    <cfRule type="colorScale" priority="79">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15563,7 +17181,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC52:AC65">
-    <cfRule type="colorScale" priority="63">
+    <cfRule type="colorScale" priority="72">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15575,7 +17193,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC66:AC79">
-    <cfRule type="colorScale" priority="56">
+    <cfRule type="colorScale" priority="65">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15587,7 +17205,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC80:AC94">
-    <cfRule type="colorScale" priority="53">
+    <cfRule type="colorScale" priority="62">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15599,6 +17217,18 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC95:AC108">
+    <cfRule type="colorScale" priority="49">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC109:AC124">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="min"/>
@@ -15610,7 +17240,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC109:AC124">
+  <conditionalFormatting sqref="AC125:AC138">
     <cfRule type="colorScale" priority="31">
       <colorScale>
         <cfvo type="min"/>
@@ -15622,7 +17252,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC125:AC138">
+  <conditionalFormatting sqref="AC139:AC154">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min"/>
@@ -15634,7 +17264,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC139:AC154">
+  <conditionalFormatting sqref="AC155:AC170">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -15646,7 +17276,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC155:AC170">
+  <conditionalFormatting sqref="AC171:AC186">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -15659,7 +17289,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD9:AD23">
-    <cfRule type="colorScale" priority="88">
+    <cfRule type="colorScale" priority="97">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15671,7 +17301,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD24:AD38">
-    <cfRule type="colorScale" priority="81">
+    <cfRule type="colorScale" priority="90">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15683,7 +17313,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD39:AD51">
-    <cfRule type="colorScale" priority="71">
+    <cfRule type="colorScale" priority="80">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15695,7 +17325,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD52:AD65">
-    <cfRule type="colorScale" priority="64">
+    <cfRule type="colorScale" priority="73">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15707,7 +17337,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD66:AD79">
-    <cfRule type="colorScale" priority="57">
+    <cfRule type="colorScale" priority="66">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15719,7 +17349,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD80:AD94">
-    <cfRule type="colorScale" priority="52">
+    <cfRule type="colorScale" priority="61">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15731,6 +17361,18 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD95:AD108">
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD109:AD124">
     <cfRule type="colorScale" priority="41">
       <colorScale>
         <cfvo type="min"/>
@@ -15742,7 +17384,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD109:AD124">
+  <conditionalFormatting sqref="AD125:AD138">
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="min"/>
@@ -15754,7 +17396,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD125:AD138">
+  <conditionalFormatting sqref="AD139:AD154">
     <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
@@ -15766,7 +17408,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD139:AD154">
+  <conditionalFormatting sqref="AD155:AD170">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -15778,7 +17420,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD155:AD170">
+  <conditionalFormatting sqref="AD171:AD186">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -15791,7 +17433,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE9:AE23">
-    <cfRule type="colorScale" priority="87">
+    <cfRule type="colorScale" priority="96">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15803,7 +17445,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE24:AE38">
-    <cfRule type="colorScale" priority="80">
+    <cfRule type="colorScale" priority="89">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15815,7 +17457,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE39:AE51">
-    <cfRule type="colorScale" priority="72">
+    <cfRule type="colorScale" priority="81">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15827,7 +17469,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE52:AE65">
-    <cfRule type="colorScale" priority="65">
+    <cfRule type="colorScale" priority="74">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15839,7 +17481,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE66:AE79">
-    <cfRule type="colorScale" priority="58">
+    <cfRule type="colorScale" priority="67">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15851,6 +17493,18 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE80:AE94">
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE95:AE108">
     <cfRule type="colorScale" priority="51">
       <colorScale>
         <cfvo type="min"/>
@@ -15862,7 +17516,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE95:AE108">
+  <conditionalFormatting sqref="AE109:AE124">
     <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="min"/>
@@ -15874,7 +17528,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE109:AE124">
+  <conditionalFormatting sqref="AE125:AE138">
     <cfRule type="colorScale" priority="33">
       <colorScale>
         <cfvo type="min"/>
@@ -15886,7 +17540,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE125:AE138">
+  <conditionalFormatting sqref="AE139:AE154">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
@@ -15898,7 +17552,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE139:AE154">
+  <conditionalFormatting sqref="AE155:AE170">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -15910,7 +17564,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE155:AE170">
+  <conditionalFormatting sqref="AE171:AE186">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -15923,7 +17577,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF9:AF23">
-    <cfRule type="colorScale" priority="86">
+    <cfRule type="colorScale" priority="95">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15935,7 +17589,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF24:AF38">
-    <cfRule type="colorScale" priority="79">
+    <cfRule type="colorScale" priority="88">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15947,7 +17601,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF39:AF51">
-    <cfRule type="colorScale" priority="73">
+    <cfRule type="colorScale" priority="82">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15959,7 +17613,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF52:AF65">
-    <cfRule type="colorScale" priority="66">
+    <cfRule type="colorScale" priority="75">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15971,6 +17625,18 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF66:AF79">
+    <cfRule type="colorScale" priority="68">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF80:AF94">
     <cfRule type="colorScale" priority="59">
       <colorScale>
         <cfvo type="min"/>
@@ -15982,8 +17648,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF80:AF94">
-    <cfRule type="colorScale" priority="50">
+  <conditionalFormatting sqref="AF95:AF108">
+    <cfRule type="colorScale" priority="52">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15994,7 +17660,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF95:AF108">
+  <conditionalFormatting sqref="AF109:AF124">
     <cfRule type="colorScale" priority="43">
       <colorScale>
         <cfvo type="min"/>
@@ -16006,7 +17672,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF109:AF124">
+  <conditionalFormatting sqref="AF125:AF138">
     <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min"/>
@@ -16018,7 +17684,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF125:AF138">
+  <conditionalFormatting sqref="AF139:AF154">
     <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="min"/>
@@ -16030,7 +17696,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF139:AF154">
+  <conditionalFormatting sqref="AF155:AF170">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -16042,7 +17708,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF155:AF170">
+  <conditionalFormatting sqref="AF171:AF186">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -16055,7 +17721,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG9:AG23">
-    <cfRule type="colorScale" priority="85">
+    <cfRule type="colorScale" priority="94">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -16067,7 +17733,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG24:AG38">
-    <cfRule type="colorScale" priority="78">
+    <cfRule type="colorScale" priority="87">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -16079,7 +17745,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG39:AG51">
-    <cfRule type="colorScale" priority="74">
+    <cfRule type="colorScale" priority="83">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -16091,7 +17757,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG52:AG65">
-    <cfRule type="colorScale" priority="67">
+    <cfRule type="colorScale" priority="76">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -16103,7 +17769,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG66:AG79">
-    <cfRule type="colorScale" priority="60">
+    <cfRule type="colorScale" priority="69">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -16115,7 +17781,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG80:AG94">
-    <cfRule type="colorScale" priority="49">
+    <cfRule type="colorScale" priority="58">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -16127,6 +17793,18 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG95:AG108">
+    <cfRule type="colorScale" priority="53">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG109:AG124">
     <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="min"/>
@@ -16138,7 +17816,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG109:AG124">
+  <conditionalFormatting sqref="AG125:AG138">
     <cfRule type="colorScale" priority="35">
       <colorScale>
         <cfvo type="min"/>
@@ -16150,7 +17828,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG125:AG138">
+  <conditionalFormatting sqref="AG139:AG154">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
@@ -16162,7 +17840,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG139:AG154">
+  <conditionalFormatting sqref="AG155:AG170">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -16174,7 +17852,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG155:AG170">
+  <conditionalFormatting sqref="AG171:AG186">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -16187,6 +17865,30 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH9:AH23">
+    <cfRule type="colorScale" priority="93">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH24:AH38">
+    <cfRule type="colorScale" priority="86">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH39:AH51">
     <cfRule type="colorScale" priority="84">
       <colorScale>
         <cfvo type="min"/>
@@ -16198,7 +17900,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH24:AH38">
+  <conditionalFormatting sqref="AH52:AH65">
     <cfRule type="colorScale" priority="77">
       <colorScale>
         <cfvo type="min"/>
@@ -16210,32 +17912,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH39:AH51">
-    <cfRule type="colorScale" priority="75">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH52:AH65">
-    <cfRule type="colorScale" priority="68">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AH66:AH79">
-    <cfRule type="colorScale" priority="61">
+    <cfRule type="colorScale" priority="70">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -16247,7 +17925,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH80:AH94">
-    <cfRule type="colorScale" priority="48">
+    <cfRule type="colorScale" priority="57">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -16259,6 +17937,18 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH95:AH108">
+    <cfRule type="colorScale" priority="54">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH109:AH124">
     <cfRule type="colorScale" priority="45">
       <colorScale>
         <cfvo type="min"/>
@@ -16270,7 +17960,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH109:AH124">
+  <conditionalFormatting sqref="AH125:AH138">
     <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="min"/>
@@ -16282,7 +17972,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH125:AH138">
+  <conditionalFormatting sqref="AH139:AH154">
     <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="min"/>
@@ -16294,7 +17984,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH139:AH154">
+  <conditionalFormatting sqref="AH155:AH170">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
@@ -16306,7 +17996,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH155:AH170">
+  <conditionalFormatting sqref="AH171:AH186">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -16326,7 +18016,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="54" id="{EDEA8277-96E2-534B-9496-1DB5484BFD68}">
+          <x14:cfRule type="iconSet" priority="63" id="{EDEA8277-96E2-534B-9496-1DB5484BFD68}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -16345,7 +18035,7 @@
           <xm:sqref>N80:N94</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="37" id="{DD4EF5CC-2E62-F245-AF58-2756E5752FDF}">
+          <x14:cfRule type="iconSet" priority="46" id="{DD4EF5CC-2E62-F245-AF58-2756E5752FDF}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -16364,7 +18054,7 @@
           <xm:sqref>N95:N108</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="28" id="{37C61786-4A12-0746-A763-4990B69F05C7}">
+          <x14:cfRule type="iconSet" priority="37" id="{37C61786-4A12-0746-A763-4990B69F05C7}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -16383,7 +18073,7 @@
           <xm:sqref>N109:N124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="19" id="{212E7F37-E966-AF4F-A0C3-E0E8E1340734}">
+          <x14:cfRule type="iconSet" priority="28" id="{212E7F37-E966-AF4F-A0C3-E0E8E1340734}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -16402,7 +18092,7 @@
           <xm:sqref>N125:N138</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="10" id="{9742010F-AC5F-C647-A8CE-71E3275DF15E}">
+          <x14:cfRule type="iconSet" priority="19" id="{9742010F-AC5F-C647-A8CE-71E3275DF15E}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -16421,7 +18111,7 @@
           <xm:sqref>N139:N154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="1" id="{53BBD899-D2C8-074A-936B-361D7C508C63}">
+          <x14:cfRule type="iconSet" priority="10" id="{53BBD899-D2C8-074A-936B-361D7C508C63}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -16440,7 +18130,26 @@
           <xm:sqref>N155:N170</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="76" id="{48C4D57C-361D-AB47-A2B7-3D4E42CE6188}">
+          <x14:cfRule type="iconSet" priority="1" id="{A12D9CF1-1026-094B-90AD-EA1CA9A2D92B}">
+            <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>N171:N186</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="85" id="{48C4D57C-361D-AB47-A2B7-3D4E42CE6188}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -16459,7 +18168,7 @@
           <xm:sqref>N24:AA38</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="69" id="{C3D59626-8CA7-8645-8330-0E71AB30C540}">
+          <x14:cfRule type="iconSet" priority="78" id="{C3D59626-8CA7-8645-8330-0E71AB30C540}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -16478,7 +18187,7 @@
           <xm:sqref>N39:AA51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="62" id="{6D153A18-6D77-9445-BF8D-3BA4EDDD3FBA}">
+          <x14:cfRule type="iconSet" priority="71" id="{6D153A18-6D77-9445-BF8D-3BA4EDDD3FBA}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -16497,7 +18206,7 @@
           <xm:sqref>N52:AA65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="55" id="{C34C5491-7DF8-D04C-B3C0-3779DAAA33EE}">
+          <x14:cfRule type="iconSet" priority="64" id="{C34C5491-7DF8-D04C-B3C0-3779DAAA33EE}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -16516,7 +18225,7 @@
           <xm:sqref>N66:AA79</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="83" id="{4DC6D28C-E799-D04F-BAD2-092B8419C03D}">
+          <x14:cfRule type="iconSet" priority="92" id="{4DC6D28C-E799-D04F-BAD2-092B8419C03D}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -16535,7 +18244,7 @@
           <xm:sqref>N9:AB23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="47" id="{92AD66C2-D91E-D648-9AC6-2417C2445C43}">
+          <x14:cfRule type="iconSet" priority="56" id="{92AD66C2-D91E-D648-9AC6-2417C2445C43}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -16554,7 +18263,7 @@
           <xm:sqref>V80:V94</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="38" id="{2D523F71-4BB4-9940-8B5D-C962CA9D6F15}">
+          <x14:cfRule type="iconSet" priority="47" id="{2D523F71-4BB4-9940-8B5D-C962CA9D6F15}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -16573,7 +18282,7 @@
           <xm:sqref>V95:V108</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="29" id="{2094B9A9-658A-3D41-A969-4F7B5F1A7D42}">
+          <x14:cfRule type="iconSet" priority="38" id="{2094B9A9-658A-3D41-A969-4F7B5F1A7D42}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -16592,7 +18301,7 @@
           <xm:sqref>V109:V124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="20" id="{7AD482D6-AFFD-C546-9642-22AC15E71775}">
+          <x14:cfRule type="iconSet" priority="29" id="{7AD482D6-AFFD-C546-9642-22AC15E71775}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -16611,7 +18320,7 @@
           <xm:sqref>V125:V138</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="11" id="{3B475BB3-A842-F24C-8D71-84FCC9C136B4}">
+          <x14:cfRule type="iconSet" priority="20" id="{3B475BB3-A842-F24C-8D71-84FCC9C136B4}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -16630,7 +18339,7 @@
           <xm:sqref>V139:V154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="2" id="{ADD77C7B-8E6B-7A48-8AAC-8A63FE24FF97}">
+          <x14:cfRule type="iconSet" priority="11" id="{ADD77C7B-8E6B-7A48-8AAC-8A63FE24FF97}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -16649,7 +18358,26 @@
           <xm:sqref>V155:V170</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="46" id="{409D8166-545E-3045-805D-7C96DC6956B1}">
+          <x14:cfRule type="iconSet" priority="2" id="{17F128E4-E069-B54E-9112-2E64042DD7FA}">
+            <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>V171:V186</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="55" id="{409D8166-545E-3045-805D-7C96DC6956B1}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -16668,7 +18396,7 @@
           <xm:sqref>AB80:AB94</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="39" id="{578139A0-9556-A24C-89D1-3B66D89331FA}">
+          <x14:cfRule type="iconSet" priority="48" id="{578139A0-9556-A24C-89D1-3B66D89331FA}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -16687,7 +18415,7 @@
           <xm:sqref>AB95:AB108</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="30" id="{869A3731-7EDB-9143-AD0D-591DEB781BAF}">
+          <x14:cfRule type="iconSet" priority="39" id="{869A3731-7EDB-9143-AD0D-591DEB781BAF}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -16706,7 +18434,7 @@
           <xm:sqref>AB109:AB124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="21" id="{90EFE230-91F0-784C-B726-5BE6F84EE2FC}">
+          <x14:cfRule type="iconSet" priority="30" id="{90EFE230-91F0-784C-B726-5BE6F84EE2FC}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -16725,7 +18453,7 @@
           <xm:sqref>AB125:AB138</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="12" id="{7941D79E-AD1D-3F44-8D4F-313B45BDFDD4}">
+          <x14:cfRule type="iconSet" priority="21" id="{7941D79E-AD1D-3F44-8D4F-313B45BDFDD4}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -16744,7 +18472,7 @@
           <xm:sqref>AB139:AB154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="3" id="{DEBE5BDC-29DE-8246-9122-5A2B43CD922F}">
+          <x14:cfRule type="iconSet" priority="12" id="{DEBE5BDC-29DE-8246-9122-5A2B43CD922F}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -16761,6 +18489,25 @@
             </x14:iconSet>
           </x14:cfRule>
           <xm:sqref>AB155:AB170</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="3" id="{6EF58D86-81A1-CC4C-B5CF-2174EDC27A28}">
+            <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>AB171:AB186</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -24541,9 +26288,2002 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30C39093-D2E4-C14D-97FC-13D68708F603}">
+  <dimension ref="B2:AH24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="3" width="9.5" customWidth="1"/>
+    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.1640625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="4.83203125" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="6.6640625" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="14" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="11.6640625" customWidth="1"/>
+    <col min="17" max="17" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="10.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B2" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="13">
+        <f>COUNTA($C$9:$C$24)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B3" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="13">
+        <f>SUM(N9:$N$24)</f>
+        <v>10</v>
+      </c>
+      <c r="D3" s="14">
+        <f>C3/$C$2</f>
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="4" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B4" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="13">
+        <f>SUM(V9:$V$24)</f>
+        <v>10</v>
+      </c>
+      <c r="D4" s="14">
+        <f t="shared" ref="D4:D5" si="0">C4/$C$2</f>
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="5" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B5" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5" s="13">
+        <f>SUM(AB9:$AB$24)</f>
+        <v>7</v>
+      </c>
+      <c r="D5" s="14">
+        <f t="shared" si="0"/>
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="6" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="C6" s="6"/>
+    </row>
+    <row r="7" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="H7" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="R7" s="19"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="19"/>
+      <c r="U7" s="19"/>
+      <c r="V7" s="19"/>
+      <c r="W7" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="X7" s="19"/>
+      <c r="Y7" s="19"/>
+      <c r="Z7" s="19"/>
+      <c r="AA7" s="19"/>
+      <c r="AB7" s="19"/>
+      <c r="AC7" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD7" s="19"/>
+      <c r="AE7" s="19"/>
+      <c r="AF7" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG7" s="19"/>
+      <c r="AH7" s="19"/>
+    </row>
+    <row r="8" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="Z8" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AA8" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AB8" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AC8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AE8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AH8" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B9" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C9" s="4">
+        <v>17</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="4">
+        <v>23</v>
+      </c>
+      <c r="G9" s="4">
+        <v>30</v>
+      </c>
+      <c r="H9" s="8">
+        <v>0.41282143019888617</v>
+      </c>
+      <c r="I9" s="4">
+        <v>142</v>
+      </c>
+      <c r="J9" s="8">
+        <v>0.58717856980111383</v>
+      </c>
+      <c r="K9" s="4">
+        <v>-142</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N9" s="4">
+        <v>1</v>
+      </c>
+      <c r="O9" s="15">
+        <v>21.332065901802299</v>
+      </c>
+      <c r="P9" s="15">
+        <v>24.126748990821628</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>-8.5</v>
+      </c>
+      <c r="R9" s="15">
+        <v>-2.7946830890193302</v>
+      </c>
+      <c r="S9" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T9" s="4">
+        <v>-7</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V9" s="4">
+        <v>1</v>
+      </c>
+      <c r="W9" s="4">
+        <v>50.5</v>
+      </c>
+      <c r="X9" s="9">
+        <v>45.458814892623927</v>
+      </c>
+      <c r="Y9" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z9" s="4">
+        <v>53</v>
+      </c>
+      <c r="AA9" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="5">
+        <v>0.2319403360056323</v>
+      </c>
+      <c r="AD9" s="5">
+        <v>-0.22120343083920679</v>
+      </c>
+      <c r="AE9" s="5">
+        <v>9.9053645956105205E-2</v>
+      </c>
+      <c r="AF9" s="5">
+        <v>0.22120343083920679</v>
+      </c>
+      <c r="AG9" s="5">
+        <v>-0.2319403360056323</v>
+      </c>
+      <c r="AH9" s="5">
+        <v>-9.9053645956105205E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B10" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C10" s="4">
+        <v>17</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="4">
+        <v>23</v>
+      </c>
+      <c r="G10" s="4">
+        <v>10</v>
+      </c>
+      <c r="H10" s="8">
+        <v>0.42549773720014372</v>
+      </c>
+      <c r="I10" s="4">
+        <v>135</v>
+      </c>
+      <c r="J10" s="8">
+        <v>0.57450226279985628</v>
+      </c>
+      <c r="K10" s="4">
+        <v>-135</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="N10" s="4">
+        <v>0</v>
+      </c>
+      <c r="O10" s="15">
+        <v>20.706238304403229</v>
+      </c>
+      <c r="P10" s="15">
+        <v>24.307338431866409</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>-7.5</v>
+      </c>
+      <c r="R10" s="15">
+        <v>-3.6011001274631802</v>
+      </c>
+      <c r="S10" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T10" s="4">
+        <v>13</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V10" s="4">
+        <v>1</v>
+      </c>
+      <c r="W10" s="4">
+        <v>43.5</v>
+      </c>
+      <c r="X10" s="9">
+        <v>45.013576736269641</v>
+      </c>
+      <c r="Y10" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z10" s="4">
+        <v>33</v>
+      </c>
+      <c r="AA10" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="5">
+        <v>-0.25252072016398108</v>
+      </c>
+      <c r="AD10" s="5">
+        <v>0.46371796727180481</v>
+      </c>
+      <c r="AE10" s="5">
+        <v>-2.5729133532597471E-2</v>
+      </c>
+      <c r="AF10" s="5">
+        <v>-0.46371796727180481</v>
+      </c>
+      <c r="AG10" s="5">
+        <v>0.25252072016398108</v>
+      </c>
+      <c r="AH10" s="5">
+        <v>2.5729133532597471E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B11" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C11" s="4">
+        <v>17</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="4">
+        <v>13</v>
+      </c>
+      <c r="G11" s="4">
+        <v>20</v>
+      </c>
+      <c r="H11" s="8">
+        <v>0.43793113003547351</v>
+      </c>
+      <c r="I11" s="4">
+        <v>128</v>
+      </c>
+      <c r="J11" s="8">
+        <v>0.56206886996452643</v>
+      </c>
+      <c r="K11" s="4">
+        <v>-128</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N11" s="4">
+        <v>1</v>
+      </c>
+      <c r="O11" s="15">
+        <v>22.35682837886436</v>
+      </c>
+      <c r="P11" s="15">
+        <v>23.84626020725829</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>-13.5</v>
+      </c>
+      <c r="R11" s="9">
+        <v>-1.489431828393929</v>
+      </c>
+      <c r="S11" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T11" s="4">
+        <v>-7</v>
+      </c>
+      <c r="U11" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V11" s="4">
+        <v>1</v>
+      </c>
+      <c r="W11" s="4">
+        <v>36.5</v>
+      </c>
+      <c r="X11" s="9">
+        <v>46.203088586122647</v>
+      </c>
+      <c r="Y11" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z11" s="4">
+        <v>33</v>
+      </c>
+      <c r="AA11" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="5">
+        <v>-0.15266824903942289</v>
+      </c>
+      <c r="AD11" s="5">
+        <v>-8.4641396159857094E-2</v>
+      </c>
+      <c r="AE11" s="5">
+        <v>0.28701658937193097</v>
+      </c>
+      <c r="AF11" s="5">
+        <v>8.4641396159857094E-2</v>
+      </c>
+      <c r="AG11" s="5">
+        <v>0.15266824903942289</v>
+      </c>
+      <c r="AH11" s="5">
+        <v>-0.28701658937193097</v>
+      </c>
+    </row>
+    <row r="12" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B12" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C12" s="4">
+        <v>17</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" s="4">
+        <v>16</v>
+      </c>
+      <c r="G12" s="4">
+        <v>20</v>
+      </c>
+      <c r="H12" s="8">
+        <v>0.53751412059105863</v>
+      </c>
+      <c r="I12" s="4">
+        <v>-116</v>
+      </c>
+      <c r="J12" s="8">
+        <v>0.46248587940894142</v>
+      </c>
+      <c r="K12" s="4">
+        <v>116</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="N12" s="4">
+        <v>0</v>
+      </c>
+      <c r="O12" s="15">
+        <v>22.239051791293011</v>
+      </c>
+      <c r="P12" s="15">
+        <v>22.121618389548519</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="R12" s="9">
+        <v>0.11743340174448851</v>
+      </c>
+      <c r="S12" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T12" s="4">
+        <v>-4</v>
+      </c>
+      <c r="U12" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V12" s="4">
+        <v>1</v>
+      </c>
+      <c r="W12" s="4">
+        <v>39.5</v>
+      </c>
+      <c r="X12" s="9">
+        <v>44.360670180841517</v>
+      </c>
+      <c r="Y12" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z12" s="4">
+        <v>36</v>
+      </c>
+      <c r="AA12" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB12" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="5">
+        <v>-0.14214936513749379</v>
+      </c>
+      <c r="AD12" s="5">
+        <v>7.9646910390546249E-2</v>
+      </c>
+      <c r="AE12" s="5">
+        <v>-0.21228645587789599</v>
+      </c>
+      <c r="AF12" s="5">
+        <v>-7.9646910390546249E-2</v>
+      </c>
+      <c r="AG12" s="5">
+        <v>0.14214936513749379</v>
+      </c>
+      <c r="AH12" s="5">
+        <v>0.21228645587789599</v>
+      </c>
+    </row>
+    <row r="13" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B13" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C13" s="4">
+        <v>17</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="4">
+        <v>24</v>
+      </c>
+      <c r="G13" s="4">
+        <v>41</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0.63540445235652621</v>
+      </c>
+      <c r="I13" s="4">
+        <v>-174</v>
+      </c>
+      <c r="J13" s="8">
+        <v>0.36459554764347379</v>
+      </c>
+      <c r="K13" s="4">
+        <v>174</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N13" s="4">
+        <v>0</v>
+      </c>
+      <c r="O13" s="15">
+        <v>25.37538507781553</v>
+      </c>
+      <c r="P13" s="15">
+        <v>25.26811681177249</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>3</v>
+      </c>
+      <c r="R13" s="9">
+        <v>0.1072682660430466</v>
+      </c>
+      <c r="S13" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T13" s="4">
+        <v>-17</v>
+      </c>
+      <c r="U13" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V13" s="4">
+        <v>1</v>
+      </c>
+      <c r="W13" s="4">
+        <v>40.5</v>
+      </c>
+      <c r="X13" s="9">
+        <v>50.643501889588023</v>
+      </c>
+      <c r="Y13" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z13" s="4">
+        <v>65</v>
+      </c>
+      <c r="AA13" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB13" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="5">
+        <v>0.117405456966824</v>
+      </c>
+      <c r="AD13" s="5">
+        <v>-0.33768915812174483</v>
+      </c>
+      <c r="AE13" s="5">
+        <v>-4.0311717987060536E-3</v>
+      </c>
+      <c r="AF13" s="5">
+        <v>0.33768915812174483</v>
+      </c>
+      <c r="AG13" s="5">
+        <v>-0.117405456966824</v>
+      </c>
+      <c r="AH13" s="5">
+        <v>4.0311717987060536E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B14" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C14" s="4">
+        <v>17</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="4">
+        <v>10</v>
+      </c>
+      <c r="G14" s="4">
+        <v>27</v>
+      </c>
+      <c r="H14" s="8">
+        <v>0.35131865483870311</v>
+      </c>
+      <c r="I14" s="4">
+        <v>184</v>
+      </c>
+      <c r="J14" s="8">
+        <v>0.64868134516129694</v>
+      </c>
+      <c r="K14" s="4">
+        <v>-184</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N14" s="4">
+        <v>1</v>
+      </c>
+      <c r="O14" s="15">
+        <v>18.598230455760248</v>
+      </c>
+      <c r="P14" s="15">
+        <v>28.40619118159827</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>-7</v>
+      </c>
+      <c r="R14" s="15">
+        <v>-9.807960725838015</v>
+      </c>
+      <c r="S14" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T14" s="4">
+        <v>-17</v>
+      </c>
+      <c r="U14" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V14" s="4">
+        <v>1</v>
+      </c>
+      <c r="W14" s="4">
+        <v>42.5</v>
+      </c>
+      <c r="X14" s="9">
+        <v>47.004421637358519</v>
+      </c>
+      <c r="Y14" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z14" s="4">
+        <v>37</v>
+      </c>
+      <c r="AA14" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB14" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="5">
+        <v>-0.47411228179931642</v>
+      </c>
+      <c r="AD14" s="5">
+        <v>5.35889038672814E-2</v>
+      </c>
+      <c r="AE14" s="5">
+        <v>-9.2909699394589373E-2</v>
+      </c>
+      <c r="AF14" s="5">
+        <v>-5.35889038672814E-2</v>
+      </c>
+      <c r="AG14" s="5">
+        <v>0.47411228179931642</v>
+      </c>
+      <c r="AH14" s="5">
+        <v>9.2909699394589373E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B15" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C15" s="4">
+        <v>17</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="4">
+        <v>37</v>
+      </c>
+      <c r="G15" s="4">
+        <v>14</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0.61258942461821686</v>
+      </c>
+      <c r="I15" s="4">
+        <v>-158</v>
+      </c>
+      <c r="J15" s="8">
+        <v>0.38741057538178308</v>
+      </c>
+      <c r="K15" s="4">
+        <v>158</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="N15" s="4">
+        <v>1</v>
+      </c>
+      <c r="O15" s="15">
+        <v>26.148549655458758</v>
+      </c>
+      <c r="P15" s="15">
+        <v>24.94756395998073</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="R15" s="9">
+        <v>1.200985695478028</v>
+      </c>
+      <c r="S15" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T15" s="4">
+        <v>23</v>
+      </c>
+      <c r="U15" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V15" s="4">
+        <v>0</v>
+      </c>
+      <c r="W15" s="4">
+        <v>52.5</v>
+      </c>
+      <c r="X15" s="9">
+        <v>51.096113615439492</v>
+      </c>
+      <c r="Y15" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z15" s="4">
+        <v>51</v>
+      </c>
+      <c r="AA15" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB15" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC15" s="5">
+        <v>0.33032649837128097</v>
+      </c>
+      <c r="AD15" s="5">
+        <v>2.2704843889202991E-2</v>
+      </c>
+      <c r="AE15" s="5">
+        <v>-5.1734850956843451E-2</v>
+      </c>
+      <c r="AF15" s="5">
+        <v>-2.2704843889202991E-2</v>
+      </c>
+      <c r="AG15" s="5">
+        <v>-0.33032649837128097</v>
+      </c>
+      <c r="AH15" s="5">
+        <v>5.1734850956843451E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B16" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C16" s="4">
+        <v>17</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="4">
+        <v>13</v>
+      </c>
+      <c r="G16" s="4">
+        <v>6</v>
+      </c>
+      <c r="H16" s="8">
+        <v>0.30626109673214358</v>
+      </c>
+      <c r="I16" s="4">
+        <v>226</v>
+      </c>
+      <c r="J16" s="8">
+        <v>0.69373890326785637</v>
+      </c>
+      <c r="K16" s="4">
+        <v>-226</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="N16" s="4">
+        <v>0</v>
+      </c>
+      <c r="O16" s="15">
+        <v>19.07209487906913</v>
+      </c>
+      <c r="P16" s="15">
+        <v>22.81096650874672</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>-3</v>
+      </c>
+      <c r="R16" s="15">
+        <v>-3.7388716296775901</v>
+      </c>
+      <c r="S16" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T16" s="4">
+        <v>7</v>
+      </c>
+      <c r="U16" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V16" s="4">
+        <v>0</v>
+      </c>
+      <c r="W16" s="4">
+        <v>33.5</v>
+      </c>
+      <c r="X16" s="9">
+        <v>41.883061387815857</v>
+      </c>
+      <c r="Y16" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z16" s="4">
+        <v>19</v>
+      </c>
+      <c r="AA16" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="5">
+        <v>-0.20642806034462119</v>
+      </c>
+      <c r="AD16" s="5">
+        <v>0.21981136500835419</v>
+      </c>
+      <c r="AE16" s="5">
+        <v>0.23588852655319939</v>
+      </c>
+      <c r="AF16" s="5">
+        <v>-0.21981136500835419</v>
+      </c>
+      <c r="AG16" s="5">
+        <v>0.20642806034462119</v>
+      </c>
+      <c r="AH16" s="5">
+        <v>-0.23588852655319939</v>
+      </c>
+    </row>
+    <row r="17" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B17" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C17" s="4">
+        <v>17</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="4">
+        <v>17</v>
+      </c>
+      <c r="G17" s="4">
+        <v>23</v>
+      </c>
+      <c r="H17" s="8">
+        <v>0.41131428422671379</v>
+      </c>
+      <c r="I17" s="4">
+        <v>143</v>
+      </c>
+      <c r="J17" s="8">
+        <v>0.58868571577328621</v>
+      </c>
+      <c r="K17" s="4">
+        <v>-143</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N17" s="4">
+        <v>1</v>
+      </c>
+      <c r="O17" s="15">
+        <v>20.869518837182529</v>
+      </c>
+      <c r="P17" s="15">
+        <v>24.152507244820601</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>-6.5</v>
+      </c>
+      <c r="R17" s="9">
+        <v>-3.2829884076380789</v>
+      </c>
+      <c r="S17" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T17" s="4">
+        <v>-6</v>
+      </c>
+      <c r="U17" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V17" s="4">
+        <v>1</v>
+      </c>
+      <c r="W17" s="4">
+        <v>48.5</v>
+      </c>
+      <c r="X17" s="9">
+        <v>45.02202608200313</v>
+      </c>
+      <c r="Y17" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z17" s="4">
+        <v>40</v>
+      </c>
+      <c r="AA17" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB17" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="5">
+        <v>-0.17091699232134899</v>
+      </c>
+      <c r="AD17" s="5">
+        <v>4.0298069732776576E-3</v>
+      </c>
+      <c r="AE17" s="5">
+        <v>1.0396182537078859E-2</v>
+      </c>
+      <c r="AF17" s="5">
+        <v>-4.0298069732776576E-3</v>
+      </c>
+      <c r="AG17" s="5">
+        <v>0.17091699232134899</v>
+      </c>
+      <c r="AH17" s="5">
+        <v>-1.0396182537078859E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B18" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C18" s="4">
+        <v>17</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="4">
+        <v>20</v>
+      </c>
+      <c r="G18" s="4">
+        <v>17</v>
+      </c>
+      <c r="H18" s="8">
+        <v>0.54252769259493627</v>
+      </c>
+      <c r="I18" s="4">
+        <v>-118</v>
+      </c>
+      <c r="J18" s="8">
+        <v>0.45747230740506373</v>
+      </c>
+      <c r="K18" s="4">
+        <v>118</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N18" s="4">
+        <v>1</v>
+      </c>
+      <c r="O18" s="15">
+        <v>25.357523161176289</v>
+      </c>
+      <c r="P18" s="15">
+        <v>24.216388890297029</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>-5.5</v>
+      </c>
+      <c r="R18" s="9">
+        <v>1.141134270879256</v>
+      </c>
+      <c r="S18" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T18" s="4">
+        <v>3</v>
+      </c>
+      <c r="U18" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V18" s="4">
+        <v>1</v>
+      </c>
+      <c r="W18" s="4">
+        <v>45.5</v>
+      </c>
+      <c r="X18" s="9">
+        <v>49.573912051473307</v>
+      </c>
+      <c r="Y18" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z18" s="4">
+        <v>37</v>
+      </c>
+      <c r="AA18" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB18" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="5">
+        <v>6.0104476081000432E-2</v>
+      </c>
+      <c r="AD18" s="5">
+        <v>-3.7184526671224558E-2</v>
+      </c>
+      <c r="AE18" s="5">
+        <v>0.20254220247268681</v>
+      </c>
+      <c r="AF18" s="5">
+        <v>3.7184526671224558E-2</v>
+      </c>
+      <c r="AG18" s="5">
+        <v>-6.0104476081000432E-2</v>
+      </c>
+      <c r="AH18" s="5">
+        <v>-0.20254220247268681</v>
+      </c>
+    </row>
+    <row r="19" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B19" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C19" s="4">
+        <v>17</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" s="4">
+        <v>10</v>
+      </c>
+      <c r="G19" s="4">
+        <v>42</v>
+      </c>
+      <c r="H19" s="8">
+        <v>0.233976447694279</v>
+      </c>
+      <c r="I19" s="4">
+        <v>327</v>
+      </c>
+      <c r="J19" s="8">
+        <v>0.76602355230572095</v>
+      </c>
+      <c r="K19" s="4">
+        <v>-327</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N19" s="4">
+        <v>1</v>
+      </c>
+      <c r="O19" s="15">
+        <v>18.15545795202846</v>
+      </c>
+      <c r="P19" s="15">
+        <v>27.46140112404218</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>-13.5</v>
+      </c>
+      <c r="R19" s="15">
+        <v>-9.3059431720137198</v>
+      </c>
+      <c r="S19" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T19" s="4">
+        <v>-32</v>
+      </c>
+      <c r="U19" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V19" s="4">
+        <v>0</v>
+      </c>
+      <c r="W19" s="4">
+        <v>42.5</v>
+      </c>
+      <c r="X19" s="9">
+        <v>45.616859076070639</v>
+      </c>
+      <c r="Y19" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z19" s="4">
+        <v>52</v>
+      </c>
+      <c r="AA19" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB19" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC19" s="5">
+        <v>-0.17908743023872381</v>
+      </c>
+      <c r="AD19" s="5">
+        <v>-0.50469183921813965</v>
+      </c>
+      <c r="AE19" s="5">
+        <v>0.27865218079608423</v>
+      </c>
+      <c r="AF19" s="5">
+        <v>0.50469183921813965</v>
+      </c>
+      <c r="AG19" s="5">
+        <v>0.17908743023872381</v>
+      </c>
+      <c r="AH19" s="5">
+        <v>-0.27865218079608423</v>
+      </c>
+    </row>
+    <row r="20" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B20" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C20" s="4">
+        <v>17</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="4">
+        <v>26</v>
+      </c>
+      <c r="G20" s="4">
+        <v>34</v>
+      </c>
+      <c r="H20" s="8">
+        <v>0.44607944474533329</v>
+      </c>
+      <c r="I20" s="4">
+        <v>124</v>
+      </c>
+      <c r="J20" s="8">
+        <v>0.55392055525466666</v>
+      </c>
+      <c r="K20" s="4">
+        <v>-124</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N20" s="4">
+        <v>1</v>
+      </c>
+      <c r="O20" s="15">
+        <v>22.906844836940341</v>
+      </c>
+      <c r="P20" s="15">
+        <v>21.82991600578422</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>-2.5</v>
+      </c>
+      <c r="R20" s="9">
+        <v>1.07692883115612</v>
+      </c>
+      <c r="S20" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T20" s="4">
+        <v>-8</v>
+      </c>
+      <c r="U20" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V20" s="4">
+        <v>0</v>
+      </c>
+      <c r="W20" s="4">
+        <v>39.5</v>
+      </c>
+      <c r="X20" s="9">
+        <v>44.736760842724557</v>
+      </c>
+      <c r="Y20" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z20" s="4">
+        <v>60</v>
+      </c>
+      <c r="AA20" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB20" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="5">
+        <v>-0.13270121651726799</v>
+      </c>
+      <c r="AD20" s="5">
+        <v>-0.1991390912037975</v>
+      </c>
+      <c r="AE20" s="5">
+        <v>0.2469404177232222</v>
+      </c>
+      <c r="AF20" s="5">
+        <v>0.1991390912037975</v>
+      </c>
+      <c r="AG20" s="5">
+        <v>0.13270121651726799</v>
+      </c>
+      <c r="AH20" s="5">
+        <v>-0.2469404177232222</v>
+      </c>
+    </row>
+    <row r="21" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B21" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C21" s="4">
+        <v>17</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="4">
+        <v>10</v>
+      </c>
+      <c r="G21" s="4">
+        <v>34</v>
+      </c>
+      <c r="H21" s="8">
+        <v>0.33366036237169933</v>
+      </c>
+      <c r="I21" s="4">
+        <v>199</v>
+      </c>
+      <c r="J21" s="8">
+        <v>0.66633963762830062</v>
+      </c>
+      <c r="K21" s="4">
+        <v>-199</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="N21" s="4">
+        <v>1</v>
+      </c>
+      <c r="O21" s="15">
+        <v>18.502818792130569</v>
+      </c>
+      <c r="P21" s="15">
+        <v>22.57260962654793</v>
+      </c>
+      <c r="Q21" s="4">
+        <v>-1.5</v>
+      </c>
+      <c r="R21" s="9">
+        <v>-4.0697908344173648</v>
+      </c>
+      <c r="S21" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T21" s="4">
+        <v>-24</v>
+      </c>
+      <c r="U21" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V21" s="4">
+        <v>1</v>
+      </c>
+      <c r="W21" s="4">
+        <v>41.5</v>
+      </c>
+      <c r="X21" s="9">
+        <v>41.075428418678499</v>
+      </c>
+      <c r="Y21" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z21" s="4">
+        <v>44</v>
+      </c>
+      <c r="AA21" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB21" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="5">
+        <v>-0.22700842495622309</v>
+      </c>
+      <c r="AD21" s="5">
+        <v>-0.2351310761248479</v>
+      </c>
+      <c r="AE21" s="5">
+        <v>-9.7053625366904525E-2</v>
+      </c>
+      <c r="AF21" s="5">
+        <v>0.2351310761248479</v>
+      </c>
+      <c r="AG21" s="5">
+        <v>0.22700842495622309</v>
+      </c>
+      <c r="AH21" s="5">
+        <v>9.7053625366904525E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B22" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C22" s="4">
+        <v>17</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="4">
+        <v>12</v>
+      </c>
+      <c r="G22" s="4">
+        <v>13</v>
+      </c>
+      <c r="H22" s="8">
+        <v>0.57234845190812011</v>
+      </c>
+      <c r="I22" s="4">
+        <v>-133</v>
+      </c>
+      <c r="J22" s="8">
+        <v>0.42765154809187989</v>
+      </c>
+      <c r="K22" s="4">
+        <v>133</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="N22" s="4">
+        <v>0</v>
+      </c>
+      <c r="O22" s="9">
+        <v>26.037626997972321</v>
+      </c>
+      <c r="P22" s="15">
+        <v>22.915419244049261</v>
+      </c>
+      <c r="Q22" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="R22" s="9">
+        <v>3.1222077539230599</v>
+      </c>
+      <c r="S22" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T22" s="4">
+        <v>-1</v>
+      </c>
+      <c r="U22" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V22" s="4">
+        <v>0</v>
+      </c>
+      <c r="W22" s="4">
+        <v>43.5</v>
+      </c>
+      <c r="X22" s="9">
+        <v>48.953046242021593</v>
+      </c>
+      <c r="Y22" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z22" s="4">
+        <v>25</v>
+      </c>
+      <c r="AA22" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB22" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="5">
+        <v>-5.0502319593687318E-2</v>
+      </c>
+      <c r="AD22" s="5">
+        <v>0.1195927835860342</v>
+      </c>
+      <c r="AE22" s="5">
+        <v>-0.25014792442321782</v>
+      </c>
+      <c r="AF22" s="5">
+        <v>-0.1195927835860342</v>
+      </c>
+      <c r="AG22" s="5">
+        <v>5.0502319593687318E-2</v>
+      </c>
+      <c r="AH22" s="5">
+        <v>0.25014792442321782</v>
+      </c>
+    </row>
+    <row r="23" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B23" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C23" s="4">
+        <v>17</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F23" s="4">
+        <v>42</v>
+      </c>
+      <c r="G23" s="4">
+        <v>38</v>
+      </c>
+      <c r="H23" s="8">
+        <v>0.63055471279437458</v>
+      </c>
+      <c r="I23" s="4">
+        <v>-170</v>
+      </c>
+      <c r="J23" s="8">
+        <v>0.36944528720562542</v>
+      </c>
+      <c r="K23" s="4">
+        <v>170</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="N23" s="4">
+        <v>1</v>
+      </c>
+      <c r="O23" s="9">
+        <v>28.48497409018092</v>
+      </c>
+      <c r="P23" s="15">
+        <v>24.427110672654521</v>
+      </c>
+      <c r="Q23" s="4">
+        <v>3</v>
+      </c>
+      <c r="R23" s="9">
+        <v>4.057863417526395</v>
+      </c>
+      <c r="S23" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T23" s="4">
+        <v>4</v>
+      </c>
+      <c r="U23" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V23" s="4">
+        <v>1</v>
+      </c>
+      <c r="W23" s="4">
+        <v>52.5</v>
+      </c>
+      <c r="X23" s="9">
+        <v>52.912084762835427</v>
+      </c>
+      <c r="Y23" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z23" s="4">
+        <v>80</v>
+      </c>
+      <c r="AA23" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB23" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC23" s="5">
+        <v>0.29294983545939129</v>
+      </c>
+      <c r="AD23" s="5">
+        <v>-0.32815566429725063</v>
+      </c>
+      <c r="AE23" s="5">
+        <v>1.3250324033921771E-2</v>
+      </c>
+      <c r="AF23" s="5">
+        <v>0.32815566429725063</v>
+      </c>
+      <c r="AG23" s="5">
+        <v>-0.29294983545939129</v>
+      </c>
+      <c r="AH23" s="5">
+        <v>-1.3250324033921771E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B24" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C24" s="4">
+        <v>17</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="4">
+        <v>27</v>
+      </c>
+      <c r="G24" s="4">
+        <v>24</v>
+      </c>
+      <c r="H24" s="8">
+        <v>0.29752007082527432</v>
+      </c>
+      <c r="I24" s="4">
+        <v>236</v>
+      </c>
+      <c r="J24" s="8">
+        <v>0.70247992917472568</v>
+      </c>
+      <c r="K24" s="4">
+        <v>-236</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="N24" s="4">
+        <v>0</v>
+      </c>
+      <c r="O24" s="9">
+        <v>21.72428470641804</v>
+      </c>
+      <c r="P24" s="15">
+        <v>30.27893969611544</v>
+      </c>
+      <c r="Q24" s="4">
+        <v>-7.5</v>
+      </c>
+      <c r="R24" s="9">
+        <v>-8.5546549896974042</v>
+      </c>
+      <c r="S24" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T24" s="4">
+        <v>3</v>
+      </c>
+      <c r="U24" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V24" s="4">
+        <v>0</v>
+      </c>
+      <c r="W24" s="4">
+        <v>49.5</v>
+      </c>
+      <c r="X24" s="9">
+        <v>52.003224402533483</v>
+      </c>
+      <c r="Y24" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z24" s="4">
+        <v>51</v>
+      </c>
+      <c r="AA24" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB24" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="5">
+        <v>0.11564381617420121</v>
+      </c>
+      <c r="AD24" s="5">
+        <v>0.1016359402583196</v>
+      </c>
+      <c r="AE24" s="5">
+        <v>-0.3074916090284075</v>
+      </c>
+      <c r="AF24" s="5">
+        <v>-0.1016359402583196</v>
+      </c>
+      <c r="AG24" s="5">
+        <v>-0.11564381617420121</v>
+      </c>
+      <c r="AH24" s="5">
+        <v>0.3074916090284075</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="AF7:AH7"/>
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="Q7:V7"/>
+    <mergeCell ref="W7:AB7"/>
+    <mergeCell ref="AC7:AE7"/>
+  </mergeCells>
+  <conditionalFormatting sqref="AC9:AC24">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD9:AD24">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE9:AE24">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF9:AF24">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG9:AG24">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH9:AH24">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="1" id="{BF968A68-888E-9148-93AA-5D9FC83E7C4C}">
+            <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>N9:N24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="2" id="{7C23B9B2-2E4F-ED48-B70E-216F409C9F77}">
+            <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>V9:V24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="3" id="{51E03EFA-40DF-D941-9E27-586DE1B94171}">
+            <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>AB9:AB24</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3197922-17FD-3446-ABDB-5FDED8A662DF}">
-  <dimension ref="B2:F45"/>
+  <dimension ref="B2:F46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.2">
@@ -24570,7 +28310,7 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B4" cm="1">
-        <f t="array" ref="B4:B14">_xlfn.UNIQUE(_xlfn._xlws.FILTER(Master!C9:C1000,NOT(ISBLANK(Master!C9:C1000))))</f>
+        <f t="array" ref="B4:B15">_xlfn.UNIQUE(_xlfn._xlws.FILTER(Master!C9:C1000,NOT(ISBLANK(Master!C9:C1000))))</f>
         <v>6</v>
       </c>
       <c r="C4">
@@ -24800,6 +28540,27 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B15">
+        <v>17</v>
+      </c>
+      <c r="C15">
+        <f>COUNTIFS(Master!C:C,'Weekly Record'!B15)</f>
+        <v>16</v>
+      </c>
+      <c r="D15">
+        <f>SUMIFS(Master!N:N, Master!C:C,'Weekly Record'!B15)</f>
+        <v>10</v>
+      </c>
+      <c r="E15">
+        <f t="shared" ref="E15" si="4">C15-D15</f>
+        <v>6</v>
+      </c>
+      <c r="F15" s="12">
+        <f t="shared" ref="F15" si="5">D15/C15</f>
+        <v>0.625</v>
+      </c>
+    </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B17" s="18" t="s">
         <v>146</v>
@@ -24824,7 +28585,7 @@
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B19" cm="1">
-        <f t="array" ref="B19:B29">_xlfn.UNIQUE(_xlfn._xlws.FILTER(Master!C9:C1000,NOT(ISBLANK(Master!C9:C1000))))</f>
+        <f t="array" ref="B19:B30">_xlfn.UNIQUE(_xlfn._xlws.FILTER(Master!C9:C1000,NOT(ISBLANK(Master!C9:C1000))))</f>
         <v>6</v>
       </c>
       <c r="C19">
@@ -24857,11 +28618,11 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <f t="shared" ref="E20:E28" si="4">C20-D20</f>
+        <f t="shared" ref="E20:E28" si="6">C20-D20</f>
         <v>15</v>
       </c>
       <c r="F20" s="12">
-        <f t="shared" ref="F20:F28" si="5">D20/C20</f>
+        <f t="shared" ref="F20:F28" si="7">D20/C20</f>
         <v>0</v>
       </c>
     </row>
@@ -24878,11 +28639,11 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>13</v>
       </c>
       <c r="F21" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -24899,11 +28660,11 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>14</v>
       </c>
       <c r="F22" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -24920,11 +28681,11 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>14</v>
       </c>
       <c r="F23" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -24941,11 +28702,11 @@
         <v>6</v>
       </c>
       <c r="E24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="F24" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.4</v>
       </c>
     </row>
@@ -24962,11 +28723,11 @@
         <v>8</v>
       </c>
       <c r="E25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="F25" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.5714285714285714</v>
       </c>
     </row>
@@ -24983,11 +28744,11 @@
         <v>10</v>
       </c>
       <c r="E26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="F26" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.625</v>
       </c>
     </row>
@@ -25004,11 +28765,11 @@
         <v>8</v>
       </c>
       <c r="E27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="F27" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.5714285714285714</v>
       </c>
     </row>
@@ -25025,11 +28786,11 @@
         <v>8</v>
       </c>
       <c r="E28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="F28" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
     </row>
@@ -25046,12 +28807,33 @@
         <v>6</v>
       </c>
       <c r="E29">
-        <f t="shared" ref="E29" si="6">C29-D29</f>
+        <f t="shared" ref="E29" si="8">C29-D29</f>
         <v>10</v>
       </c>
       <c r="F29" s="12">
-        <f t="shared" ref="F29" si="7">D29/C29</f>
+        <f t="shared" ref="F29" si="9">D29/C29</f>
         <v>0.375</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B30">
+        <v>17</v>
+      </c>
+      <c r="C30">
+        <f>COUNTIFS(Master!C:C,'Weekly Record'!B30)</f>
+        <v>16</v>
+      </c>
+      <c r="D30">
+        <f>SUMIFS(Master!V:V, Master!C:C,'Weekly Record'!B30)</f>
+        <v>10</v>
+      </c>
+      <c r="E30">
+        <f t="shared" ref="E30" si="10">C30-D30</f>
+        <v>6</v>
+      </c>
+      <c r="F30" s="12">
+        <f t="shared" ref="F30" si="11">D30/C30</f>
+        <v>0.625</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.2">
@@ -25078,7 +28860,7 @@
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" cm="1">
-        <f t="array" ref="B35:B45">_xlfn.UNIQUE(_xlfn._xlws.FILTER(Master!C9:C1000,NOT(ISBLANK(Master!C9:C1000))))</f>
+        <f t="array" ref="B35:B46">_xlfn.UNIQUE(_xlfn._xlws.FILTER(Master!C9:C1000,NOT(ISBLANK(Master!C9:C1000))))</f>
         <v>6</v>
       </c>
       <c r="C35">
@@ -25111,11 +28893,11 @@
         <v>0</v>
       </c>
       <c r="E36">
-        <f t="shared" ref="E36:E44" si="8">C36-D36</f>
+        <f t="shared" ref="E36:E44" si="12">C36-D36</f>
         <v>15</v>
       </c>
       <c r="F36" s="12">
-        <f t="shared" ref="F36:F44" si="9">D36/C36</f>
+        <f t="shared" ref="F36:F44" si="13">D36/C36</f>
         <v>0</v>
       </c>
     </row>
@@ -25132,11 +28914,11 @@
         <v>0</v>
       </c>
       <c r="E37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>13</v>
       </c>
       <c r="F37" s="12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -25153,11 +28935,11 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
       <c r="F38" s="12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -25174,11 +28956,11 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
       <c r="F39" s="12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -25195,11 +28977,11 @@
         <v>7</v>
       </c>
       <c r="E40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>8</v>
       </c>
       <c r="F40" s="12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0.46666666666666667</v>
       </c>
     </row>
@@ -25216,11 +28998,11 @@
         <v>7</v>
       </c>
       <c r="E41">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>7</v>
       </c>
       <c r="F41" s="12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0.5</v>
       </c>
     </row>
@@ -25237,11 +29019,11 @@
         <v>8</v>
       </c>
       <c r="E42">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>8</v>
       </c>
       <c r="F42" s="12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0.5</v>
       </c>
     </row>
@@ -25258,11 +29040,11 @@
         <v>4</v>
       </c>
       <c r="E43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="F43" s="12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0.2857142857142857</v>
       </c>
     </row>
@@ -25279,11 +29061,11 @@
         <v>6</v>
       </c>
       <c r="E44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="F44" s="12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0.375</v>
       </c>
     </row>
@@ -25300,12 +29082,33 @@
         <v>8</v>
       </c>
       <c r="E45">
-        <f t="shared" ref="E45" si="10">C45-D45</f>
+        <f t="shared" ref="E45" si="14">C45-D45</f>
         <v>8</v>
       </c>
       <c r="F45" s="12">
-        <f t="shared" ref="F45" si="11">D45/C45</f>
+        <f t="shared" ref="F45" si="15">D45/C45</f>
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B46">
+        <v>17</v>
+      </c>
+      <c r="C46">
+        <f>COUNTIFS(Master!C:C,'Weekly Record'!B46)</f>
+        <v>16</v>
+      </c>
+      <c r="D46">
+        <f>SUMIFS(Master!AB:AB, Master!C:C,'Weekly Record'!B46)</f>
+        <v>7</v>
+      </c>
+      <c r="E46">
+        <f t="shared" ref="E46" si="16">C46-D46</f>
+        <v>9</v>
+      </c>
+      <c r="F46" s="12">
+        <f t="shared" ref="F46" si="17">D46/C46</f>
+        <v>0.4375</v>
       </c>
     </row>
   </sheetData>

--- a/model results/2025 Results.xlsx
+++ b/model results/2025 Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jmiller/Documents/Fun/nfl/model results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D507C1B3-7F17-EC45-8EC8-643C03DA8679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2DB388-3AEA-9145-9CF5-53F6D6F5BA48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17360" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="2" r:id="rId1"/>
@@ -27,6 +27,7 @@
     <sheet name="Week 15" sheetId="12" r:id="rId12"/>
     <sheet name="Week 16" sheetId="14" r:id="rId13"/>
     <sheet name="Week 17" sheetId="15" r:id="rId14"/>
+    <sheet name="Week 18" sheetId="16" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -68,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3162" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3461" uniqueCount="225">
   <si>
     <t>season</t>
   </si>
@@ -896,6 +897,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -908,7 +910,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1212,7 +1213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E32420-1D15-E549-AAF4-FB71DE782F62}">
-  <dimension ref="B2:AH186"/>
+  <dimension ref="B2:AH202"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.1640625" customWidth="1"/>
@@ -1268,19 +1269,19 @@
       </c>
       <c r="C3" s="13">
         <f>COUNTA(N9:N1000)</f>
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="D3" s="13">
         <f>SUM(N9:N1000)</f>
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E3" s="13">
         <f>C3-D3</f>
-        <v>65</v>
-      </c>
-      <c r="F3" s="23">
+        <v>74</v>
+      </c>
+      <c r="F3" s="19">
         <f>D3/C3</f>
-        <v>0.6348314606741573</v>
+        <v>0.61855670103092786</v>
       </c>
       <c r="G3" s="6"/>
     </row>
@@ -1290,19 +1291,19 @@
       </c>
       <c r="C4" s="13">
         <f>COUNTA(V9:V1000)</f>
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D4" s="13">
         <f>SUM(V9:V1000)</f>
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="E4" s="13">
         <f>C4-D4</f>
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F4" s="14">
         <f>D4/C4</f>
-        <v>0.52336448598130836</v>
+        <v>0.52845528455284552</v>
       </c>
       <c r="G4" s="6"/>
     </row>
@@ -1312,19 +1313,19 @@
       </c>
       <c r="C5" s="13">
         <f>COUNTA(AB9:AB1000)</f>
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D5" s="13">
         <f>SUM(AB9:AB1000)</f>
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E5" s="13">
         <f>C5-D5</f>
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F5" s="14">
         <f>D5/C5</f>
-        <v>0.43925233644859812</v>
+        <v>0.45528455284552843</v>
       </c>
       <c r="G5" s="6"/>
     </row>
@@ -1333,45 +1334,45 @@
       <c r="C6" s="17"/>
     </row>
     <row r="7" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19" t="s">
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="19" t="s">
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19"/>
-      <c r="T7" s="19"/>
-      <c r="U7" s="19"/>
-      <c r="V7" s="19"/>
-      <c r="W7" s="19" t="s">
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="X7" s="19"/>
-      <c r="Y7" s="19"/>
-      <c r="Z7" s="19"/>
-      <c r="AA7" s="19"/>
-      <c r="AB7" s="19"/>
-      <c r="AC7" s="19" t="s">
+      <c r="X7" s="20"/>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="20"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="AD7" s="19"/>
-      <c r="AE7" s="19"/>
-      <c r="AF7" s="19" t="s">
+      <c r="AD7" s="20"/>
+      <c r="AE7" s="20"/>
+      <c r="AF7" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="AG7" s="19"/>
-      <c r="AH7" s="19"/>
+      <c r="AG7" s="20"/>
+      <c r="AH7" s="20"/>
     </row>
     <row r="8" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
@@ -17135,6 +17136,1622 @@
         <v>0.3074916090284075</v>
       </c>
     </row>
+    <row r="187" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B187" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C187" s="4">
+        <v>18</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E187" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F187" s="4">
+        <v>16</v>
+      </c>
+      <c r="G187" s="4">
+        <v>14</v>
+      </c>
+      <c r="H187" s="8">
+        <v>0.55034776813727193</v>
+      </c>
+      <c r="I187" s="4">
+        <v>-122</v>
+      </c>
+      <c r="J187" s="8">
+        <v>0.44965223186272812</v>
+      </c>
+      <c r="K187" s="4">
+        <v>122</v>
+      </c>
+      <c r="L187" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="M187" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="N187" s="4">
+        <v>1</v>
+      </c>
+      <c r="O187" s="15">
+        <v>24.274662090852111</v>
+      </c>
+      <c r="P187" s="15">
+        <v>22.010583615012141</v>
+      </c>
+      <c r="Q187" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="R187" s="15">
+        <v>2.2640784758399728</v>
+      </c>
+      <c r="S187" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T187" s="4">
+        <v>2</v>
+      </c>
+      <c r="U187" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V187" s="4">
+        <v>1</v>
+      </c>
+      <c r="W187" s="4">
+        <v>43.5</v>
+      </c>
+      <c r="X187" s="9">
+        <v>46.285245705864249</v>
+      </c>
+      <c r="Y187" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z187" s="4">
+        <v>30</v>
+      </c>
+      <c r="AA187" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB187" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC187" s="5">
+        <v>1.830032156474555E-2</v>
+      </c>
+      <c r="AD187" s="5">
+        <v>3.5524382883188682E-2</v>
+      </c>
+      <c r="AE187" s="5">
+        <v>-3.5771714015440513E-2</v>
+      </c>
+      <c r="AF187" s="5">
+        <v>-3.5524382883188682E-2</v>
+      </c>
+      <c r="AG187" s="5">
+        <v>-1.830032156474555E-2</v>
+      </c>
+      <c r="AH187" s="5">
+        <v>3.5771714015440513E-2</v>
+      </c>
+    </row>
+    <row r="188" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B188" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C188" s="4">
+        <v>18</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E188" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F188" s="4">
+        <v>3</v>
+      </c>
+      <c r="G188" s="4">
+        <v>13</v>
+      </c>
+      <c r="H188" s="8">
+        <v>0.57962029072357746</v>
+      </c>
+      <c r="I188" s="4">
+        <v>-137</v>
+      </c>
+      <c r="J188" s="8">
+        <v>0.42037970927642249</v>
+      </c>
+      <c r="K188" s="4">
+        <v>137</v>
+      </c>
+      <c r="L188" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M188" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N188" s="4">
+        <v>0</v>
+      </c>
+      <c r="O188" s="15">
+        <v>24.00409348427182</v>
+      </c>
+      <c r="P188" s="15">
+        <v>24.84763773704849</v>
+      </c>
+      <c r="Q188" s="4">
+        <v>-1.5</v>
+      </c>
+      <c r="R188" s="15">
+        <v>-0.84354425277667033</v>
+      </c>
+      <c r="S188" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T188" s="4">
+        <v>-10</v>
+      </c>
+      <c r="U188" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V188" s="4">
+        <v>0</v>
+      </c>
+      <c r="W188" s="4">
+        <v>47.5</v>
+      </c>
+      <c r="X188" s="9">
+        <v>48.851731221320307</v>
+      </c>
+      <c r="Y188" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z188" s="4">
+        <v>16</v>
+      </c>
+      <c r="AA188" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB188" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC188" s="5">
+        <v>-0.3589906919570196</v>
+      </c>
+      <c r="AD188" s="5">
+        <v>-0.10921088131991299</v>
+      </c>
+      <c r="AE188" s="5">
+        <v>0.30073720567366657</v>
+      </c>
+      <c r="AF188" s="5">
+        <v>0.10921088131991299</v>
+      </c>
+      <c r="AG188" s="5">
+        <v>0.3589906919570196</v>
+      </c>
+      <c r="AH188" s="5">
+        <v>-0.30073720567366657</v>
+      </c>
+    </row>
+    <row r="189" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B189" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C189" s="4">
+        <v>18</v>
+      </c>
+      <c r="D189" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E189" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F189" s="4">
+        <v>19</v>
+      </c>
+      <c r="G189" s="4">
+        <v>17</v>
+      </c>
+      <c r="H189" s="8">
+        <v>0.49416493182868498</v>
+      </c>
+      <c r="I189" s="4">
+        <v>102</v>
+      </c>
+      <c r="J189" s="8">
+        <v>0.50583506817131496</v>
+      </c>
+      <c r="K189" s="4">
+        <v>-102</v>
+      </c>
+      <c r="L189" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M189" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="N189" s="4">
+        <v>0</v>
+      </c>
+      <c r="O189" s="15">
+        <v>22.695152668872691</v>
+      </c>
+      <c r="P189" s="15">
+        <v>22.14771100071242</v>
+      </c>
+      <c r="Q189" s="4">
+        <v>3</v>
+      </c>
+      <c r="R189" s="9">
+        <v>0.54744166816027473</v>
+      </c>
+      <c r="S189" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T189" s="4">
+        <v>2</v>
+      </c>
+      <c r="U189" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V189" s="4">
+        <v>1</v>
+      </c>
+      <c r="W189" s="4">
+        <v>45.5</v>
+      </c>
+      <c r="X189" s="9">
+        <v>44.842863669585107</v>
+      </c>
+      <c r="Y189" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z189" s="4">
+        <v>36</v>
+      </c>
+      <c r="AA189" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB189" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC189" s="5">
+        <v>-0.24327203432718911</v>
+      </c>
+      <c r="AD189" s="5">
+        <v>0.1058234256856582</v>
+      </c>
+      <c r="AE189" s="5">
+        <v>0.43750580719539089</v>
+      </c>
+      <c r="AF189" s="5">
+        <v>-0.1058234256856582</v>
+      </c>
+      <c r="AG189" s="5">
+        <v>0.24327203432718911</v>
+      </c>
+      <c r="AH189" s="5">
+        <v>-0.43750580719539089</v>
+      </c>
+    </row>
+    <row r="190" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B190" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C190" s="4">
+        <v>18</v>
+      </c>
+      <c r="D190" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E190" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F190" s="4">
+        <v>18</v>
+      </c>
+      <c r="G190" s="4">
+        <v>20</v>
+      </c>
+      <c r="H190" s="8">
+        <v>0.66728647654381279</v>
+      </c>
+      <c r="I190" s="4">
+        <v>-200</v>
+      </c>
+      <c r="J190" s="8">
+        <v>0.33271352345618721</v>
+      </c>
+      <c r="K190" s="4">
+        <v>200</v>
+      </c>
+      <c r="L190" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M190" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="N190" s="4">
+        <v>0</v>
+      </c>
+      <c r="O190" s="15">
+        <v>27.358433832848188</v>
+      </c>
+      <c r="P190" s="15">
+        <v>21.240233418915061</v>
+      </c>
+      <c r="Q190" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="R190" s="9">
+        <v>6.1182004139331347</v>
+      </c>
+      <c r="S190" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T190" s="4">
+        <v>-2</v>
+      </c>
+      <c r="U190" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V190" s="4">
+        <v>1</v>
+      </c>
+      <c r="W190" s="4">
+        <v>44.5</v>
+      </c>
+      <c r="X190" s="9">
+        <v>48.598667251763253</v>
+      </c>
+      <c r="Y190" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z190" s="4">
+        <v>38</v>
+      </c>
+      <c r="AA190" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB190" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC190" s="5">
+        <v>-8.8743957120980793E-2</v>
+      </c>
+      <c r="AD190" s="5">
+        <v>0.12539845246535081</v>
+      </c>
+      <c r="AE190" s="5">
+        <v>-6.7371854782104487E-2</v>
+      </c>
+      <c r="AF190" s="5">
+        <v>-0.12539845246535081</v>
+      </c>
+      <c r="AG190" s="5">
+        <v>8.8743957120980793E-2</v>
+      </c>
+      <c r="AH190" s="5">
+        <v>6.7371854782104487E-2</v>
+      </c>
+    </row>
+    <row r="191" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B191" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C191" s="4">
+        <v>18</v>
+      </c>
+      <c r="D191" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E191" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F191" s="4">
+        <v>38</v>
+      </c>
+      <c r="G191" s="4">
+        <v>30</v>
+      </c>
+      <c r="H191" s="8">
+        <v>0.66446874419824187</v>
+      </c>
+      <c r="I191" s="4">
+        <v>-198</v>
+      </c>
+      <c r="J191" s="8">
+        <v>0.33553125580175808</v>
+      </c>
+      <c r="K191" s="4">
+        <v>198</v>
+      </c>
+      <c r="L191" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="M191" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="N191" s="4">
+        <v>1</v>
+      </c>
+      <c r="O191" s="15">
+        <v>25.675340032837699</v>
+      </c>
+      <c r="P191" s="15">
+        <v>17.458343133705689</v>
+      </c>
+      <c r="Q191" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="R191" s="9">
+        <v>8.2169968991320133</v>
+      </c>
+      <c r="S191" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T191" s="4">
+        <v>8</v>
+      </c>
+      <c r="U191" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V191" s="4">
+        <v>1</v>
+      </c>
+      <c r="W191" s="4">
+        <v>38.5</v>
+      </c>
+      <c r="X191" s="9">
+        <v>43.133683166543378</v>
+      </c>
+      <c r="Y191" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z191" s="4">
+        <v>68</v>
+      </c>
+      <c r="AA191" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB191" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC191" s="5">
+        <v>5.6797724161575091E-3</v>
+      </c>
+      <c r="AD191" s="5">
+        <v>3.2016913096110017E-2</v>
+      </c>
+      <c r="AE191" s="5">
+        <v>0.1492186504251817</v>
+      </c>
+      <c r="AF191" s="5">
+        <v>-3.2016913096110017E-2</v>
+      </c>
+      <c r="AG191" s="5">
+        <v>-5.6797724161575091E-3</v>
+      </c>
+      <c r="AH191" s="5">
+        <v>-0.1492186504251817</v>
+      </c>
+    </row>
+    <row r="192" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B192" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C192" s="4">
+        <v>18</v>
+      </c>
+      <c r="D192" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E192" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F192" s="4">
+        <v>41</v>
+      </c>
+      <c r="G192" s="4">
+        <v>7</v>
+      </c>
+      <c r="H192" s="8">
+        <v>0.79936369626048986</v>
+      </c>
+      <c r="I192" s="4">
+        <v>-398</v>
+      </c>
+      <c r="J192" s="8">
+        <v>0.20063630373951011</v>
+      </c>
+      <c r="K192" s="4">
+        <v>398</v>
+      </c>
+      <c r="L192" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M192" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N192" s="4">
+        <v>1</v>
+      </c>
+      <c r="O192" s="15">
+        <v>28.92424277199223</v>
+      </c>
+      <c r="P192" s="15">
+        <v>16.86055778435728</v>
+      </c>
+      <c r="Q192" s="4">
+        <v>12.5</v>
+      </c>
+      <c r="R192" s="15">
+        <v>12.063684987634939</v>
+      </c>
+      <c r="S192" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T192" s="4">
+        <v>34</v>
+      </c>
+      <c r="U192" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V192" s="4">
+        <v>0</v>
+      </c>
+      <c r="W192" s="4">
+        <v>47.5</v>
+      </c>
+      <c r="X192" s="9">
+        <v>45.784800556349509</v>
+      </c>
+      <c r="Y192" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z192" s="4">
+        <v>48</v>
+      </c>
+      <c r="AA192" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB192" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC192" s="5">
+        <v>0.25045689221086181</v>
+      </c>
+      <c r="AD192" s="5">
+        <v>0.36189835159866901</v>
+      </c>
+      <c r="AE192" s="5">
+        <v>0.15228544748746431</v>
+      </c>
+      <c r="AF192" s="5">
+        <v>-0.36189835159866901</v>
+      </c>
+      <c r="AG192" s="5">
+        <v>-0.25045689221086181</v>
+      </c>
+      <c r="AH192" s="5">
+        <v>-0.15228544748746431</v>
+      </c>
+    </row>
+    <row r="193" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B193" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C193" s="4">
+        <v>18</v>
+      </c>
+      <c r="D193" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E193" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F193" s="4">
+        <v>16</v>
+      </c>
+      <c r="G193" s="4">
+        <v>3</v>
+      </c>
+      <c r="H193" s="8">
+        <v>0.45750746688545318</v>
+      </c>
+      <c r="I193" s="4">
+        <v>118</v>
+      </c>
+      <c r="J193" s="8">
+        <v>0.54249253311454682</v>
+      </c>
+      <c r="K193" s="4">
+        <v>-118</v>
+      </c>
+      <c r="L193" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M193" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="N193" s="4">
+        <v>0</v>
+      </c>
+      <c r="O193" s="15">
+        <v>21.88287117602297</v>
+      </c>
+      <c r="P193" s="15">
+        <v>22.574200537906322</v>
+      </c>
+      <c r="Q193" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="R193" s="9">
+        <v>-0.69132936188335492</v>
+      </c>
+      <c r="S193" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T193" s="4">
+        <v>13</v>
+      </c>
+      <c r="U193" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V193" s="4">
+        <v>0</v>
+      </c>
+      <c r="W193" s="4">
+        <v>35.5</v>
+      </c>
+      <c r="X193" s="9">
+        <v>44.457071713929288</v>
+      </c>
+      <c r="Y193" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z193" s="4">
+        <v>19</v>
+      </c>
+      <c r="AA193" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB193" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC193" s="5">
+        <v>1.475566002859998E-2</v>
+      </c>
+      <c r="AD193" s="5">
+        <v>0.31598213195800778</v>
+      </c>
+      <c r="AE193" s="5">
+        <v>-8.1225872039794922E-2</v>
+      </c>
+      <c r="AF193" s="5">
+        <v>-0.31598213195800778</v>
+      </c>
+      <c r="AG193" s="5">
+        <v>-1.475566002859998E-2</v>
+      </c>
+      <c r="AH193" s="5">
+        <v>8.1225872039794922E-2</v>
+      </c>
+    </row>
+    <row r="194" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B194" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C194" s="4">
+        <v>18</v>
+      </c>
+      <c r="D194" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E194" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F194" s="4">
+        <v>34</v>
+      </c>
+      <c r="G194" s="4">
+        <v>17</v>
+      </c>
+      <c r="H194" s="8">
+        <v>0.46268494173873681</v>
+      </c>
+      <c r="I194" s="4">
+        <v>116</v>
+      </c>
+      <c r="J194" s="8">
+        <v>0.53731505826126313</v>
+      </c>
+      <c r="K194" s="4">
+        <v>-116</v>
+      </c>
+      <c r="L194" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M194" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="N194" s="4">
+        <v>0</v>
+      </c>
+      <c r="O194" s="15">
+        <v>22.235217812779322</v>
+      </c>
+      <c r="P194" s="15">
+        <v>24.724894899377698</v>
+      </c>
+      <c r="Q194" s="4">
+        <v>-3.5</v>
+      </c>
+      <c r="R194" s="15">
+        <v>-2.4896770865983799</v>
+      </c>
+      <c r="S194" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T194" s="4">
+        <v>17</v>
+      </c>
+      <c r="U194" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V194" s="4">
+        <v>1</v>
+      </c>
+      <c r="W194" s="4">
+        <v>51.5</v>
+      </c>
+      <c r="X194" s="9">
+        <v>46.960112712157027</v>
+      </c>
+      <c r="Y194" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z194" s="4">
+        <v>51</v>
+      </c>
+      <c r="AA194" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB194" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC194" s="5">
+        <v>0.1154069513887972</v>
+      </c>
+      <c r="AD194" s="5">
+        <v>8.9342214443065504E-2</v>
+      </c>
+      <c r="AE194" s="5">
+        <v>0.21678714950879421</v>
+      </c>
+      <c r="AF194" s="5">
+        <v>-8.9342214443065504E-2</v>
+      </c>
+      <c r="AG194" s="5">
+        <v>-0.1154069513887972</v>
+      </c>
+      <c r="AH194" s="5">
+        <v>-0.21678714950879421</v>
+      </c>
+    </row>
+    <row r="195" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B195" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C195" s="4">
+        <v>18</v>
+      </c>
+      <c r="D195" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E195" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F195" s="4">
+        <v>35</v>
+      </c>
+      <c r="G195" s="4">
+        <v>8</v>
+      </c>
+      <c r="H195" s="8">
+        <v>0.8305133460115266</v>
+      </c>
+      <c r="I195" s="4">
+        <v>-490</v>
+      </c>
+      <c r="J195" s="8">
+        <v>0.1694866539884734</v>
+      </c>
+      <c r="K195" s="4">
+        <v>490</v>
+      </c>
+      <c r="L195" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="M195" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="N195" s="4">
+        <v>1</v>
+      </c>
+      <c r="O195" s="15">
+        <v>28.396399630011821</v>
+      </c>
+      <c r="P195" s="15">
+        <v>15.88439993258806</v>
+      </c>
+      <c r="Q195" s="4">
+        <v>7</v>
+      </c>
+      <c r="R195" s="9">
+        <v>12.51199969742375</v>
+      </c>
+      <c r="S195" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T195" s="4">
+        <v>27</v>
+      </c>
+      <c r="U195" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V195" s="4">
+        <v>1</v>
+      </c>
+      <c r="W195" s="4">
+        <v>38.5</v>
+      </c>
+      <c r="X195" s="9">
+        <v>44.280799562599881</v>
+      </c>
+      <c r="Y195" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z195" s="4">
+        <v>43</v>
+      </c>
+      <c r="AA195" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB195" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC195" s="5">
+        <v>0.33919749052628229</v>
+      </c>
+      <c r="AD195" s="5">
+        <v>0.2842603766399881</v>
+      </c>
+      <c r="AE195" s="5">
+        <v>-0.2122704794532374</v>
+      </c>
+      <c r="AF195" s="5">
+        <v>-0.2842603766399881</v>
+      </c>
+      <c r="AG195" s="5">
+        <v>-0.33919749052628229</v>
+      </c>
+      <c r="AH195" s="5">
+        <v>0.2122704794532374</v>
+      </c>
+    </row>
+    <row r="196" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B196" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C196" s="4">
+        <v>18</v>
+      </c>
+      <c r="D196" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E196" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F196" s="4">
+        <v>16</v>
+      </c>
+      <c r="G196" s="4">
+        <v>19</v>
+      </c>
+      <c r="H196" s="8">
+        <v>0.60651137512081821</v>
+      </c>
+      <c r="I196" s="4">
+        <v>-154</v>
+      </c>
+      <c r="J196" s="8">
+        <v>0.39348862487918179</v>
+      </c>
+      <c r="K196" s="4">
+        <v>154</v>
+      </c>
+      <c r="L196" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="M196" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="N196" s="4">
+        <v>0</v>
+      </c>
+      <c r="O196" s="15">
+        <v>26.088516294902011</v>
+      </c>
+      <c r="P196" s="15">
+        <v>24.24751712056343</v>
+      </c>
+      <c r="Q196" s="4">
+        <v>3</v>
+      </c>
+      <c r="R196" s="9">
+        <v>1.840999174338577</v>
+      </c>
+      <c r="S196" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T196" s="4">
+        <v>-3</v>
+      </c>
+      <c r="U196" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V196" s="4">
+        <v>1</v>
+      </c>
+      <c r="W196" s="4">
+        <v>50.5</v>
+      </c>
+      <c r="X196" s="9">
+        <v>50.336033415465437</v>
+      </c>
+      <c r="Y196" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z196" s="4">
+        <v>35</v>
+      </c>
+      <c r="AA196" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB196" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC196" s="5">
+        <v>-4.3949065905696943E-3</v>
+      </c>
+      <c r="AD196" s="5">
+        <v>-0.1264523414716329</v>
+      </c>
+      <c r="AE196" s="5">
+        <v>0.13135414231907239</v>
+      </c>
+      <c r="AF196" s="5">
+        <v>0.1264523414716329</v>
+      </c>
+      <c r="AG196" s="5">
+        <v>4.3949065905696943E-3</v>
+      </c>
+      <c r="AH196" s="5">
+        <v>-0.13135414231907239</v>
+      </c>
+    </row>
+    <row r="197" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B197" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C197" s="4">
+        <v>18</v>
+      </c>
+      <c r="D197" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E197" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F197" s="4">
+        <v>19</v>
+      </c>
+      <c r="G197" s="4">
+        <v>3</v>
+      </c>
+      <c r="H197" s="8">
+        <v>0.53324335709005655</v>
+      </c>
+      <c r="I197" s="4">
+        <v>-114</v>
+      </c>
+      <c r="J197" s="8">
+        <v>0.46675664290994351</v>
+      </c>
+      <c r="K197" s="4">
+        <v>114</v>
+      </c>
+      <c r="L197" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M197" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N197" s="4">
+        <v>1</v>
+      </c>
+      <c r="O197" s="15">
+        <v>23.164765347823149</v>
+      </c>
+      <c r="P197" s="15">
+        <v>21.727382908323669</v>
+      </c>
+      <c r="Q197" s="4">
+        <v>12.5</v>
+      </c>
+      <c r="R197" s="15">
+        <v>1.4373824394994761</v>
+      </c>
+      <c r="S197" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T197" s="4">
+        <v>16</v>
+      </c>
+      <c r="U197" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V197" s="4">
+        <v>0</v>
+      </c>
+      <c r="W197" s="4">
+        <v>37.5</v>
+      </c>
+      <c r="X197" s="9">
+        <v>44.892148256146811</v>
+      </c>
+      <c r="Y197" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z197" s="4">
+        <v>22</v>
+      </c>
+      <c r="AA197" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB197" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC197" s="5">
+        <v>-0.1939274135388826</v>
+      </c>
+      <c r="AD197" s="5">
+        <v>0.42070012934067669</v>
+      </c>
+      <c r="AE197" s="5">
+        <v>-1.952468907391583E-2</v>
+      </c>
+      <c r="AF197" s="5">
+        <v>-0.42070012934067669</v>
+      </c>
+      <c r="AG197" s="5">
+        <v>0.1939274135388826</v>
+      </c>
+      <c r="AH197" s="5">
+        <v>1.952468907391583E-2</v>
+      </c>
+    </row>
+    <row r="198" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B198" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C198" s="4">
+        <v>18</v>
+      </c>
+      <c r="D198" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E198" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F198" s="4">
+        <v>37</v>
+      </c>
+      <c r="G198" s="4">
+        <v>20</v>
+      </c>
+      <c r="H198" s="8">
+        <v>0.81384823395549688</v>
+      </c>
+      <c r="I198" s="4">
+        <v>-437</v>
+      </c>
+      <c r="J198" s="8">
+        <v>0.18615176604450309</v>
+      </c>
+      <c r="K198" s="4">
+        <v>437</v>
+      </c>
+      <c r="L198" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M198" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="N198" s="4">
+        <v>1</v>
+      </c>
+      <c r="O198" s="15">
+        <v>30.905485139186009</v>
+      </c>
+      <c r="P198" s="15">
+        <v>18.61532459110186</v>
+      </c>
+      <c r="Q198" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="R198" s="9">
+        <v>12.290160548084151</v>
+      </c>
+      <c r="S198" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T198" s="4">
+        <v>17</v>
+      </c>
+      <c r="U198" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V198" s="4">
+        <v>1</v>
+      </c>
+      <c r="W198" s="4">
+        <v>46.5</v>
+      </c>
+      <c r="X198" s="9">
+        <v>49.520809730287873</v>
+      </c>
+      <c r="Y198" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z198" s="4">
+        <v>57</v>
+      </c>
+      <c r="AA198" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB198" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC198" s="5">
+        <v>0.2202407541409345</v>
+      </c>
+      <c r="AD198" s="5">
+        <v>2.6646969573838369E-2</v>
+      </c>
+      <c r="AE198" s="5">
+        <v>-1.7873119424890591E-2</v>
+      </c>
+      <c r="AF198" s="5">
+        <v>-2.6646969573838369E-2</v>
+      </c>
+      <c r="AG198" s="5">
+        <v>-0.2202407541409345</v>
+      </c>
+      <c r="AH198" s="5">
+        <v>1.7873119424890591E-2</v>
+      </c>
+    </row>
+    <row r="199" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B199" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C199" s="4">
+        <v>18</v>
+      </c>
+      <c r="D199" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E199" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F199" s="4">
+        <v>14</v>
+      </c>
+      <c r="G199" s="4">
+        <v>12</v>
+      </c>
+      <c r="H199" s="8">
+        <v>0.23667107572911189</v>
+      </c>
+      <c r="I199" s="4">
+        <v>322</v>
+      </c>
+      <c r="J199" s="8">
+        <v>0.76332892427088817</v>
+      </c>
+      <c r="K199" s="4">
+        <v>-322</v>
+      </c>
+      <c r="L199" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M199" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N199" s="4">
+        <v>0</v>
+      </c>
+      <c r="O199" s="15">
+        <v>13.489612544682471</v>
+      </c>
+      <c r="P199" s="15">
+        <v>25.643059377796028</v>
+      </c>
+      <c r="Q199" s="4">
+        <v>-5.5</v>
+      </c>
+      <c r="R199" s="9">
+        <v>-12.153446833113559</v>
+      </c>
+      <c r="S199" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T199" s="4">
+        <v>2</v>
+      </c>
+      <c r="U199" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V199" s="4">
+        <v>0</v>
+      </c>
+      <c r="W199" s="4">
+        <v>36.5</v>
+      </c>
+      <c r="X199" s="9">
+        <v>39.132671922478487</v>
+      </c>
+      <c r="Y199" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z199" s="4">
+        <v>26</v>
+      </c>
+      <c r="AA199" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB199" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC199" s="5">
+        <v>-0.45686231340680811</v>
+      </c>
+      <c r="AD199" s="5">
+        <v>0.47610270977020258</v>
+      </c>
+      <c r="AE199" s="5">
+        <v>-8.1185160144682855E-2</v>
+      </c>
+      <c r="AF199" s="5">
+        <v>-0.47610270977020258</v>
+      </c>
+      <c r="AG199" s="5">
+        <v>0.45686231340680811</v>
+      </c>
+      <c r="AH199" s="5">
+        <v>8.1185160144682855E-2</v>
+      </c>
+    </row>
+    <row r="200" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B200" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C200" s="4">
+        <v>18</v>
+      </c>
+      <c r="D200" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E200" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F200" s="4">
+        <v>38</v>
+      </c>
+      <c r="G200" s="4">
+        <v>10</v>
+      </c>
+      <c r="H200" s="8">
+        <v>0.74870152000406931</v>
+      </c>
+      <c r="I200" s="4">
+        <v>-297</v>
+      </c>
+      <c r="J200" s="8">
+        <v>0.25129847999593069</v>
+      </c>
+      <c r="K200" s="4">
+        <v>297</v>
+      </c>
+      <c r="L200" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M200" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N200" s="4">
+        <v>1</v>
+      </c>
+      <c r="O200" s="9">
+        <v>30.075581822722199</v>
+      </c>
+      <c r="P200" s="15">
+        <v>19.747653641316589</v>
+      </c>
+      <c r="Q200" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="R200" s="9">
+        <v>10.3279281814056</v>
+      </c>
+      <c r="S200" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T200" s="4">
+        <v>28</v>
+      </c>
+      <c r="U200" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V200" s="4">
+        <v>0</v>
+      </c>
+      <c r="W200" s="4">
+        <v>45.5</v>
+      </c>
+      <c r="X200" s="9">
+        <v>49.823235464038788</v>
+      </c>
+      <c r="Y200" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z200" s="4">
+        <v>48</v>
+      </c>
+      <c r="AA200" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB200" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC200" s="5">
+        <v>0.32397203278123288</v>
+      </c>
+      <c r="AD200" s="5">
+        <v>0.31436092512948172</v>
+      </c>
+      <c r="AE200" s="5">
+        <v>-7.6890102139225716E-2</v>
+      </c>
+      <c r="AF200" s="5">
+        <v>-0.31436092512948172</v>
+      </c>
+      <c r="AG200" s="5">
+        <v>-0.32397203278123288</v>
+      </c>
+      <c r="AH200" s="5">
+        <v>7.6890102139225716E-2</v>
+      </c>
+    </row>
+    <row r="201" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B201" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C201" s="4">
+        <v>18</v>
+      </c>
+      <c r="D201" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E201" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F201" s="4">
+        <v>17</v>
+      </c>
+      <c r="G201" s="4">
+        <v>24</v>
+      </c>
+      <c r="H201" s="8">
+        <v>0.70480469602802465</v>
+      </c>
+      <c r="I201" s="4">
+        <v>-238</v>
+      </c>
+      <c r="J201" s="8">
+        <v>0.29519530397197541</v>
+      </c>
+      <c r="K201" s="4">
+        <v>238</v>
+      </c>
+      <c r="L201" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M201" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="N201" s="4">
+        <v>0</v>
+      </c>
+      <c r="O201" s="9">
+        <v>26.189862456781221</v>
+      </c>
+      <c r="P201" s="15">
+        <v>19.81586437078397</v>
+      </c>
+      <c r="Q201" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="R201" s="9">
+        <v>6.3739980859972576</v>
+      </c>
+      <c r="S201" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T201" s="4">
+        <v>-7</v>
+      </c>
+      <c r="U201" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V201" s="4">
+        <v>0</v>
+      </c>
+      <c r="W201" s="4">
+        <v>38.5</v>
+      </c>
+      <c r="X201" s="9">
+        <v>46.005726827565191</v>
+      </c>
+      <c r="Y201" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z201" s="4">
+        <v>41</v>
+      </c>
+      <c r="AA201" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB201" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC201" s="5">
+        <v>-8.6598269641399384E-2</v>
+      </c>
+      <c r="AD201" s="5">
+        <v>-0.1271072643906323</v>
+      </c>
+      <c r="AE201" s="5">
+        <v>0.11109153790907431</v>
+      </c>
+      <c r="AF201" s="5">
+        <v>0.1271072643906323</v>
+      </c>
+      <c r="AG201" s="5">
+        <v>8.6598269641399384E-2</v>
+      </c>
+      <c r="AH201" s="5">
+        <v>-0.11109153790907431</v>
+      </c>
+    </row>
+    <row r="202" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B202" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C202" s="4">
+        <v>18</v>
+      </c>
+      <c r="D202" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E202" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F202" s="4">
+        <v>26</v>
+      </c>
+      <c r="G202" s="4">
+        <v>24</v>
+      </c>
+      <c r="H202" s="8">
+        <v>0.49279668363379742</v>
+      </c>
+      <c r="I202" s="4">
+        <v>102</v>
+      </c>
+      <c r="J202" s="8">
+        <v>0.50720331636620264</v>
+      </c>
+      <c r="K202" s="4">
+        <v>-102</v>
+      </c>
+      <c r="L202" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M202" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N202" s="4">
+        <v>0</v>
+      </c>
+      <c r="O202" s="9">
+        <v>23.145400712847241</v>
+      </c>
+      <c r="P202" s="15">
+        <v>22.175801719287058</v>
+      </c>
+      <c r="Q202" s="4">
+        <v>-3.5</v>
+      </c>
+      <c r="R202" s="9">
+        <v>0.96959899356018298</v>
+      </c>
+      <c r="S202" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T202" s="4">
+        <v>2</v>
+      </c>
+      <c r="U202" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V202" s="4">
+        <v>1</v>
+      </c>
+      <c r="W202" s="4">
+        <v>40.5</v>
+      </c>
+      <c r="X202" s="9">
+        <v>45.321202432134307</v>
+      </c>
+      <c r="Y202" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z202" s="4">
+        <v>50</v>
+      </c>
+      <c r="AA202" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB202" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC202" s="5">
+        <v>5.1401243209838868E-2</v>
+      </c>
+      <c r="AD202" s="5">
+        <v>-0.14020941734313969</v>
+      </c>
+      <c r="AE202" s="5">
+        <v>0.16552998338426861</v>
+      </c>
+      <c r="AF202" s="5">
+        <v>0.14020941734313969</v>
+      </c>
+      <c r="AG202" s="5">
+        <v>-5.1401243209838868E-2</v>
+      </c>
+      <c r="AH202" s="5">
+        <v>-0.16552998338426861</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="AF7:AH7"/>
@@ -17145,6 +18762,306 @@
     <mergeCell ref="AC7:AE7"/>
   </mergeCells>
   <conditionalFormatting sqref="AC9:AC23">
+    <cfRule type="colorScale" priority="107">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC24:AC38">
+    <cfRule type="colorScale" priority="100">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC39:AC51">
+    <cfRule type="colorScale" priority="88">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC52:AC65">
+    <cfRule type="colorScale" priority="81">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC66:AC79">
+    <cfRule type="colorScale" priority="74">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC80:AC94">
+    <cfRule type="colorScale" priority="71">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC95:AC108">
+    <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC109:AC124">
+    <cfRule type="colorScale" priority="49">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC125:AC138">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC139:AC154">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC155:AC170">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC171:AC186">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD9:AD23">
+    <cfRule type="colorScale" priority="106">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD24:AD38">
+    <cfRule type="colorScale" priority="99">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD39:AD51">
+    <cfRule type="colorScale" priority="89">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD52:AD65">
+    <cfRule type="colorScale" priority="82">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD66:AD79">
+    <cfRule type="colorScale" priority="75">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD80:AD94">
+    <cfRule type="colorScale" priority="70">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD95:AD108">
+    <cfRule type="colorScale" priority="59">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD109:AD124">
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD125:AD138">
+    <cfRule type="colorScale" priority="41">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD139:AD154">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD155:AD170">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD171:AD186">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE9:AE23">
+    <cfRule type="colorScale" priority="105">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE24:AE38">
     <cfRule type="colorScale" priority="98">
       <colorScale>
         <cfvo type="min"/>
@@ -17156,7 +19073,151 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC24:AC38">
+  <conditionalFormatting sqref="AE39:AE51">
+    <cfRule type="colorScale" priority="90">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE52:AE65">
+    <cfRule type="colorScale" priority="83">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE66:AE79">
+    <cfRule type="colorScale" priority="76">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE80:AE94">
+    <cfRule type="colorScale" priority="69">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE95:AE108">
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE109:AE124">
+    <cfRule type="colorScale" priority="51">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE125:AE138">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE139:AE154">
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE155:AE170">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE171:AE186">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF9:AF23">
+    <cfRule type="colorScale" priority="104">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF24:AF38">
+    <cfRule type="colorScale" priority="97">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF39:AF51">
     <cfRule type="colorScale" priority="91">
       <colorScale>
         <cfvo type="min"/>
@@ -17168,7 +19229,307 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC39:AC51">
+  <conditionalFormatting sqref="AF52:AF65">
+    <cfRule type="colorScale" priority="84">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF66:AF79">
+    <cfRule type="colorScale" priority="77">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF80:AF94">
+    <cfRule type="colorScale" priority="68">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF95:AF108">
+    <cfRule type="colorScale" priority="61">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF109:AF124">
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF125:AF138">
+    <cfRule type="colorScale" priority="43">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF139:AF154">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF155:AF170">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF171:AF186">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG9:AG23">
+    <cfRule type="colorScale" priority="103">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG24:AG38">
+    <cfRule type="colorScale" priority="96">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG39:AG51">
+    <cfRule type="colorScale" priority="92">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG52:AG65">
+    <cfRule type="colorScale" priority="85">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG66:AG79">
+    <cfRule type="colorScale" priority="78">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG80:AG94">
+    <cfRule type="colorScale" priority="67">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG95:AG108">
+    <cfRule type="colorScale" priority="62">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG109:AG124">
+    <cfRule type="colorScale" priority="53">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG125:AG138">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG139:AG154">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG155:AG170">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG171:AG186">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH9:AH23">
+    <cfRule type="colorScale" priority="102">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH24:AH38">
+    <cfRule type="colorScale" priority="95">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH39:AH51">
+    <cfRule type="colorScale" priority="93">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH52:AH65">
+    <cfRule type="colorScale" priority="86">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH66:AH79">
     <cfRule type="colorScale" priority="79">
       <colorScale>
         <cfvo type="min"/>
@@ -17180,8 +19541,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC52:AC65">
-    <cfRule type="colorScale" priority="72">
+  <conditionalFormatting sqref="AH80:AH94">
+    <cfRule type="colorScale" priority="66">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -17192,8 +19553,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC66:AC79">
-    <cfRule type="colorScale" priority="65">
+  <conditionalFormatting sqref="AH95:AH108">
+    <cfRule type="colorScale" priority="63">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -17204,8 +19565,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC80:AC94">
-    <cfRule type="colorScale" priority="62">
+  <conditionalFormatting sqref="AH109:AH124">
+    <cfRule type="colorScale" priority="54">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -17216,8 +19577,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC95:AC108">
-    <cfRule type="colorScale" priority="49">
+  <conditionalFormatting sqref="AH125:AH138">
+    <cfRule type="colorScale" priority="45">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -17228,8 +19589,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC109:AC124">
-    <cfRule type="colorScale" priority="40">
+  <conditionalFormatting sqref="AH139:AH154">
+    <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -17240,8 +19601,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC125:AC138">
-    <cfRule type="colorScale" priority="31">
+  <conditionalFormatting sqref="AH155:AH170">
+    <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -17252,8 +19613,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC139:AC154">
-    <cfRule type="colorScale" priority="22">
+  <conditionalFormatting sqref="AH171:AH186">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -17264,19 +19625,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC155:AC170">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC171:AC186">
+  <conditionalFormatting sqref="AC187:AC202">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -17288,139 +19637,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD9:AD23">
-    <cfRule type="colorScale" priority="97">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD24:AD38">
-    <cfRule type="colorScale" priority="90">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD39:AD51">
-    <cfRule type="colorScale" priority="80">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD52:AD65">
-    <cfRule type="colorScale" priority="73">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD66:AD79">
-    <cfRule type="colorScale" priority="66">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD80:AD94">
-    <cfRule type="colorScale" priority="61">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD95:AD108">
-    <cfRule type="colorScale" priority="50">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD109:AD124">
-    <cfRule type="colorScale" priority="41">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD125:AD138">
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD139:AD154">
-    <cfRule type="colorScale" priority="23">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD155:AD170">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD171:AD186">
+  <conditionalFormatting sqref="AD187:AD202">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -17432,139 +19649,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE9:AE23">
-    <cfRule type="colorScale" priority="96">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE24:AE38">
-    <cfRule type="colorScale" priority="89">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE39:AE51">
-    <cfRule type="colorScale" priority="81">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE52:AE65">
-    <cfRule type="colorScale" priority="74">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE66:AE79">
-    <cfRule type="colorScale" priority="67">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE80:AE94">
-    <cfRule type="colorScale" priority="60">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE95:AE108">
-    <cfRule type="colorScale" priority="51">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE109:AE124">
-    <cfRule type="colorScale" priority="42">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE125:AE138">
-    <cfRule type="colorScale" priority="33">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE139:AE154">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE155:AE170">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE171:AE186">
+  <conditionalFormatting sqref="AE187:AE202">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -17576,139 +19661,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF9:AF23">
-    <cfRule type="colorScale" priority="95">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF24:AF38">
-    <cfRule type="colorScale" priority="88">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF39:AF51">
-    <cfRule type="colorScale" priority="82">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF52:AF65">
-    <cfRule type="colorScale" priority="75">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF66:AF79">
-    <cfRule type="colorScale" priority="68">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF80:AF94">
-    <cfRule type="colorScale" priority="59">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF95:AF108">
-    <cfRule type="colorScale" priority="52">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF109:AF124">
-    <cfRule type="colorScale" priority="43">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF125:AF138">
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF139:AF154">
-    <cfRule type="colorScale" priority="25">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF155:AF170">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF171:AF186">
+  <conditionalFormatting sqref="AF187:AF202">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -17720,139 +19673,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG9:AG23">
-    <cfRule type="colorScale" priority="94">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG24:AG38">
-    <cfRule type="colorScale" priority="87">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG39:AG51">
-    <cfRule type="colorScale" priority="83">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG52:AG65">
-    <cfRule type="colorScale" priority="76">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG66:AG79">
-    <cfRule type="colorScale" priority="69">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG80:AG94">
-    <cfRule type="colorScale" priority="58">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG95:AG108">
-    <cfRule type="colorScale" priority="53">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG109:AG124">
-    <cfRule type="colorScale" priority="44">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG125:AG138">
-    <cfRule type="colorScale" priority="35">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG139:AG154">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG155:AG170">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG171:AG186">
+  <conditionalFormatting sqref="AG187:AG202">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -17864,139 +19685,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH9:AH23">
-    <cfRule type="colorScale" priority="93">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH24:AH38">
-    <cfRule type="colorScale" priority="86">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH39:AH51">
-    <cfRule type="colorScale" priority="84">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH52:AH65">
-    <cfRule type="colorScale" priority="77">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH66:AH79">
-    <cfRule type="colorScale" priority="70">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH80:AH94">
-    <cfRule type="colorScale" priority="57">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH95:AH108">
-    <cfRule type="colorScale" priority="54">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH109:AH124">
-    <cfRule type="colorScale" priority="45">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH125:AH138">
-    <cfRule type="colorScale" priority="36">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH139:AH154">
-    <cfRule type="colorScale" priority="27">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH155:AH170">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH171:AH186">
+  <conditionalFormatting sqref="AH187:AH202">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -18016,7 +19705,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="63" id="{EDEA8277-96E2-534B-9496-1DB5484BFD68}">
+          <x14:cfRule type="iconSet" priority="72" id="{EDEA8277-96E2-534B-9496-1DB5484BFD68}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18035,7 +19724,7 @@
           <xm:sqref>N80:N94</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="46" id="{DD4EF5CC-2E62-F245-AF58-2756E5752FDF}">
+          <x14:cfRule type="iconSet" priority="55" id="{DD4EF5CC-2E62-F245-AF58-2756E5752FDF}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18054,7 +19743,7 @@
           <xm:sqref>N95:N108</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="37" id="{37C61786-4A12-0746-A763-4990B69F05C7}">
+          <x14:cfRule type="iconSet" priority="46" id="{37C61786-4A12-0746-A763-4990B69F05C7}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18073,7 +19762,7 @@
           <xm:sqref>N109:N124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="28" id="{212E7F37-E966-AF4F-A0C3-E0E8E1340734}">
+          <x14:cfRule type="iconSet" priority="37" id="{212E7F37-E966-AF4F-A0C3-E0E8E1340734}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18092,7 +19781,7 @@
           <xm:sqref>N125:N138</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="19" id="{9742010F-AC5F-C647-A8CE-71E3275DF15E}">
+          <x14:cfRule type="iconSet" priority="28" id="{9742010F-AC5F-C647-A8CE-71E3275DF15E}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18111,7 +19800,7 @@
           <xm:sqref>N139:N154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="10" id="{53BBD899-D2C8-074A-936B-361D7C508C63}">
+          <x14:cfRule type="iconSet" priority="19" id="{53BBD899-D2C8-074A-936B-361D7C508C63}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18130,7 +19819,7 @@
           <xm:sqref>N155:N170</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="1" id="{A12D9CF1-1026-094B-90AD-EA1CA9A2D92B}">
+          <x14:cfRule type="iconSet" priority="10" id="{A12D9CF1-1026-094B-90AD-EA1CA9A2D92B}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18149,7 +19838,7 @@
           <xm:sqref>N171:N186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="85" id="{48C4D57C-361D-AB47-A2B7-3D4E42CE6188}">
+          <x14:cfRule type="iconSet" priority="94" id="{48C4D57C-361D-AB47-A2B7-3D4E42CE6188}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18168,7 +19857,7 @@
           <xm:sqref>N24:AA38</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="78" id="{C3D59626-8CA7-8645-8330-0E71AB30C540}">
+          <x14:cfRule type="iconSet" priority="87" id="{C3D59626-8CA7-8645-8330-0E71AB30C540}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18187,7 +19876,7 @@
           <xm:sqref>N39:AA51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="71" id="{6D153A18-6D77-9445-BF8D-3BA4EDDD3FBA}">
+          <x14:cfRule type="iconSet" priority="80" id="{6D153A18-6D77-9445-BF8D-3BA4EDDD3FBA}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18206,7 +19895,7 @@
           <xm:sqref>N52:AA65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="64" id="{C34C5491-7DF8-D04C-B3C0-3779DAAA33EE}">
+          <x14:cfRule type="iconSet" priority="73" id="{C34C5491-7DF8-D04C-B3C0-3779DAAA33EE}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18225,7 +19914,7 @@
           <xm:sqref>N66:AA79</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="92" id="{4DC6D28C-E799-D04F-BAD2-092B8419C03D}">
+          <x14:cfRule type="iconSet" priority="101" id="{4DC6D28C-E799-D04F-BAD2-092B8419C03D}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18244,7 +19933,7 @@
           <xm:sqref>N9:AB23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="56" id="{92AD66C2-D91E-D648-9AC6-2417C2445C43}">
+          <x14:cfRule type="iconSet" priority="65" id="{92AD66C2-D91E-D648-9AC6-2417C2445C43}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18263,7 +19952,7 @@
           <xm:sqref>V80:V94</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="47" id="{2D523F71-4BB4-9940-8B5D-C962CA9D6F15}">
+          <x14:cfRule type="iconSet" priority="56" id="{2D523F71-4BB4-9940-8B5D-C962CA9D6F15}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18282,7 +19971,7 @@
           <xm:sqref>V95:V108</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="38" id="{2094B9A9-658A-3D41-A969-4F7B5F1A7D42}">
+          <x14:cfRule type="iconSet" priority="47" id="{2094B9A9-658A-3D41-A969-4F7B5F1A7D42}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18301,7 +19990,7 @@
           <xm:sqref>V109:V124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="29" id="{7AD482D6-AFFD-C546-9642-22AC15E71775}">
+          <x14:cfRule type="iconSet" priority="38" id="{7AD482D6-AFFD-C546-9642-22AC15E71775}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18320,7 +20009,7 @@
           <xm:sqref>V125:V138</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="20" id="{3B475BB3-A842-F24C-8D71-84FCC9C136B4}">
+          <x14:cfRule type="iconSet" priority="29" id="{3B475BB3-A842-F24C-8D71-84FCC9C136B4}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18339,7 +20028,7 @@
           <xm:sqref>V139:V154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="11" id="{ADD77C7B-8E6B-7A48-8AAC-8A63FE24FF97}">
+          <x14:cfRule type="iconSet" priority="20" id="{ADD77C7B-8E6B-7A48-8AAC-8A63FE24FF97}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18358,7 +20047,7 @@
           <xm:sqref>V155:V170</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="2" id="{17F128E4-E069-B54E-9112-2E64042DD7FA}">
+          <x14:cfRule type="iconSet" priority="11" id="{17F128E4-E069-B54E-9112-2E64042DD7FA}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18377,7 +20066,7 @@
           <xm:sqref>V171:V186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="55" id="{409D8166-545E-3045-805D-7C96DC6956B1}">
+          <x14:cfRule type="iconSet" priority="64" id="{409D8166-545E-3045-805D-7C96DC6956B1}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18396,7 +20085,7 @@
           <xm:sqref>AB80:AB94</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="48" id="{578139A0-9556-A24C-89D1-3B66D89331FA}">
+          <x14:cfRule type="iconSet" priority="57" id="{578139A0-9556-A24C-89D1-3B66D89331FA}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18415,7 +20104,7 @@
           <xm:sqref>AB95:AB108</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="39" id="{869A3731-7EDB-9143-AD0D-591DEB781BAF}">
+          <x14:cfRule type="iconSet" priority="48" id="{869A3731-7EDB-9143-AD0D-591DEB781BAF}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18434,7 +20123,7 @@
           <xm:sqref>AB109:AB124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="30" id="{90EFE230-91F0-784C-B726-5BE6F84EE2FC}">
+          <x14:cfRule type="iconSet" priority="39" id="{90EFE230-91F0-784C-B726-5BE6F84EE2FC}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18453,7 +20142,7 @@
           <xm:sqref>AB125:AB138</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="21" id="{7941D79E-AD1D-3F44-8D4F-313B45BDFDD4}">
+          <x14:cfRule type="iconSet" priority="30" id="{7941D79E-AD1D-3F44-8D4F-313B45BDFDD4}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18472,7 +20161,7 @@
           <xm:sqref>AB139:AB154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="12" id="{DEBE5BDC-29DE-8246-9122-5A2B43CD922F}">
+          <x14:cfRule type="iconSet" priority="21" id="{DEBE5BDC-29DE-8246-9122-5A2B43CD922F}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18491,7 +20180,7 @@
           <xm:sqref>AB155:AB170</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="3" id="{6EF58D86-81A1-CC4C-B5CF-2174EDC27A28}">
+          <x14:cfRule type="iconSet" priority="12" id="{6EF58D86-81A1-CC4C-B5CF-2174EDC27A28}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -18508,6 +20197,63 @@
             </x14:iconSet>
           </x14:cfRule>
           <xm:sqref>AB171:AB186</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="1" id="{45E17C71-3C4A-9248-8E64-529100B00271}">
+            <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>N187:N202</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="2" id="{DAD5E8EA-F4DA-7E4E-9FFA-52F388734A27}">
+            <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>V187:V202</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="3" id="{18ED4D56-16D4-3E4D-8DB7-26B21E81C10A}">
+            <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>AB187:AB202</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -18603,45 +20349,45 @@
       <c r="C6" s="6"/>
     </row>
     <row r="7" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19" t="s">
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="19" t="s">
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19"/>
-      <c r="T7" s="19"/>
-      <c r="U7" s="19"/>
-      <c r="V7" s="19"/>
-      <c r="W7" s="19" t="s">
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="X7" s="19"/>
-      <c r="Y7" s="19"/>
-      <c r="Z7" s="19"/>
-      <c r="AA7" s="19"/>
-      <c r="AB7" s="19"/>
-      <c r="AC7" s="19" t="s">
+      <c r="X7" s="20"/>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="20"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="AD7" s="19"/>
-      <c r="AE7" s="19"/>
-      <c r="AF7" s="19" t="s">
+      <c r="AD7" s="20"/>
+      <c r="AE7" s="20"/>
+      <c r="AF7" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="AG7" s="19"/>
-      <c r="AH7" s="19"/>
+      <c r="AG7" s="20"/>
+      <c r="AH7" s="20"/>
     </row>
     <row r="8" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
@@ -20599,45 +22345,45 @@
       <c r="C6" s="6"/>
     </row>
     <row r="7" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19" t="s">
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="19" t="s">
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19"/>
-      <c r="T7" s="19"/>
-      <c r="U7" s="19"/>
-      <c r="V7" s="19"/>
-      <c r="W7" s="19" t="s">
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="X7" s="19"/>
-      <c r="Y7" s="19"/>
-      <c r="Z7" s="19"/>
-      <c r="AA7" s="19"/>
-      <c r="AB7" s="19"/>
-      <c r="AC7" s="19" t="s">
+      <c r="X7" s="20"/>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="20"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="AD7" s="19"/>
-      <c r="AE7" s="19"/>
-      <c r="AF7" s="19" t="s">
+      <c r="AD7" s="20"/>
+      <c r="AE7" s="20"/>
+      <c r="AF7" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="AG7" s="19"/>
-      <c r="AH7" s="19"/>
+      <c r="AG7" s="20"/>
+      <c r="AH7" s="20"/>
     </row>
     <row r="8" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
@@ -22390,45 +24136,45 @@
       <c r="C6" s="6"/>
     </row>
     <row r="7" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19" t="s">
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="19" t="s">
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19"/>
-      <c r="T7" s="19"/>
-      <c r="U7" s="19"/>
-      <c r="V7" s="19"/>
-      <c r="W7" s="19" t="s">
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="X7" s="19"/>
-      <c r="Y7" s="19"/>
-      <c r="Z7" s="19"/>
-      <c r="AA7" s="19"/>
-      <c r="AB7" s="19"/>
-      <c r="AC7" s="19" t="s">
+      <c r="X7" s="20"/>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="20"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="AD7" s="19"/>
-      <c r="AE7" s="19"/>
-      <c r="AF7" s="19" t="s">
+      <c r="AD7" s="20"/>
+      <c r="AE7" s="20"/>
+      <c r="AF7" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="AG7" s="19"/>
-      <c r="AH7" s="19"/>
+      <c r="AG7" s="20"/>
+      <c r="AH7" s="20"/>
     </row>
     <row r="8" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
@@ -24383,45 +26129,45 @@
       <c r="C6" s="6"/>
     </row>
     <row r="7" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19" t="s">
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="19" t="s">
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19"/>
-      <c r="T7" s="19"/>
-      <c r="U7" s="19"/>
-      <c r="V7" s="19"/>
-      <c r="W7" s="19" t="s">
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="X7" s="19"/>
-      <c r="Y7" s="19"/>
-      <c r="Z7" s="19"/>
-      <c r="AA7" s="19"/>
-      <c r="AB7" s="19"/>
-      <c r="AC7" s="19" t="s">
+      <c r="X7" s="20"/>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="20"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="AD7" s="19"/>
-      <c r="AE7" s="19"/>
-      <c r="AF7" s="19" t="s">
+      <c r="AD7" s="20"/>
+      <c r="AE7" s="20"/>
+      <c r="AF7" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="AG7" s="19"/>
-      <c r="AH7" s="19"/>
+      <c r="AG7" s="20"/>
+      <c r="AH7" s="20"/>
     </row>
     <row r="8" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
@@ -26376,45 +28122,45 @@
       <c r="C6" s="6"/>
     </row>
     <row r="7" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19" t="s">
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="19" t="s">
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19"/>
-      <c r="T7" s="19"/>
-      <c r="U7" s="19"/>
-      <c r="V7" s="19"/>
-      <c r="W7" s="19" t="s">
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="X7" s="19"/>
-      <c r="Y7" s="19"/>
-      <c r="Z7" s="19"/>
-      <c r="AA7" s="19"/>
-      <c r="AB7" s="19"/>
-      <c r="AC7" s="19" t="s">
+      <c r="X7" s="20"/>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="20"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="AD7" s="19"/>
-      <c r="AE7" s="19"/>
-      <c r="AF7" s="19" t="s">
+      <c r="AD7" s="20"/>
+      <c r="AE7" s="20"/>
+      <c r="AF7" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="AG7" s="19"/>
-      <c r="AH7" s="19"/>
+      <c r="AG7" s="20"/>
+      <c r="AH7" s="20"/>
     </row>
     <row r="8" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
@@ -28281,9 +30027,2002 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36B7D98C-4C23-1D41-8F54-3AE5DDA59A0D}">
+  <dimension ref="B2:AH24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="3" width="9.5" customWidth="1"/>
+    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.1640625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="4.83203125" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="6.6640625" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="14" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="11.6640625" customWidth="1"/>
+    <col min="17" max="17" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="10.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B2" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="13">
+        <f>COUNTA($C$9:$C$24)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B3" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="13">
+        <f>SUM(N9:$N$24)</f>
+        <v>7</v>
+      </c>
+      <c r="D3" s="14">
+        <f>C3/$C$2</f>
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="4" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B4" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="13">
+        <f>SUM(V9:$V$24)</f>
+        <v>9</v>
+      </c>
+      <c r="D4" s="14">
+        <f t="shared" ref="D4:D5" si="0">C4/$C$2</f>
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="5" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B5" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5" s="13">
+        <f>SUM(AB9:$AB$24)</f>
+        <v>9</v>
+      </c>
+      <c r="D5" s="14">
+        <f t="shared" si="0"/>
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="6" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="C6" s="6"/>
+    </row>
+    <row r="7" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="H7" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="X7" s="20"/>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="20"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD7" s="20"/>
+      <c r="AE7" s="20"/>
+      <c r="AF7" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG7" s="20"/>
+      <c r="AH7" s="20"/>
+    </row>
+    <row r="8" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="Z8" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AA8" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AB8" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AC8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AE8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AH8" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B9" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C9" s="4">
+        <v>18</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="4">
+        <v>16</v>
+      </c>
+      <c r="G9" s="4">
+        <v>14</v>
+      </c>
+      <c r="H9" s="8">
+        <v>0.55034776813727193</v>
+      </c>
+      <c r="I9" s="4">
+        <v>-122</v>
+      </c>
+      <c r="J9" s="8">
+        <v>0.44965223186272812</v>
+      </c>
+      <c r="K9" s="4">
+        <v>122</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="N9" s="4">
+        <v>1</v>
+      </c>
+      <c r="O9" s="15">
+        <v>24.274662090852111</v>
+      </c>
+      <c r="P9" s="15">
+        <v>22.010583615012141</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="R9" s="15">
+        <v>2.2640784758399728</v>
+      </c>
+      <c r="S9" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T9" s="4">
+        <v>2</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V9" s="4">
+        <v>1</v>
+      </c>
+      <c r="W9" s="4">
+        <v>43.5</v>
+      </c>
+      <c r="X9" s="9">
+        <v>46.285245705864249</v>
+      </c>
+      <c r="Y9" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z9" s="4">
+        <v>30</v>
+      </c>
+      <c r="AA9" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="5">
+        <v>1.830032156474555E-2</v>
+      </c>
+      <c r="AD9" s="5">
+        <v>3.5524382883188682E-2</v>
+      </c>
+      <c r="AE9" s="5">
+        <v>-3.5771714015440513E-2</v>
+      </c>
+      <c r="AF9" s="5">
+        <v>-3.5524382883188682E-2</v>
+      </c>
+      <c r="AG9" s="5">
+        <v>-1.830032156474555E-2</v>
+      </c>
+      <c r="AH9" s="5">
+        <v>3.5771714015440513E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B10" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C10" s="4">
+        <v>18</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="4">
+        <v>3</v>
+      </c>
+      <c r="G10" s="4">
+        <v>13</v>
+      </c>
+      <c r="H10" s="8">
+        <v>0.57962029072357746</v>
+      </c>
+      <c r="I10" s="4">
+        <v>-137</v>
+      </c>
+      <c r="J10" s="8">
+        <v>0.42037970927642249</v>
+      </c>
+      <c r="K10" s="4">
+        <v>137</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N10" s="4">
+        <v>0</v>
+      </c>
+      <c r="O10" s="15">
+        <v>24.00409348427182</v>
+      </c>
+      <c r="P10" s="15">
+        <v>24.84763773704849</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>-1.5</v>
+      </c>
+      <c r="R10" s="15">
+        <v>-0.84354425277667033</v>
+      </c>
+      <c r="S10" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T10" s="4">
+        <v>-10</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V10" s="4">
+        <v>0</v>
+      </c>
+      <c r="W10" s="4">
+        <v>47.5</v>
+      </c>
+      <c r="X10" s="9">
+        <v>48.851731221320307</v>
+      </c>
+      <c r="Y10" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z10" s="4">
+        <v>16</v>
+      </c>
+      <c r="AA10" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="5">
+        <v>-0.3589906919570196</v>
+      </c>
+      <c r="AD10" s="5">
+        <v>-0.10921088131991299</v>
+      </c>
+      <c r="AE10" s="5">
+        <v>0.30073720567366657</v>
+      </c>
+      <c r="AF10" s="5">
+        <v>0.10921088131991299</v>
+      </c>
+      <c r="AG10" s="5">
+        <v>0.3589906919570196</v>
+      </c>
+      <c r="AH10" s="5">
+        <v>-0.30073720567366657</v>
+      </c>
+    </row>
+    <row r="11" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B11" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C11" s="4">
+        <v>18</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="4">
+        <v>19</v>
+      </c>
+      <c r="G11" s="4">
+        <v>17</v>
+      </c>
+      <c r="H11" s="8">
+        <v>0.49416493182868498</v>
+      </c>
+      <c r="I11" s="4">
+        <v>102</v>
+      </c>
+      <c r="J11" s="8">
+        <v>0.50583506817131496</v>
+      </c>
+      <c r="K11" s="4">
+        <v>-102</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="N11" s="4">
+        <v>0</v>
+      </c>
+      <c r="O11" s="15">
+        <v>22.695152668872691</v>
+      </c>
+      <c r="P11" s="15">
+        <v>22.14771100071242</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>3</v>
+      </c>
+      <c r="R11" s="9">
+        <v>0.54744166816027473</v>
+      </c>
+      <c r="S11" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T11" s="4">
+        <v>2</v>
+      </c>
+      <c r="U11" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V11" s="4">
+        <v>1</v>
+      </c>
+      <c r="W11" s="4">
+        <v>45.5</v>
+      </c>
+      <c r="X11" s="9">
+        <v>44.842863669585107</v>
+      </c>
+      <c r="Y11" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z11" s="4">
+        <v>36</v>
+      </c>
+      <c r="AA11" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB11" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="5">
+        <v>-0.24327203432718911</v>
+      </c>
+      <c r="AD11" s="5">
+        <v>0.1058234256856582</v>
+      </c>
+      <c r="AE11" s="5">
+        <v>0.43750580719539089</v>
+      </c>
+      <c r="AF11" s="5">
+        <v>-0.1058234256856582</v>
+      </c>
+      <c r="AG11" s="5">
+        <v>0.24327203432718911</v>
+      </c>
+      <c r="AH11" s="5">
+        <v>-0.43750580719539089</v>
+      </c>
+    </row>
+    <row r="12" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B12" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C12" s="4">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="4">
+        <v>18</v>
+      </c>
+      <c r="G12" s="4">
+        <v>20</v>
+      </c>
+      <c r="H12" s="8">
+        <v>0.66728647654381279</v>
+      </c>
+      <c r="I12" s="4">
+        <v>-200</v>
+      </c>
+      <c r="J12" s="8">
+        <v>0.33271352345618721</v>
+      </c>
+      <c r="K12" s="4">
+        <v>200</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="N12" s="4">
+        <v>0</v>
+      </c>
+      <c r="O12" s="15">
+        <v>27.358433832848188</v>
+      </c>
+      <c r="P12" s="15">
+        <v>21.240233418915061</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="R12" s="9">
+        <v>6.1182004139331347</v>
+      </c>
+      <c r="S12" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T12" s="4">
+        <v>-2</v>
+      </c>
+      <c r="U12" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V12" s="4">
+        <v>1</v>
+      </c>
+      <c r="W12" s="4">
+        <v>44.5</v>
+      </c>
+      <c r="X12" s="9">
+        <v>48.598667251763253</v>
+      </c>
+      <c r="Y12" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z12" s="4">
+        <v>38</v>
+      </c>
+      <c r="AA12" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB12" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="5">
+        <v>-8.8743957120980793E-2</v>
+      </c>
+      <c r="AD12" s="5">
+        <v>0.12539845246535081</v>
+      </c>
+      <c r="AE12" s="5">
+        <v>-6.7371854782104487E-2</v>
+      </c>
+      <c r="AF12" s="5">
+        <v>-0.12539845246535081</v>
+      </c>
+      <c r="AG12" s="5">
+        <v>8.8743957120980793E-2</v>
+      </c>
+      <c r="AH12" s="5">
+        <v>6.7371854782104487E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B13" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C13" s="4">
+        <v>18</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="4">
+        <v>38</v>
+      </c>
+      <c r="G13" s="4">
+        <v>30</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0.66446874419824187</v>
+      </c>
+      <c r="I13" s="4">
+        <v>-198</v>
+      </c>
+      <c r="J13" s="8">
+        <v>0.33553125580175808</v>
+      </c>
+      <c r="K13" s="4">
+        <v>198</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="N13" s="4">
+        <v>1</v>
+      </c>
+      <c r="O13" s="15">
+        <v>25.675340032837699</v>
+      </c>
+      <c r="P13" s="15">
+        <v>17.458343133705689</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="R13" s="9">
+        <v>8.2169968991320133</v>
+      </c>
+      <c r="S13" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T13" s="4">
+        <v>8</v>
+      </c>
+      <c r="U13" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V13" s="4">
+        <v>1</v>
+      </c>
+      <c r="W13" s="4">
+        <v>38.5</v>
+      </c>
+      <c r="X13" s="9">
+        <v>43.133683166543378</v>
+      </c>
+      <c r="Y13" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z13" s="4">
+        <v>68</v>
+      </c>
+      <c r="AA13" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB13" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="5">
+        <v>5.6797724161575091E-3</v>
+      </c>
+      <c r="AD13" s="5">
+        <v>3.2016913096110017E-2</v>
+      </c>
+      <c r="AE13" s="5">
+        <v>0.1492186504251817</v>
+      </c>
+      <c r="AF13" s="5">
+        <v>-3.2016913096110017E-2</v>
+      </c>
+      <c r="AG13" s="5">
+        <v>-5.6797724161575091E-3</v>
+      </c>
+      <c r="AH13" s="5">
+        <v>-0.1492186504251817</v>
+      </c>
+    </row>
+    <row r="14" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B14" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C14" s="4">
+        <v>18</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="4">
+        <v>41</v>
+      </c>
+      <c r="G14" s="4">
+        <v>7</v>
+      </c>
+      <c r="H14" s="8">
+        <v>0.79936369626048986</v>
+      </c>
+      <c r="I14" s="4">
+        <v>-398</v>
+      </c>
+      <c r="J14" s="8">
+        <v>0.20063630373951011</v>
+      </c>
+      <c r="K14" s="4">
+        <v>398</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N14" s="4">
+        <v>1</v>
+      </c>
+      <c r="O14" s="15">
+        <v>28.92424277199223</v>
+      </c>
+      <c r="P14" s="15">
+        <v>16.86055778435728</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>12.5</v>
+      </c>
+      <c r="R14" s="15">
+        <v>12.063684987634939</v>
+      </c>
+      <c r="S14" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T14" s="4">
+        <v>34</v>
+      </c>
+      <c r="U14" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V14" s="4">
+        <v>0</v>
+      </c>
+      <c r="W14" s="4">
+        <v>47.5</v>
+      </c>
+      <c r="X14" s="9">
+        <v>45.784800556349509</v>
+      </c>
+      <c r="Y14" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z14" s="4">
+        <v>48</v>
+      </c>
+      <c r="AA14" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB14" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="5">
+        <v>0.25045689221086181</v>
+      </c>
+      <c r="AD14" s="5">
+        <v>0.36189835159866901</v>
+      </c>
+      <c r="AE14" s="5">
+        <v>0.15228544748746431</v>
+      </c>
+      <c r="AF14" s="5">
+        <v>-0.36189835159866901</v>
+      </c>
+      <c r="AG14" s="5">
+        <v>-0.25045689221086181</v>
+      </c>
+      <c r="AH14" s="5">
+        <v>-0.15228544748746431</v>
+      </c>
+    </row>
+    <row r="15" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B15" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C15" s="4">
+        <v>18</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="4">
+        <v>16</v>
+      </c>
+      <c r="G15" s="4">
+        <v>3</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0.45750746688545318</v>
+      </c>
+      <c r="I15" s="4">
+        <v>118</v>
+      </c>
+      <c r="J15" s="8">
+        <v>0.54249253311454682</v>
+      </c>
+      <c r="K15" s="4">
+        <v>-118</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="N15" s="4">
+        <v>0</v>
+      </c>
+      <c r="O15" s="15">
+        <v>21.88287117602297</v>
+      </c>
+      <c r="P15" s="15">
+        <v>22.574200537906322</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="R15" s="9">
+        <v>-0.69132936188335492</v>
+      </c>
+      <c r="S15" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T15" s="4">
+        <v>13</v>
+      </c>
+      <c r="U15" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V15" s="4">
+        <v>0</v>
+      </c>
+      <c r="W15" s="4">
+        <v>35.5</v>
+      </c>
+      <c r="X15" s="9">
+        <v>44.457071713929288</v>
+      </c>
+      <c r="Y15" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z15" s="4">
+        <v>19</v>
+      </c>
+      <c r="AA15" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="5">
+        <v>1.475566002859998E-2</v>
+      </c>
+      <c r="AD15" s="5">
+        <v>0.31598213195800778</v>
+      </c>
+      <c r="AE15" s="5">
+        <v>-8.1225872039794922E-2</v>
+      </c>
+      <c r="AF15" s="5">
+        <v>-0.31598213195800778</v>
+      </c>
+      <c r="AG15" s="5">
+        <v>-1.475566002859998E-2</v>
+      </c>
+      <c r="AH15" s="5">
+        <v>8.1225872039794922E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B16" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C16" s="4">
+        <v>18</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="4">
+        <v>34</v>
+      </c>
+      <c r="G16" s="4">
+        <v>17</v>
+      </c>
+      <c r="H16" s="8">
+        <v>0.46268494173873681</v>
+      </c>
+      <c r="I16" s="4">
+        <v>116</v>
+      </c>
+      <c r="J16" s="8">
+        <v>0.53731505826126313</v>
+      </c>
+      <c r="K16" s="4">
+        <v>-116</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="N16" s="4">
+        <v>0</v>
+      </c>
+      <c r="O16" s="15">
+        <v>22.235217812779322</v>
+      </c>
+      <c r="P16" s="15">
+        <v>24.724894899377698</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>-3.5</v>
+      </c>
+      <c r="R16" s="15">
+        <v>-2.4896770865983799</v>
+      </c>
+      <c r="S16" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T16" s="4">
+        <v>17</v>
+      </c>
+      <c r="U16" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V16" s="4">
+        <v>1</v>
+      </c>
+      <c r="W16" s="4">
+        <v>51.5</v>
+      </c>
+      <c r="X16" s="9">
+        <v>46.960112712157027</v>
+      </c>
+      <c r="Y16" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z16" s="4">
+        <v>51</v>
+      </c>
+      <c r="AA16" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB16" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC16" s="5">
+        <v>0.1154069513887972</v>
+      </c>
+      <c r="AD16" s="5">
+        <v>8.9342214443065504E-2</v>
+      </c>
+      <c r="AE16" s="5">
+        <v>0.21678714950879421</v>
+      </c>
+      <c r="AF16" s="5">
+        <v>-8.9342214443065504E-2</v>
+      </c>
+      <c r="AG16" s="5">
+        <v>-0.1154069513887972</v>
+      </c>
+      <c r="AH16" s="5">
+        <v>-0.21678714950879421</v>
+      </c>
+    </row>
+    <row r="17" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B17" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C17" s="4">
+        <v>18</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="4">
+        <v>35</v>
+      </c>
+      <c r="G17" s="4">
+        <v>8</v>
+      </c>
+      <c r="H17" s="8">
+        <v>0.8305133460115266</v>
+      </c>
+      <c r="I17" s="4">
+        <v>-490</v>
+      </c>
+      <c r="J17" s="8">
+        <v>0.1694866539884734</v>
+      </c>
+      <c r="K17" s="4">
+        <v>490</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="N17" s="4">
+        <v>1</v>
+      </c>
+      <c r="O17" s="15">
+        <v>28.396399630011821</v>
+      </c>
+      <c r="P17" s="15">
+        <v>15.88439993258806</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>7</v>
+      </c>
+      <c r="R17" s="9">
+        <v>12.51199969742375</v>
+      </c>
+      <c r="S17" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T17" s="4">
+        <v>27</v>
+      </c>
+      <c r="U17" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V17" s="4">
+        <v>1</v>
+      </c>
+      <c r="W17" s="4">
+        <v>38.5</v>
+      </c>
+      <c r="X17" s="9">
+        <v>44.280799562599881</v>
+      </c>
+      <c r="Y17" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z17" s="4">
+        <v>43</v>
+      </c>
+      <c r="AA17" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB17" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="5">
+        <v>0.33919749052628229</v>
+      </c>
+      <c r="AD17" s="5">
+        <v>0.2842603766399881</v>
+      </c>
+      <c r="AE17" s="5">
+        <v>-0.2122704794532374</v>
+      </c>
+      <c r="AF17" s="5">
+        <v>-0.2842603766399881</v>
+      </c>
+      <c r="AG17" s="5">
+        <v>-0.33919749052628229</v>
+      </c>
+      <c r="AH17" s="5">
+        <v>0.2122704794532374</v>
+      </c>
+    </row>
+    <row r="18" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B18" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C18" s="4">
+        <v>18</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" s="4">
+        <v>16</v>
+      </c>
+      <c r="G18" s="4">
+        <v>19</v>
+      </c>
+      <c r="H18" s="8">
+        <v>0.60651137512081821</v>
+      </c>
+      <c r="I18" s="4">
+        <v>-154</v>
+      </c>
+      <c r="J18" s="8">
+        <v>0.39348862487918179</v>
+      </c>
+      <c r="K18" s="4">
+        <v>154</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="N18" s="4">
+        <v>0</v>
+      </c>
+      <c r="O18" s="15">
+        <v>26.088516294902011</v>
+      </c>
+      <c r="P18" s="15">
+        <v>24.24751712056343</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>3</v>
+      </c>
+      <c r="R18" s="9">
+        <v>1.840999174338577</v>
+      </c>
+      <c r="S18" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T18" s="4">
+        <v>-3</v>
+      </c>
+      <c r="U18" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V18" s="4">
+        <v>1</v>
+      </c>
+      <c r="W18" s="4">
+        <v>50.5</v>
+      </c>
+      <c r="X18" s="9">
+        <v>50.336033415465437</v>
+      </c>
+      <c r="Y18" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z18" s="4">
+        <v>35</v>
+      </c>
+      <c r="AA18" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB18" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="5">
+        <v>-4.3949065905696943E-3</v>
+      </c>
+      <c r="AD18" s="5">
+        <v>-0.1264523414716329</v>
+      </c>
+      <c r="AE18" s="5">
+        <v>0.13135414231907239</v>
+      </c>
+      <c r="AF18" s="5">
+        <v>0.1264523414716329</v>
+      </c>
+      <c r="AG18" s="5">
+        <v>4.3949065905696943E-3</v>
+      </c>
+      <c r="AH18" s="5">
+        <v>-0.13135414231907239</v>
+      </c>
+    </row>
+    <row r="19" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B19" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C19" s="4">
+        <v>18</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="4">
+        <v>19</v>
+      </c>
+      <c r="G19" s="4">
+        <v>3</v>
+      </c>
+      <c r="H19" s="8">
+        <v>0.53324335709005655</v>
+      </c>
+      <c r="I19" s="4">
+        <v>-114</v>
+      </c>
+      <c r="J19" s="8">
+        <v>0.46675664290994351</v>
+      </c>
+      <c r="K19" s="4">
+        <v>114</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N19" s="4">
+        <v>1</v>
+      </c>
+      <c r="O19" s="15">
+        <v>23.164765347823149</v>
+      </c>
+      <c r="P19" s="15">
+        <v>21.727382908323669</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>12.5</v>
+      </c>
+      <c r="R19" s="15">
+        <v>1.4373824394994761</v>
+      </c>
+      <c r="S19" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T19" s="4">
+        <v>16</v>
+      </c>
+      <c r="U19" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V19" s="4">
+        <v>0</v>
+      </c>
+      <c r="W19" s="4">
+        <v>37.5</v>
+      </c>
+      <c r="X19" s="9">
+        <v>44.892148256146811</v>
+      </c>
+      <c r="Y19" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z19" s="4">
+        <v>22</v>
+      </c>
+      <c r="AA19" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB19" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="5">
+        <v>-0.1939274135388826</v>
+      </c>
+      <c r="AD19" s="5">
+        <v>0.42070012934067669</v>
+      </c>
+      <c r="AE19" s="5">
+        <v>-1.952468907391583E-2</v>
+      </c>
+      <c r="AF19" s="5">
+        <v>-0.42070012934067669</v>
+      </c>
+      <c r="AG19" s="5">
+        <v>0.1939274135388826</v>
+      </c>
+      <c r="AH19" s="5">
+        <v>1.952468907391583E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B20" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C20" s="4">
+        <v>18</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" s="4">
+        <v>37</v>
+      </c>
+      <c r="G20" s="4">
+        <v>20</v>
+      </c>
+      <c r="H20" s="8">
+        <v>0.81384823395549688</v>
+      </c>
+      <c r="I20" s="4">
+        <v>-437</v>
+      </c>
+      <c r="J20" s="8">
+        <v>0.18615176604450309</v>
+      </c>
+      <c r="K20" s="4">
+        <v>437</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="N20" s="4">
+        <v>1</v>
+      </c>
+      <c r="O20" s="15">
+        <v>30.905485139186009</v>
+      </c>
+      <c r="P20" s="15">
+        <v>18.61532459110186</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="R20" s="9">
+        <v>12.290160548084151</v>
+      </c>
+      <c r="S20" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T20" s="4">
+        <v>17</v>
+      </c>
+      <c r="U20" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V20" s="4">
+        <v>1</v>
+      </c>
+      <c r="W20" s="4">
+        <v>46.5</v>
+      </c>
+      <c r="X20" s="9">
+        <v>49.520809730287873</v>
+      </c>
+      <c r="Y20" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z20" s="4">
+        <v>57</v>
+      </c>
+      <c r="AA20" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB20" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="5">
+        <v>0.2202407541409345</v>
+      </c>
+      <c r="AD20" s="5">
+        <v>2.6646969573838369E-2</v>
+      </c>
+      <c r="AE20" s="5">
+        <v>-1.7873119424890591E-2</v>
+      </c>
+      <c r="AF20" s="5">
+        <v>-2.6646969573838369E-2</v>
+      </c>
+      <c r="AG20" s="5">
+        <v>-0.2202407541409345</v>
+      </c>
+      <c r="AH20" s="5">
+        <v>1.7873119424890591E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B21" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C21" s="4">
+        <v>18</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="4">
+        <v>14</v>
+      </c>
+      <c r="G21" s="4">
+        <v>12</v>
+      </c>
+      <c r="H21" s="8">
+        <v>0.23667107572911189</v>
+      </c>
+      <c r="I21" s="4">
+        <v>322</v>
+      </c>
+      <c r="J21" s="8">
+        <v>0.76332892427088817</v>
+      </c>
+      <c r="K21" s="4">
+        <v>-322</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N21" s="4">
+        <v>0</v>
+      </c>
+      <c r="O21" s="15">
+        <v>13.489612544682471</v>
+      </c>
+      <c r="P21" s="15">
+        <v>25.643059377796028</v>
+      </c>
+      <c r="Q21" s="4">
+        <v>-5.5</v>
+      </c>
+      <c r="R21" s="9">
+        <v>-12.153446833113559</v>
+      </c>
+      <c r="S21" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T21" s="4">
+        <v>2</v>
+      </c>
+      <c r="U21" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V21" s="4">
+        <v>0</v>
+      </c>
+      <c r="W21" s="4">
+        <v>36.5</v>
+      </c>
+      <c r="X21" s="9">
+        <v>39.132671922478487</v>
+      </c>
+      <c r="Y21" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z21" s="4">
+        <v>26</v>
+      </c>
+      <c r="AA21" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB21" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="5">
+        <v>-0.45686231340680811</v>
+      </c>
+      <c r="AD21" s="5">
+        <v>0.47610270977020258</v>
+      </c>
+      <c r="AE21" s="5">
+        <v>-8.1185160144682855E-2</v>
+      </c>
+      <c r="AF21" s="5">
+        <v>-0.47610270977020258</v>
+      </c>
+      <c r="AG21" s="5">
+        <v>0.45686231340680811</v>
+      </c>
+      <c r="AH21" s="5">
+        <v>8.1185160144682855E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B22" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C22" s="4">
+        <v>18</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" s="4">
+        <v>38</v>
+      </c>
+      <c r="G22" s="4">
+        <v>10</v>
+      </c>
+      <c r="H22" s="8">
+        <v>0.74870152000406931</v>
+      </c>
+      <c r="I22" s="4">
+        <v>-297</v>
+      </c>
+      <c r="J22" s="8">
+        <v>0.25129847999593069</v>
+      </c>
+      <c r="K22" s="4">
+        <v>297</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N22" s="4">
+        <v>1</v>
+      </c>
+      <c r="O22" s="9">
+        <v>30.075581822722199</v>
+      </c>
+      <c r="P22" s="15">
+        <v>19.747653641316589</v>
+      </c>
+      <c r="Q22" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="R22" s="9">
+        <v>10.3279281814056</v>
+      </c>
+      <c r="S22" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T22" s="4">
+        <v>28</v>
+      </c>
+      <c r="U22" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V22" s="4">
+        <v>0</v>
+      </c>
+      <c r="W22" s="4">
+        <v>45.5</v>
+      </c>
+      <c r="X22" s="9">
+        <v>49.823235464038788</v>
+      </c>
+      <c r="Y22" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z22" s="4">
+        <v>48</v>
+      </c>
+      <c r="AA22" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB22" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC22" s="5">
+        <v>0.32397203278123288</v>
+      </c>
+      <c r="AD22" s="5">
+        <v>0.31436092512948172</v>
+      </c>
+      <c r="AE22" s="5">
+        <v>-7.6890102139225716E-2</v>
+      </c>
+      <c r="AF22" s="5">
+        <v>-0.31436092512948172</v>
+      </c>
+      <c r="AG22" s="5">
+        <v>-0.32397203278123288</v>
+      </c>
+      <c r="AH22" s="5">
+        <v>7.6890102139225716E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B23" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C23" s="4">
+        <v>18</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F23" s="4">
+        <v>17</v>
+      </c>
+      <c r="G23" s="4">
+        <v>24</v>
+      </c>
+      <c r="H23" s="8">
+        <v>0.70480469602802465</v>
+      </c>
+      <c r="I23" s="4">
+        <v>-238</v>
+      </c>
+      <c r="J23" s="8">
+        <v>0.29519530397197541</v>
+      </c>
+      <c r="K23" s="4">
+        <v>238</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="N23" s="4">
+        <v>0</v>
+      </c>
+      <c r="O23" s="9">
+        <v>26.189862456781221</v>
+      </c>
+      <c r="P23" s="15">
+        <v>19.81586437078397</v>
+      </c>
+      <c r="Q23" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="R23" s="9">
+        <v>6.3739980859972576</v>
+      </c>
+      <c r="S23" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T23" s="4">
+        <v>-7</v>
+      </c>
+      <c r="U23" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V23" s="4">
+        <v>0</v>
+      </c>
+      <c r="W23" s="4">
+        <v>38.5</v>
+      </c>
+      <c r="X23" s="9">
+        <v>46.005726827565191</v>
+      </c>
+      <c r="Y23" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z23" s="4">
+        <v>41</v>
+      </c>
+      <c r="AA23" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB23" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC23" s="5">
+        <v>-8.6598269641399384E-2</v>
+      </c>
+      <c r="AD23" s="5">
+        <v>-0.1271072643906323</v>
+      </c>
+      <c r="AE23" s="5">
+        <v>0.11109153790907431</v>
+      </c>
+      <c r="AF23" s="5">
+        <v>0.1271072643906323</v>
+      </c>
+      <c r="AG23" s="5">
+        <v>8.6598269641399384E-2</v>
+      </c>
+      <c r="AH23" s="5">
+        <v>-0.11109153790907431</v>
+      </c>
+    </row>
+    <row r="24" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B24" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C24" s="4">
+        <v>18</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="4">
+        <v>26</v>
+      </c>
+      <c r="G24" s="4">
+        <v>24</v>
+      </c>
+      <c r="H24" s="8">
+        <v>0.49279668363379742</v>
+      </c>
+      <c r="I24" s="4">
+        <v>102</v>
+      </c>
+      <c r="J24" s="8">
+        <v>0.50720331636620264</v>
+      </c>
+      <c r="K24" s="4">
+        <v>-102</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N24" s="4">
+        <v>0</v>
+      </c>
+      <c r="O24" s="9">
+        <v>23.145400712847241</v>
+      </c>
+      <c r="P24" s="15">
+        <v>22.175801719287058</v>
+      </c>
+      <c r="Q24" s="4">
+        <v>-3.5</v>
+      </c>
+      <c r="R24" s="9">
+        <v>0.96959899356018298</v>
+      </c>
+      <c r="S24" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T24" s="4">
+        <v>2</v>
+      </c>
+      <c r="U24" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V24" s="4">
+        <v>1</v>
+      </c>
+      <c r="W24" s="4">
+        <v>40.5</v>
+      </c>
+      <c r="X24" s="9">
+        <v>45.321202432134307</v>
+      </c>
+      <c r="Y24" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z24" s="4">
+        <v>50</v>
+      </c>
+      <c r="AA24" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB24" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="5">
+        <v>5.1401243209838868E-2</v>
+      </c>
+      <c r="AD24" s="5">
+        <v>-0.14020941734313969</v>
+      </c>
+      <c r="AE24" s="5">
+        <v>0.16552998338426861</v>
+      </c>
+      <c r="AF24" s="5">
+        <v>0.14020941734313969</v>
+      </c>
+      <c r="AG24" s="5">
+        <v>-5.1401243209838868E-2</v>
+      </c>
+      <c r="AH24" s="5">
+        <v>-0.16552998338426861</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="Q7:V7"/>
+    <mergeCell ref="W7:AB7"/>
+    <mergeCell ref="AC7:AE7"/>
+    <mergeCell ref="AF7:AH7"/>
+  </mergeCells>
+  <conditionalFormatting sqref="AC9:AC24">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD9:AD24">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE9:AE24">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF9:AF24">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG9:AG24">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH9:AH24">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="1" id="{842BA054-213D-484C-8305-E1A32BC78F36}">
+            <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>N9:N24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="2" id="{7B662BFB-6111-0742-ABDC-6A72455D58AB}">
+            <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>V9:V24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="3" id="{723EBDCB-3937-3640-8C60-E03AB9ABBC33}">
+            <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>AB9:AB24</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3197922-17FD-3446-ABDB-5FDED8A662DF}">
-  <dimension ref="B2:F46"/>
+  <dimension ref="B2:F47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.2">
@@ -28310,7 +32049,7 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B4" cm="1">
-        <f t="array" ref="B4:B15">_xlfn.UNIQUE(_xlfn._xlws.FILTER(Master!C9:C1000,NOT(ISBLANK(Master!C9:C1000))))</f>
+        <f t="array" ref="B4:B16">_xlfn.UNIQUE(_xlfn._xlws.FILTER(Master!C9:C1000,NOT(ISBLANK(Master!C9:C1000))))</f>
         <v>6</v>
       </c>
       <c r="C4">
@@ -28561,6 +32300,11 @@
         <v>0.625</v>
       </c>
     </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B16">
+        <v>18</v>
+      </c>
+    </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B17" s="18" t="s">
         <v>146</v>
@@ -28585,7 +32329,7 @@
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B19" cm="1">
-        <f t="array" ref="B19:B30">_xlfn.UNIQUE(_xlfn._xlws.FILTER(Master!C9:C1000,NOT(ISBLANK(Master!C9:C1000))))</f>
+        <f t="array" ref="B19:B31">_xlfn.UNIQUE(_xlfn._xlws.FILTER(Master!C9:C1000,NOT(ISBLANK(Master!C9:C1000))))</f>
         <v>6</v>
       </c>
       <c r="C19">
@@ -28836,6 +32580,11 @@
         <v>0.625</v>
       </c>
     </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B31">
+        <v>18</v>
+      </c>
+    </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" s="18" t="s">
         <v>146</v>
@@ -28860,7 +32609,7 @@
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" cm="1">
-        <f t="array" ref="B35:B46">_xlfn.UNIQUE(_xlfn._xlws.FILTER(Master!C9:C1000,NOT(ISBLANK(Master!C9:C1000))))</f>
+        <f t="array" ref="B35:B47">_xlfn.UNIQUE(_xlfn._xlws.FILTER(Master!C9:C1000,NOT(ISBLANK(Master!C9:C1000))))</f>
         <v>6</v>
       </c>
       <c r="C35">
@@ -29109,6 +32858,11 @@
       <c r="F46" s="12">
         <f t="shared" ref="F46" si="17">D46/C46</f>
         <v>0.4375</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B47">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -29166,27 +32920,27 @@
       <c r="C5" s="6"/>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="19" t="s">
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19" t="s">
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19" t="s">
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="Q6" s="19"/>
-      <c r="R6" s="19"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
@@ -30219,28 +33973,28 @@
       <c r="C5" s="6"/>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="19" t="s">
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
       <c r="M6" s="7"/>
-      <c r="N6" s="19" t="s">
+      <c r="N6" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19" t="s">
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="R6" s="19"/>
-      <c r="S6" s="19"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
@@ -31306,28 +35060,28 @@
       <c r="C5" s="6"/>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="19" t="s">
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
       <c r="M6" s="7"/>
-      <c r="N6" s="19" t="s">
+      <c r="N6" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19" t="s">
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="R6" s="19"/>
-      <c r="S6" s="19"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
@@ -32281,28 +36035,28 @@
       <c r="C5" s="6"/>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="19" t="s">
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
       <c r="M6" s="7"/>
-      <c r="N6" s="19" t="s">
+      <c r="N6" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19" t="s">
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="R6" s="19"/>
-      <c r="S6" s="19"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
@@ -33305,28 +37059,28 @@
       <c r="C5" s="6"/>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="19" t="s">
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
       <c r="M6" s="7"/>
-      <c r="N6" s="19" t="s">
+      <c r="N6" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19" t="s">
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="R6" s="19"/>
-      <c r="S6" s="19"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
@@ -35382,45 +39136,45 @@
       <c r="C6" s="6"/>
     </row>
     <row r="7" spans="2:32" x14ac:dyDescent="0.2">
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19" t="s">
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19" t="s">
+      <c r="N7" s="20"/>
+      <c r="O7" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="19"/>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19"/>
-      <c r="T7" s="19"/>
-      <c r="U7" s="19" t="s">
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20"/>
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="V7" s="19"/>
-      <c r="W7" s="19"/>
-      <c r="X7" s="19"/>
-      <c r="Y7" s="19"/>
-      <c r="Z7" s="19"/>
-      <c r="AA7" s="19" t="s">
+      <c r="V7" s="20"/>
+      <c r="W7" s="20"/>
+      <c r="X7" s="20"/>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="20"/>
+      <c r="AA7" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="AB7" s="19"/>
-      <c r="AC7" s="19"/>
-      <c r="AD7" s="19" t="s">
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="20"/>
+      <c r="AD7" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="AE7" s="19"/>
-      <c r="AF7" s="19"/>
+      <c r="AE7" s="20"/>
+      <c r="AF7" s="20"/>
     </row>
     <row r="8" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
@@ -37178,45 +40932,45 @@
       <c r="C6" s="6"/>
     </row>
     <row r="7" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19" t="s">
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="19" t="s">
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19"/>
-      <c r="T7" s="19"/>
-      <c r="U7" s="19"/>
-      <c r="V7" s="19"/>
-      <c r="W7" s="19" t="s">
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="X7" s="19"/>
-      <c r="Y7" s="19"/>
-      <c r="Z7" s="19"/>
-      <c r="AA7" s="19"/>
-      <c r="AB7" s="19"/>
-      <c r="AC7" s="19" t="s">
+      <c r="X7" s="20"/>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="20"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="AD7" s="19"/>
-      <c r="AE7" s="19"/>
-      <c r="AF7" s="19" t="s">
+      <c r="AD7" s="20"/>
+      <c r="AE7" s="20"/>
+      <c r="AF7" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="AG7" s="19"/>
-      <c r="AH7" s="19"/>
+      <c r="AG7" s="20"/>
+      <c r="AH7" s="20"/>
     </row>
     <row r="8" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">

--- a/model results/2025 Results.xlsx
+++ b/model results/2025 Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jmiller/Documents/Fun/nfl/model results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2DB388-3AEA-9145-9CF5-53F6D6F5BA48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263CA9AC-A511-5F4B-B977-E452A119337A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17360" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17360" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="2" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <sheet name="Week 16" sheetId="14" r:id="rId13"/>
     <sheet name="Week 17" sheetId="15" r:id="rId14"/>
     <sheet name="Week 18" sheetId="16" r:id="rId15"/>
+    <sheet name="Wild Card" sheetId="17" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,9 +48,10 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="2">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
@@ -60,16 +62,30 @@
       </extLst>
     </bk>
   </futureMetadata>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="2" v="0"/>
+    </bk>
+  </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3461" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3600" uniqueCount="225">
   <si>
     <t>season</t>
   </si>
@@ -928,6 +944,68 @@
 </styleSheet>
 </file>
 
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>8</v>
+    <v>13</v>
+    <v>1</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_error">
+    <k n="colOffset" t="i"/>
+    <k n="errorType" t="i"/>
+    <k n="rwOffset" t="i"/>
+    <k n="subType" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1213,7 +1291,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E32420-1D15-E549-AAF4-FB71DE782F62}">
-  <dimension ref="B2:AH202"/>
+  <dimension ref="B2:AH208"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.1640625" customWidth="1"/>
@@ -1269,19 +1347,19 @@
       </c>
       <c r="C3" s="13">
         <f>COUNTA(N9:N1000)</f>
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D3" s="13">
         <f>SUM(N9:N1000)</f>
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E3" s="13">
         <f>C3-D3</f>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F3" s="19">
         <f>D3/C3</f>
-        <v>0.61855670103092786</v>
+        <v>0.625</v>
       </c>
       <c r="G3" s="6"/>
     </row>
@@ -1291,19 +1369,19 @@
       </c>
       <c r="C4" s="13">
         <f>COUNTA(V9:V1000)</f>
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D4" s="13">
         <f>SUM(V9:V1000)</f>
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E4" s="13">
         <f>C4-D4</f>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F4" s="14">
         <f>D4/C4</f>
-        <v>0.52845528455284552</v>
+        <v>0.54263565891472865</v>
       </c>
       <c r="G4" s="6"/>
     </row>
@@ -1313,19 +1391,19 @@
       </c>
       <c r="C5" s="13">
         <f>COUNTA(AB9:AB1000)</f>
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D5" s="13">
         <f>SUM(AB9:AB1000)</f>
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E5" s="13">
         <f>C5-D5</f>
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F5" s="14">
         <f>D5/C5</f>
-        <v>0.45528455284552843</v>
+        <v>0.44961240310077522</v>
       </c>
       <c r="G5" s="6"/>
     </row>
@@ -18752,6 +18830,504 @@
         <v>-0.16552998338426861</v>
       </c>
     </row>
+    <row r="203" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B203" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C203" s="4">
+        <v>19</v>
+      </c>
+      <c r="D203" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E203" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F203" s="4">
+        <v>31</v>
+      </c>
+      <c r="G203" s="4">
+        <v>34</v>
+      </c>
+      <c r="H203" s="8">
+        <v>0.29018179618082302</v>
+      </c>
+      <c r="I203" s="4">
+        <v>244</v>
+      </c>
+      <c r="J203" s="8">
+        <v>0.70981820381917704</v>
+      </c>
+      <c r="K203" s="4">
+        <v>-244</v>
+      </c>
+      <c r="L203" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M203" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="N203" s="4">
+        <v>1</v>
+      </c>
+      <c r="O203" s="15">
+        <v>19.394053352958149</v>
+      </c>
+      <c r="P203" s="15">
+        <v>26.817894340589358</v>
+      </c>
+      <c r="Q203" s="4">
+        <v>-10.5</v>
+      </c>
+      <c r="R203" s="15">
+        <v>-7.4238409876312126</v>
+      </c>
+      <c r="S203" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T203" s="4">
+        <v>-3</v>
+      </c>
+      <c r="U203" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V203" s="4">
+        <v>1</v>
+      </c>
+      <c r="W203" s="4">
+        <v>46.5</v>
+      </c>
+      <c r="X203" s="9">
+        <v>46.211947693547501</v>
+      </c>
+      <c r="Y203" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z203" s="4">
+        <v>65</v>
+      </c>
+      <c r="AA203" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB203" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B204" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C204" s="4">
+        <v>19</v>
+      </c>
+      <c r="D204" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E204" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F204" s="4">
+        <v>31</v>
+      </c>
+      <c r="G204" s="4">
+        <v>27</v>
+      </c>
+      <c r="H204" s="8">
+        <v>0.58406292373303081</v>
+      </c>
+      <c r="I204" s="4">
+        <v>-140</v>
+      </c>
+      <c r="J204" s="8">
+        <v>0.41593707626696919</v>
+      </c>
+      <c r="K204" s="4">
+        <v>140</v>
+      </c>
+      <c r="L204" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="M204" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N204" s="4">
+        <v>1</v>
+      </c>
+      <c r="O204" s="15">
+        <v>26.148568788948669</v>
+      </c>
+      <c r="P204" s="15">
+        <v>26.46996890305395</v>
+      </c>
+      <c r="Q204" s="4">
+        <v>-1.5</v>
+      </c>
+      <c r="R204" s="15">
+        <v>-0.32140011410528402</v>
+      </c>
+      <c r="S204" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T204" s="4">
+        <v>4</v>
+      </c>
+      <c r="U204" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V204" s="4">
+        <v>1</v>
+      </c>
+      <c r="W204" s="4">
+        <v>45.5</v>
+      </c>
+      <c r="X204" s="9">
+        <v>52.618537692002619</v>
+      </c>
+      <c r="Y204" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z204" s="4">
+        <v>58</v>
+      </c>
+      <c r="AA204" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB204" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B205" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C205" s="4">
+        <v>19</v>
+      </c>
+      <c r="D205" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E205" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F205" s="4">
+        <v>24</v>
+      </c>
+      <c r="G205" s="4">
+        <v>27</v>
+      </c>
+      <c r="H205" s="8">
+        <v>0.60932757308712082</v>
+      </c>
+      <c r="I205" s="4">
+        <v>-155</v>
+      </c>
+      <c r="J205" s="8">
+        <v>0.39067242691287918</v>
+      </c>
+      <c r="K205" s="4">
+        <v>155</v>
+      </c>
+      <c r="L205" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M205" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="N205" s="4">
+        <v>0</v>
+      </c>
+      <c r="O205" s="15">
+        <v>26.09500735212626</v>
+      </c>
+      <c r="P205" s="15">
+        <v>24.12083548004232</v>
+      </c>
+      <c r="Q205" s="4">
+        <v>-1.5</v>
+      </c>
+      <c r="R205" s="9">
+        <v>1.974171872083939</v>
+      </c>
+      <c r="S205" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T205" s="4">
+        <v>-3</v>
+      </c>
+      <c r="U205" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V205" s="4">
+        <v>0</v>
+      </c>
+      <c r="W205" s="4">
+        <v>51.5</v>
+      </c>
+      <c r="X205" s="9">
+        <v>50.215842832168583</v>
+      </c>
+      <c r="Y205" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z205" s="4">
+        <v>51</v>
+      </c>
+      <c r="AA205" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB205" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B206" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C206" s="4">
+        <v>19</v>
+      </c>
+      <c r="D206" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E206" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F206" s="4">
+        <v>19</v>
+      </c>
+      <c r="G206" s="4">
+        <v>23</v>
+      </c>
+      <c r="H206" s="8">
+        <v>0.49617496342080702</v>
+      </c>
+      <c r="I206" s="4">
+        <v>101</v>
+      </c>
+      <c r="J206" s="8">
+        <v>0.50382503657919298</v>
+      </c>
+      <c r="K206" s="4">
+        <v>-101</v>
+      </c>
+      <c r="L206" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M206" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="N206" s="4">
+        <v>1</v>
+      </c>
+      <c r="O206" s="15">
+        <v>24.496753433649442</v>
+      </c>
+      <c r="P206" s="15">
+        <v>23.711678199787059</v>
+      </c>
+      <c r="Q206" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="R206" s="9">
+        <v>0.78507523386238276</v>
+      </c>
+      <c r="S206" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T206" s="4">
+        <v>-4</v>
+      </c>
+      <c r="U206" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V206" s="4">
+        <v>1</v>
+      </c>
+      <c r="W206" s="4">
+        <v>44.5</v>
+      </c>
+      <c r="X206" s="9">
+        <v>48.208431633436497</v>
+      </c>
+      <c r="Y206" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z206" s="4">
+        <v>42</v>
+      </c>
+      <c r="AA206" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB206" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B207" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C207" s="4">
+        <v>19</v>
+      </c>
+      <c r="D207" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E207" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F207" s="4">
+        <v>16</v>
+      </c>
+      <c r="G207" s="4">
+        <v>3</v>
+      </c>
+      <c r="H207" s="8">
+        <v>0.77533578600133835</v>
+      </c>
+      <c r="I207" s="4">
+        <v>-345</v>
+      </c>
+      <c r="J207" s="8">
+        <v>0.22466421399866171</v>
+      </c>
+      <c r="K207" s="4">
+        <v>345</v>
+      </c>
+      <c r="L207" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M207" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N207" s="4">
+        <v>1</v>
+      </c>
+      <c r="O207" s="15">
+        <v>28.938898589423289</v>
+      </c>
+      <c r="P207" s="15">
+        <v>17.705749610579009</v>
+      </c>
+      <c r="Q207" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="R207" s="9">
+        <v>11.23314897884428</v>
+      </c>
+      <c r="S207" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T207" s="4">
+        <v>13</v>
+      </c>
+      <c r="U207" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V207" s="4">
+        <v>1</v>
+      </c>
+      <c r="W207" s="4">
+        <v>46.5</v>
+      </c>
+      <c r="X207" s="9">
+        <v>46.644648200002287</v>
+      </c>
+      <c r="Y207" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z207" s="4">
+        <v>19</v>
+      </c>
+      <c r="AA207" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB207" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B208" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C208" s="4">
+        <v>19</v>
+      </c>
+      <c r="D208" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E208" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F208" s="4">
+        <v>6</v>
+      </c>
+      <c r="G208" s="4">
+        <v>30</v>
+      </c>
+      <c r="H208" s="8">
+        <v>0.45496618005377543</v>
+      </c>
+      <c r="I208" s="4">
+        <v>119</v>
+      </c>
+      <c r="J208" s="8">
+        <v>0.54503381994622457</v>
+      </c>
+      <c r="K208" s="4">
+        <v>-119</v>
+      </c>
+      <c r="L208" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="M208" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="N208" s="4">
+        <v>1</v>
+      </c>
+      <c r="O208" s="15">
+        <v>18.481034206854751</v>
+      </c>
+      <c r="P208" s="15">
+        <v>23.550891694555919</v>
+      </c>
+      <c r="Q208" s="4">
+        <v>-3</v>
+      </c>
+      <c r="R208" s="15">
+        <v>-5.0698574877011673</v>
+      </c>
+      <c r="S208" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T208" s="4">
+        <v>-24</v>
+      </c>
+      <c r="U208" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V208" s="4">
+        <v>1</v>
+      </c>
+      <c r="W208" s="4">
+        <v>39.5</v>
+      </c>
+      <c r="X208" s="9">
+        <v>42.031925901410673</v>
+      </c>
+      <c r="Y208" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z208" s="4">
+        <v>36</v>
+      </c>
+      <c r="AA208" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB208" s="4">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="AF7:AH7"/>
@@ -18762,6 +19338,474 @@
     <mergeCell ref="AC7:AE7"/>
   </mergeCells>
   <conditionalFormatting sqref="AC9:AC23">
+    <cfRule type="colorScale" priority="110">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC24:AC38">
+    <cfRule type="colorScale" priority="103">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC39:AC51">
+    <cfRule type="colorScale" priority="91">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC52:AC65">
+    <cfRule type="colorScale" priority="84">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC66:AC79">
+    <cfRule type="colorScale" priority="77">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC80:AC94">
+    <cfRule type="colorScale" priority="74">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC95:AC108">
+    <cfRule type="colorScale" priority="61">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC109:AC124">
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC125:AC138">
+    <cfRule type="colorScale" priority="43">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC139:AC154">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC155:AC170">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC171:AC186">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC187:AC202">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD9:AD23">
+    <cfRule type="colorScale" priority="109">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD24:AD38">
+    <cfRule type="colorScale" priority="102">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD39:AD51">
+    <cfRule type="colorScale" priority="92">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD52:AD65">
+    <cfRule type="colorScale" priority="85">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD66:AD79">
+    <cfRule type="colorScale" priority="78">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD80:AD94">
+    <cfRule type="colorScale" priority="73">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD95:AD108">
+    <cfRule type="colorScale" priority="62">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD109:AD124">
+    <cfRule type="colorScale" priority="53">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD125:AD138">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD139:AD154">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD155:AD170">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD171:AD186">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD187:AD202">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE9:AE23">
+    <cfRule type="colorScale" priority="108">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE24:AE38">
+    <cfRule type="colorScale" priority="101">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE39:AE51">
+    <cfRule type="colorScale" priority="93">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE52:AE65">
+    <cfRule type="colorScale" priority="86">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE66:AE79">
+    <cfRule type="colorScale" priority="79">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE80:AE94">
+    <cfRule type="colorScale" priority="72">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE95:AE108">
+    <cfRule type="colorScale" priority="63">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE109:AE124">
+    <cfRule type="colorScale" priority="54">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE125:AE138">
+    <cfRule type="colorScale" priority="45">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE139:AE154">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE155:AE170">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE171:AE186">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE187:AE202">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF9:AF23">
     <cfRule type="colorScale" priority="107">
       <colorScale>
         <cfvo type="min"/>
@@ -18773,7 +19817,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC24:AC38">
+  <conditionalFormatting sqref="AF24:AF38">
     <cfRule type="colorScale" priority="100">
       <colorScale>
         <cfvo type="min"/>
@@ -18785,7 +19829,175 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC39:AC51">
+  <conditionalFormatting sqref="AF39:AF51">
+    <cfRule type="colorScale" priority="94">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF52:AF65">
+    <cfRule type="colorScale" priority="87">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF66:AF79">
+    <cfRule type="colorScale" priority="80">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF80:AF94">
+    <cfRule type="colorScale" priority="71">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF95:AF108">
+    <cfRule type="colorScale" priority="64">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF109:AF124">
+    <cfRule type="colorScale" priority="55">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF125:AF138">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF139:AF154">
+    <cfRule type="colorScale" priority="37">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF155:AF170">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF171:AF186">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF187:AF202">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG9:AG23">
+    <cfRule type="colorScale" priority="106">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG24:AG38">
+    <cfRule type="colorScale" priority="99">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG39:AG51">
+    <cfRule type="colorScale" priority="95">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG52:AG65">
     <cfRule type="colorScale" priority="88">
       <colorScale>
         <cfvo type="min"/>
@@ -18797,7 +20009,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC52:AC65">
+  <conditionalFormatting sqref="AG66:AG79">
     <cfRule type="colorScale" priority="81">
       <colorScale>
         <cfvo type="min"/>
@@ -18809,8 +20021,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC66:AC79">
-    <cfRule type="colorScale" priority="74">
+  <conditionalFormatting sqref="AG80:AG94">
+    <cfRule type="colorScale" priority="70">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -18821,8 +20033,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC80:AC94">
-    <cfRule type="colorScale" priority="71">
+  <conditionalFormatting sqref="AG95:AG108">
+    <cfRule type="colorScale" priority="65">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -18833,8 +20045,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC95:AC108">
-    <cfRule type="colorScale" priority="58">
+  <conditionalFormatting sqref="AG109:AG124">
+    <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -18845,8 +20057,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC109:AC124">
-    <cfRule type="colorScale" priority="49">
+  <conditionalFormatting sqref="AG125:AG138">
+    <cfRule type="colorScale" priority="47">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -18857,8 +20069,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC125:AC138">
-    <cfRule type="colorScale" priority="40">
+  <conditionalFormatting sqref="AG139:AG154">
+    <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -18869,8 +20081,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC139:AC154">
-    <cfRule type="colorScale" priority="31">
+  <conditionalFormatting sqref="AG155:AG170">
+    <cfRule type="colorScale" priority="29">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -18881,8 +20093,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC155:AC170">
-    <cfRule type="colorScale" priority="22">
+  <conditionalFormatting sqref="AG171:AG186">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -18893,8 +20105,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC171:AC186">
-    <cfRule type="colorScale" priority="13">
+  <conditionalFormatting sqref="AG187:AG202">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -18905,8 +20117,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD9:AD23">
-    <cfRule type="colorScale" priority="106">
+  <conditionalFormatting sqref="AH9:AH23">
+    <cfRule type="colorScale" priority="105">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -18917,8 +20129,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD24:AD38">
-    <cfRule type="colorScale" priority="99">
+  <conditionalFormatting sqref="AH24:AH38">
+    <cfRule type="colorScale" priority="98">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -18929,7 +20141,19 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD39:AD51">
+  <conditionalFormatting sqref="AH39:AH51">
+    <cfRule type="colorScale" priority="96">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH52:AH65">
     <cfRule type="colorScale" priority="89">
       <colorScale>
         <cfvo type="min"/>
@@ -18941,7 +20165,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD52:AD65">
+  <conditionalFormatting sqref="AH66:AH79">
     <cfRule type="colorScale" priority="82">
       <colorScale>
         <cfvo type="min"/>
@@ -18953,163 +20177,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD66:AD79">
-    <cfRule type="colorScale" priority="75">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD80:AD94">
-    <cfRule type="colorScale" priority="70">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD95:AD108">
-    <cfRule type="colorScale" priority="59">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD109:AD124">
-    <cfRule type="colorScale" priority="50">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD125:AD138">
-    <cfRule type="colorScale" priority="41">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD139:AD154">
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD155:AD170">
-    <cfRule type="colorScale" priority="23">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD171:AD186">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE9:AE23">
-    <cfRule type="colorScale" priority="105">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE24:AE38">
-    <cfRule type="colorScale" priority="98">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE39:AE51">
-    <cfRule type="colorScale" priority="90">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE52:AE65">
-    <cfRule type="colorScale" priority="83">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE66:AE79">
-    <cfRule type="colorScale" priority="76">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE80:AE94">
+  <conditionalFormatting sqref="AH80:AH94">
     <cfRule type="colorScale" priority="69">
       <colorScale>
         <cfvo type="min"/>
@@ -19121,427 +20189,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE95:AE108">
-    <cfRule type="colorScale" priority="60">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE109:AE124">
-    <cfRule type="colorScale" priority="51">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE125:AE138">
-    <cfRule type="colorScale" priority="42">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE139:AE154">
-    <cfRule type="colorScale" priority="33">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE155:AE170">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE171:AE186">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF9:AF23">
-    <cfRule type="colorScale" priority="104">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF24:AF38">
-    <cfRule type="colorScale" priority="97">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF39:AF51">
-    <cfRule type="colorScale" priority="91">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF52:AF65">
-    <cfRule type="colorScale" priority="84">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF66:AF79">
-    <cfRule type="colorScale" priority="77">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF80:AF94">
-    <cfRule type="colorScale" priority="68">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF95:AF108">
-    <cfRule type="colorScale" priority="61">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF109:AF124">
-    <cfRule type="colorScale" priority="52">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF125:AF138">
-    <cfRule type="colorScale" priority="43">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF139:AF154">
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF155:AF170">
-    <cfRule type="colorScale" priority="25">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF171:AF186">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG9:AG23">
-    <cfRule type="colorScale" priority="103">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG24:AG38">
-    <cfRule type="colorScale" priority="96">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG39:AG51">
-    <cfRule type="colorScale" priority="92">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG52:AG65">
-    <cfRule type="colorScale" priority="85">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG66:AG79">
-    <cfRule type="colorScale" priority="78">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG80:AG94">
-    <cfRule type="colorScale" priority="67">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG95:AG108">
-    <cfRule type="colorScale" priority="62">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG109:AG124">
-    <cfRule type="colorScale" priority="53">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG125:AG138">
-    <cfRule type="colorScale" priority="44">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG139:AG154">
-    <cfRule type="colorScale" priority="35">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG155:AG170">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG171:AG186">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH9:AH23">
-    <cfRule type="colorScale" priority="102">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH24:AH38">
-    <cfRule type="colorScale" priority="95">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH39:AH51">
-    <cfRule type="colorScale" priority="93">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH52:AH65">
-    <cfRule type="colorScale" priority="86">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH66:AH79">
-    <cfRule type="colorScale" priority="79">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH80:AH94">
+  <conditionalFormatting sqref="AH95:AH108">
     <cfRule type="colorScale" priority="66">
       <colorScale>
         <cfvo type="min"/>
@@ -19553,20 +20201,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH95:AH108">
-    <cfRule type="colorScale" priority="63">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AH109:AH124">
-    <cfRule type="colorScale" priority="54">
+    <cfRule type="colorScale" priority="57">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -19578,7 +20214,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH125:AH138">
-    <cfRule type="colorScale" priority="45">
+    <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -19590,7 +20226,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH139:AH154">
-    <cfRule type="colorScale" priority="36">
+    <cfRule type="colorScale" priority="39">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -19602,7 +20238,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH155:AH170">
-    <cfRule type="colorScale" priority="27">
+    <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -19614,67 +20250,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH171:AH186">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC187:AC202">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD187:AD202">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE187:AE202">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF187:AF202">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG187:AG202">
-    <cfRule type="colorScale" priority="8">
+    <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -19686,7 +20262,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH187:AH202">
-    <cfRule type="colorScale" priority="9">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -19705,7 +20281,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="72" id="{EDEA8277-96E2-534B-9496-1DB5484BFD68}">
+          <x14:cfRule type="iconSet" priority="75" id="{EDEA8277-96E2-534B-9496-1DB5484BFD68}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19724,7 +20300,7 @@
           <xm:sqref>N80:N94</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="55" id="{DD4EF5CC-2E62-F245-AF58-2756E5752FDF}">
+          <x14:cfRule type="iconSet" priority="58" id="{DD4EF5CC-2E62-F245-AF58-2756E5752FDF}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19743,7 +20319,7 @@
           <xm:sqref>N95:N108</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="46" id="{37C61786-4A12-0746-A763-4990B69F05C7}">
+          <x14:cfRule type="iconSet" priority="49" id="{37C61786-4A12-0746-A763-4990B69F05C7}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19762,7 +20338,7 @@
           <xm:sqref>N109:N124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="37" id="{212E7F37-E966-AF4F-A0C3-E0E8E1340734}">
+          <x14:cfRule type="iconSet" priority="40" id="{212E7F37-E966-AF4F-A0C3-E0E8E1340734}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19781,7 +20357,7 @@
           <xm:sqref>N125:N138</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="28" id="{9742010F-AC5F-C647-A8CE-71E3275DF15E}">
+          <x14:cfRule type="iconSet" priority="31" id="{9742010F-AC5F-C647-A8CE-71E3275DF15E}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19800,7 +20376,7 @@
           <xm:sqref>N139:N154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="19" id="{53BBD899-D2C8-074A-936B-361D7C508C63}">
+          <x14:cfRule type="iconSet" priority="22" id="{53BBD899-D2C8-074A-936B-361D7C508C63}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19819,7 +20395,7 @@
           <xm:sqref>N155:N170</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="10" id="{A12D9CF1-1026-094B-90AD-EA1CA9A2D92B}">
+          <x14:cfRule type="iconSet" priority="13" id="{A12D9CF1-1026-094B-90AD-EA1CA9A2D92B}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19838,7 +20414,26 @@
           <xm:sqref>N171:N186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="94" id="{48C4D57C-361D-AB47-A2B7-3D4E42CE6188}">
+          <x14:cfRule type="iconSet" priority="4" id="{45E17C71-3C4A-9248-8E64-529100B00271}">
+            <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>N187:N202</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="97" id="{48C4D57C-361D-AB47-A2B7-3D4E42CE6188}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19857,7 +20452,7 @@
           <xm:sqref>N24:AA38</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="87" id="{C3D59626-8CA7-8645-8330-0E71AB30C540}">
+          <x14:cfRule type="iconSet" priority="90" id="{C3D59626-8CA7-8645-8330-0E71AB30C540}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19876,7 +20471,7 @@
           <xm:sqref>N39:AA51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="80" id="{6D153A18-6D77-9445-BF8D-3BA4EDDD3FBA}">
+          <x14:cfRule type="iconSet" priority="83" id="{6D153A18-6D77-9445-BF8D-3BA4EDDD3FBA}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19895,7 +20490,7 @@
           <xm:sqref>N52:AA65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="73" id="{C34C5491-7DF8-D04C-B3C0-3779DAAA33EE}">
+          <x14:cfRule type="iconSet" priority="76" id="{C34C5491-7DF8-D04C-B3C0-3779DAAA33EE}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19914,7 +20509,7 @@
           <xm:sqref>N66:AA79</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="101" id="{4DC6D28C-E799-D04F-BAD2-092B8419C03D}">
+          <x14:cfRule type="iconSet" priority="104" id="{4DC6D28C-E799-D04F-BAD2-092B8419C03D}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19933,7 +20528,7 @@
           <xm:sqref>N9:AB23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="65" id="{92AD66C2-D91E-D648-9AC6-2417C2445C43}">
+          <x14:cfRule type="iconSet" priority="68" id="{92AD66C2-D91E-D648-9AC6-2417C2445C43}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19952,7 +20547,7 @@
           <xm:sqref>V80:V94</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="56" id="{2D523F71-4BB4-9940-8B5D-C962CA9D6F15}">
+          <x14:cfRule type="iconSet" priority="59" id="{2D523F71-4BB4-9940-8B5D-C962CA9D6F15}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19971,7 +20566,7 @@
           <xm:sqref>V95:V108</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="47" id="{2094B9A9-658A-3D41-A969-4F7B5F1A7D42}">
+          <x14:cfRule type="iconSet" priority="50" id="{2094B9A9-658A-3D41-A969-4F7B5F1A7D42}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19990,7 +20585,7 @@
           <xm:sqref>V109:V124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="38" id="{7AD482D6-AFFD-C546-9642-22AC15E71775}">
+          <x14:cfRule type="iconSet" priority="41" id="{7AD482D6-AFFD-C546-9642-22AC15E71775}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -20009,7 +20604,7 @@
           <xm:sqref>V125:V138</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="29" id="{3B475BB3-A842-F24C-8D71-84FCC9C136B4}">
+          <x14:cfRule type="iconSet" priority="32" id="{3B475BB3-A842-F24C-8D71-84FCC9C136B4}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -20028,7 +20623,7 @@
           <xm:sqref>V139:V154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="20" id="{ADD77C7B-8E6B-7A48-8AAC-8A63FE24FF97}">
+          <x14:cfRule type="iconSet" priority="23" id="{ADD77C7B-8E6B-7A48-8AAC-8A63FE24FF97}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -20047,7 +20642,7 @@
           <xm:sqref>V155:V170</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="11" id="{17F128E4-E069-B54E-9112-2E64042DD7FA}">
+          <x14:cfRule type="iconSet" priority="14" id="{17F128E4-E069-B54E-9112-2E64042DD7FA}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -20066,7 +20661,26 @@
           <xm:sqref>V171:V186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="64" id="{409D8166-545E-3045-805D-7C96DC6956B1}">
+          <x14:cfRule type="iconSet" priority="5" id="{DAD5E8EA-F4DA-7E4E-9FFA-52F388734A27}">
+            <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>V187:V202</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="67" id="{409D8166-545E-3045-805D-7C96DC6956B1}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -20085,7 +20699,7 @@
           <xm:sqref>AB80:AB94</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="57" id="{578139A0-9556-A24C-89D1-3B66D89331FA}">
+          <x14:cfRule type="iconSet" priority="60" id="{578139A0-9556-A24C-89D1-3B66D89331FA}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -20104,7 +20718,7 @@
           <xm:sqref>AB95:AB108</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="48" id="{869A3731-7EDB-9143-AD0D-591DEB781BAF}">
+          <x14:cfRule type="iconSet" priority="51" id="{869A3731-7EDB-9143-AD0D-591DEB781BAF}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -20123,7 +20737,7 @@
           <xm:sqref>AB109:AB124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="39" id="{90EFE230-91F0-784C-B726-5BE6F84EE2FC}">
+          <x14:cfRule type="iconSet" priority="42" id="{90EFE230-91F0-784C-B726-5BE6F84EE2FC}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -20142,7 +20756,7 @@
           <xm:sqref>AB125:AB138</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="30" id="{7941D79E-AD1D-3F44-8D4F-313B45BDFDD4}">
+          <x14:cfRule type="iconSet" priority="33" id="{7941D79E-AD1D-3F44-8D4F-313B45BDFDD4}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -20161,7 +20775,7 @@
           <xm:sqref>AB139:AB154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="21" id="{DEBE5BDC-29DE-8246-9122-5A2B43CD922F}">
+          <x14:cfRule type="iconSet" priority="24" id="{DEBE5BDC-29DE-8246-9122-5A2B43CD922F}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -20180,7 +20794,7 @@
           <xm:sqref>AB155:AB170</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="12" id="{6EF58D86-81A1-CC4C-B5CF-2174EDC27A28}">
+          <x14:cfRule type="iconSet" priority="15" id="{6EF58D86-81A1-CC4C-B5CF-2174EDC27A28}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -20199,45 +20813,7 @@
           <xm:sqref>AB171:AB186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="1" id="{45E17C71-3C4A-9248-8E64-529100B00271}">
-            <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>N187:N202</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="2" id="{DAD5E8EA-F4DA-7E4E-9FFA-52F388734A27}">
-            <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>V187:V202</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="3" id="{18ED4D56-16D4-3E4D-8DB7-26B21E81C10A}">
+          <x14:cfRule type="iconSet" priority="6" id="{18ED4D56-16D4-3E4D-8DB7-26B21E81C10A}">
             <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -20254,6 +20830,63 @@
             </x14:iconSet>
           </x14:cfRule>
           <xm:sqref>AB187:AB202</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="1" id="{556C4078-B3B5-3E4B-A450-84B83212CF26}">
+            <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>N203:N208</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="2" id="{8DCBDD1A-6D6B-AC4E-9A52-43472B7A1B78}">
+            <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>V203:V208</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="3" id="{B00C705B-29CE-DA49-A129-44FA23D9CB43}">
+            <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>AB203:AB208</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -31874,12 +32507,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="AF7:AH7"/>
     <mergeCell ref="H7:N7"/>
     <mergeCell ref="O7:P7"/>
     <mergeCell ref="Q7:V7"/>
     <mergeCell ref="W7:AB7"/>
     <mergeCell ref="AC7:AE7"/>
-    <mergeCell ref="AF7:AH7"/>
   </mergeCells>
   <conditionalFormatting sqref="AC9:AC24">
     <cfRule type="colorScale" priority="4">
@@ -32020,9 +32653,920 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46E61A6C-5319-6E42-8D70-5A0FBB289F47}">
+  <dimension ref="B2:AH14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="3" width="9.5" customWidth="1"/>
+    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.1640625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="4.83203125" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="6.6640625" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="14" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="11.6640625" customWidth="1"/>
+    <col min="17" max="17" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="10.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B2" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="13">
+        <f>COUNTA($C$9:$C$14)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B3" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="13">
+        <f>SUM(N9:$N$14)</f>
+        <v>5</v>
+      </c>
+      <c r="D3" s="14">
+        <f>C3/$C$2</f>
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="4" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B4" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="13">
+        <f>SUM(V9:$V$14)</f>
+        <v>5</v>
+      </c>
+      <c r="D4" s="14">
+        <f t="shared" ref="D4:D5" si="0">C4/$C$2</f>
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="5" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B5" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5" s="13">
+        <f>SUM(AB9:$AB$14)</f>
+        <v>2</v>
+      </c>
+      <c r="D5" s="14">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="6" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="C6" s="6"/>
+    </row>
+    <row r="7" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="H7" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="X7" s="20"/>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="20"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD7" s="20"/>
+      <c r="AE7" s="20"/>
+      <c r="AF7" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG7" s="20"/>
+      <c r="AH7" s="20"/>
+    </row>
+    <row r="8" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="Z8" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AA8" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AB8" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AC8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AE8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AH8" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B9" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C9" s="4">
+        <v>19</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="4">
+        <v>31</v>
+      </c>
+      <c r="G9" s="4">
+        <v>34</v>
+      </c>
+      <c r="H9" s="8">
+        <v>0.29018179618082302</v>
+      </c>
+      <c r="I9" s="4">
+        <v>244</v>
+      </c>
+      <c r="J9" s="8">
+        <v>0.70981820381917704</v>
+      </c>
+      <c r="K9" s="4">
+        <v>-244</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" s="4">
+        <v>1</v>
+      </c>
+      <c r="O9" s="15">
+        <v>19.394053352958149</v>
+      </c>
+      <c r="P9" s="15">
+        <v>26.817894340589358</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>-10.5</v>
+      </c>
+      <c r="R9" s="15">
+        <v>-7.4238409876312126</v>
+      </c>
+      <c r="S9" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T9" s="4">
+        <v>-3</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V9" s="4">
+        <v>1</v>
+      </c>
+      <c r="W9" s="4">
+        <v>46.5</v>
+      </c>
+      <c r="X9" s="9">
+        <v>46.211947693547501</v>
+      </c>
+      <c r="Y9" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z9" s="4">
+        <v>65</v>
+      </c>
+      <c r="AA9" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="5"/>
+      <c r="AD9" s="5"/>
+      <c r="AE9" s="5"/>
+      <c r="AF9" s="5"/>
+      <c r="AG9" s="5"/>
+      <c r="AH9" s="5"/>
+    </row>
+    <row r="10" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B10" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C10" s="4">
+        <v>19</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="4">
+        <v>31</v>
+      </c>
+      <c r="G10" s="4">
+        <v>27</v>
+      </c>
+      <c r="H10" s="8">
+        <v>0.58406292373303081</v>
+      </c>
+      <c r="I10" s="4">
+        <v>-140</v>
+      </c>
+      <c r="J10" s="8">
+        <v>0.41593707626696919</v>
+      </c>
+      <c r="K10" s="4">
+        <v>140</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N10" s="4">
+        <v>1</v>
+      </c>
+      <c r="O10" s="15">
+        <v>26.148568788948669</v>
+      </c>
+      <c r="P10" s="15">
+        <v>26.46996890305395</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>-1.5</v>
+      </c>
+      <c r="R10" s="15">
+        <v>-0.32140011410528402</v>
+      </c>
+      <c r="S10" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T10" s="4">
+        <v>4</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V10" s="4">
+        <v>1</v>
+      </c>
+      <c r="W10" s="4">
+        <v>45.5</v>
+      </c>
+      <c r="X10" s="9">
+        <v>52.618537692002619</v>
+      </c>
+      <c r="Y10" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z10" s="4">
+        <v>58</v>
+      </c>
+      <c r="AA10" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB10" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="5"/>
+      <c r="AD10" s="5"/>
+      <c r="AE10" s="5"/>
+      <c r="AF10" s="5"/>
+      <c r="AG10" s="5"/>
+      <c r="AH10" s="5"/>
+    </row>
+    <row r="11" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B11" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C11" s="4">
+        <v>19</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="4">
+        <v>24</v>
+      </c>
+      <c r="G11" s="4">
+        <v>27</v>
+      </c>
+      <c r="H11" s="8">
+        <v>0.60932757308712082</v>
+      </c>
+      <c r="I11" s="4">
+        <v>-155</v>
+      </c>
+      <c r="J11" s="8">
+        <v>0.39067242691287918</v>
+      </c>
+      <c r="K11" s="4">
+        <v>155</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="N11" s="4">
+        <v>0</v>
+      </c>
+      <c r="O11" s="15">
+        <v>26.09500735212626</v>
+      </c>
+      <c r="P11" s="15">
+        <v>24.12083548004232</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>-1.5</v>
+      </c>
+      <c r="R11" s="9">
+        <v>1.974171872083939</v>
+      </c>
+      <c r="S11" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T11" s="4">
+        <v>-3</v>
+      </c>
+      <c r="U11" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V11" s="4">
+        <v>0</v>
+      </c>
+      <c r="W11" s="4">
+        <v>51.5</v>
+      </c>
+      <c r="X11" s="9">
+        <v>50.215842832168583</v>
+      </c>
+      <c r="Y11" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z11" s="4">
+        <v>51</v>
+      </c>
+      <c r="AA11" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB11" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="5"/>
+      <c r="AD11" s="5"/>
+      <c r="AE11" s="5"/>
+      <c r="AF11" s="5"/>
+      <c r="AG11" s="5"/>
+      <c r="AH11" s="5"/>
+    </row>
+    <row r="12" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B12" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C12" s="4">
+        <v>19</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="4">
+        <v>19</v>
+      </c>
+      <c r="G12" s="4">
+        <v>23</v>
+      </c>
+      <c r="H12" s="8">
+        <v>0.49617496342080702</v>
+      </c>
+      <c r="I12" s="4">
+        <v>101</v>
+      </c>
+      <c r="J12" s="8">
+        <v>0.50382503657919298</v>
+      </c>
+      <c r="K12" s="4">
+        <v>-101</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="N12" s="4">
+        <v>1</v>
+      </c>
+      <c r="O12" s="15">
+        <v>24.496753433649442</v>
+      </c>
+      <c r="P12" s="15">
+        <v>23.711678199787059</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="R12" s="9">
+        <v>0.78507523386238276</v>
+      </c>
+      <c r="S12" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T12" s="4">
+        <v>-4</v>
+      </c>
+      <c r="U12" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V12" s="4">
+        <v>1</v>
+      </c>
+      <c r="W12" s="4">
+        <v>44.5</v>
+      </c>
+      <c r="X12" s="9">
+        <v>48.208431633436497</v>
+      </c>
+      <c r="Y12" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z12" s="4">
+        <v>42</v>
+      </c>
+      <c r="AA12" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB12" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="5"/>
+      <c r="AD12" s="5"/>
+      <c r="AE12" s="5"/>
+      <c r="AF12" s="5"/>
+      <c r="AG12" s="5"/>
+      <c r="AH12" s="5"/>
+    </row>
+    <row r="13" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B13" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C13" s="4">
+        <v>19</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="4">
+        <v>16</v>
+      </c>
+      <c r="G13" s="4">
+        <v>3</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0.77533578600133835</v>
+      </c>
+      <c r="I13" s="4">
+        <v>-345</v>
+      </c>
+      <c r="J13" s="8">
+        <v>0.22466421399866171</v>
+      </c>
+      <c r="K13" s="4">
+        <v>345</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N13" s="4">
+        <v>1</v>
+      </c>
+      <c r="O13" s="15">
+        <v>28.938898589423289</v>
+      </c>
+      <c r="P13" s="15">
+        <v>17.705749610579009</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="R13" s="9">
+        <v>11.23314897884428</v>
+      </c>
+      <c r="S13" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T13" s="4">
+        <v>13</v>
+      </c>
+      <c r="U13" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="V13" s="4">
+        <v>1</v>
+      </c>
+      <c r="W13" s="4">
+        <v>46.5</v>
+      </c>
+      <c r="X13" s="9">
+        <v>46.644648200002287</v>
+      </c>
+      <c r="Y13" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z13" s="4">
+        <v>19</v>
+      </c>
+      <c r="AA13" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB13" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="5"/>
+      <c r="AD13" s="5"/>
+      <c r="AE13" s="5"/>
+      <c r="AF13" s="5"/>
+      <c r="AG13" s="5"/>
+      <c r="AH13" s="5"/>
+    </row>
+    <row r="14" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B14" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C14" s="4">
+        <v>19</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" s="4">
+        <v>6</v>
+      </c>
+      <c r="G14" s="4">
+        <v>30</v>
+      </c>
+      <c r="H14" s="8">
+        <v>0.45496618005377543</v>
+      </c>
+      <c r="I14" s="4">
+        <v>119</v>
+      </c>
+      <c r="J14" s="8">
+        <v>0.54503381994622457</v>
+      </c>
+      <c r="K14" s="4">
+        <v>-119</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="N14" s="4">
+        <v>1</v>
+      </c>
+      <c r="O14" s="15">
+        <v>18.481034206854751</v>
+      </c>
+      <c r="P14" s="15">
+        <v>23.550891694555919</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>-3</v>
+      </c>
+      <c r="R14" s="15">
+        <v>-5.0698574877011673</v>
+      </c>
+      <c r="S14" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T14" s="4">
+        <v>-24</v>
+      </c>
+      <c r="U14" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V14" s="4">
+        <v>1</v>
+      </c>
+      <c r="W14" s="4">
+        <v>39.5</v>
+      </c>
+      <c r="X14" s="9">
+        <v>42.031925901410673</v>
+      </c>
+      <c r="Y14" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z14" s="4">
+        <v>36</v>
+      </c>
+      <c r="AA14" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB14" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="5"/>
+      <c r="AD14" s="5"/>
+      <c r="AE14" s="5"/>
+      <c r="AF14" s="5"/>
+      <c r="AG14" s="5"/>
+      <c r="AH14" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="Q7:V7"/>
+    <mergeCell ref="W7:AB7"/>
+    <mergeCell ref="AC7:AE7"/>
+    <mergeCell ref="AF7:AH7"/>
+  </mergeCells>
+  <conditionalFormatting sqref="AC9:AC14">
+    <cfRule type="colorScale" priority="111">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD9:AD14">
+    <cfRule type="colorScale" priority="112">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE9:AE14">
+    <cfRule type="colorScale" priority="113">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF9:AF14">
+    <cfRule type="colorScale" priority="114">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG9:AG14">
+    <cfRule type="colorScale" priority="115">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH9:AH14">
+    <cfRule type="colorScale" priority="116">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="108" id="{A87B13F2-CDBA-B641-AB2C-D05932E550B7}">
+            <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>N9:N14</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="109" id="{C0EEA867-ED34-284F-8CD9-73B0731EBEEB}">
+            <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>V9:V14</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="110" id="{4D9903A0-0C5A-A64B-9BDC-C0D48C065596}">
+            <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>AB9:AB14</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3197922-17FD-3446-ABDB-5FDED8A662DF}">
-  <dimension ref="B2:F47"/>
+  <dimension ref="B2:F48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.2">
@@ -32048,261 +33592,223 @@
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B4" cm="1">
-        <f t="array" ref="B4:B16">_xlfn.UNIQUE(_xlfn._xlws.FILTER(Master!C9:C1000,NOT(ISBLANK(Master!C9:C1000))))</f>
-        <v>6</v>
+      <c r="B4" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="B4" ca="1">_xlfn.UNIQUE(_xlfn._xlws.FILTER(Master!C9:C1000,NOT(ISBLANK(Master!C9:C1000))))</f>
+        <v>#VALUE!</v>
       </c>
       <c r="C4">
-        <f>COUNTIFS(Master!C:C,'Weekly Record'!B4)</f>
-        <v>15</v>
+        <f ca="1">COUNTIFS(Master!C:C,'Weekly Record'!B4)</f>
+        <v>0</v>
       </c>
       <c r="D4">
-        <f>SUMIFS(Master!N:N, Master!C:C,'Weekly Record'!B4)</f>
-        <v>9</v>
+        <f ca="1">SUMIFS(Master!N:N, Master!C:C,'Weekly Record'!B4)</f>
+        <v>0</v>
       </c>
       <c r="E4">
-        <f>C4-D4</f>
-        <v>6</v>
-      </c>
-      <c r="F4" s="12">
-        <f>D4/C4</f>
-        <v>0.6</v>
+        <f ca="1">C4-D4</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="12" t="e">
+        <f ca="1">D4/C4</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B5">
-        <v>7</v>
-      </c>
       <c r="C5">
         <f>COUNTIFS(Master!C:C,'Weekly Record'!B5)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <f>SUMIFS(Master!N:N, Master!C:C,'Weekly Record'!B5)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <f t="shared" ref="E5:E13" si="0">C5-D5</f>
-        <v>3</v>
-      </c>
-      <c r="F5" s="12">
+        <v>0</v>
+      </c>
+      <c r="F5" s="12" t="e">
         <f t="shared" ref="F5:F13" si="1">D5/C5</f>
-        <v>0.8</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B6">
-        <v>8</v>
-      </c>
       <c r="C6">
         <f>COUNTIFS(Master!C:C,'Weekly Record'!B6)</f>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <f>SUMIFS(Master!N:N, Master!C:C,'Weekly Record'!B6)</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="F6" s="12">
+        <v>0</v>
+      </c>
+      <c r="F6" s="12" t="e">
         <f t="shared" si="1"/>
-        <v>0.84615384615384615</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B7">
-        <v>9</v>
-      </c>
       <c r="C7">
         <f>COUNTIFS(Master!C:C,'Weekly Record'!B7)</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <f>SUMIFS(Master!N:N, Master!C:C,'Weekly Record'!B7)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="F7" s="12">
+        <v>0</v>
+      </c>
+      <c r="F7" s="12" t="e">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B8">
-        <v>10</v>
-      </c>
       <c r="C8">
         <f>COUNTIFS(Master!C:C,'Weekly Record'!B8)</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <f>SUMIFS(Master!N:N, Master!C:C,'Weekly Record'!B8)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="F8" s="12">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12" t="e">
         <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B9">
-        <v>11</v>
-      </c>
       <c r="C9">
         <f>COUNTIFS(Master!C:C,'Weekly Record'!B9)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <f>SUMIFS(Master!N:N, Master!C:C,'Weekly Record'!B9)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="F9" s="12">
+        <v>0</v>
+      </c>
+      <c r="F9" s="12" t="e">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B10">
-        <v>12</v>
-      </c>
       <c r="C10">
         <f>COUNTIFS(Master!C:C,'Weekly Record'!B10)</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <f>SUMIFS(Master!N:N, Master!C:C,'Weekly Record'!B10)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="F10" s="12">
+        <v>0</v>
+      </c>
+      <c r="F10" s="12" t="e">
         <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B11">
-        <v>13</v>
-      </c>
       <c r="C11">
         <f>COUNTIFS(Master!C:C,'Weekly Record'!B11)</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <f>SUMIFS(Master!N:N, Master!C:C,'Weekly Record'!B11)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="F11" s="12" t="e">
         <f t="shared" si="1"/>
-        <v>0.625</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B12">
-        <v>14</v>
-      </c>
       <c r="C12">
         <f>COUNTIFS(Master!C:C,'Weekly Record'!B12)</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <f>SUMIFS(Master!N:N, Master!C:C,'Weekly Record'!B12)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="F12" s="12">
+        <v>0</v>
+      </c>
+      <c r="F12" s="12" t="e">
         <f t="shared" si="1"/>
-        <v>0.5714285714285714</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B13">
-        <v>15</v>
-      </c>
       <c r="C13">
         <f>COUNTIFS(Master!C:C,'Weekly Record'!B13)</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <f>SUMIFS(Master!N:N, Master!C:C,'Weekly Record'!B13)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="F13" s="12">
+        <v>0</v>
+      </c>
+      <c r="F13" s="12" t="e">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B14">
-        <v>16</v>
-      </c>
       <c r="C14">
         <f>COUNTIFS(Master!C:C,'Weekly Record'!B14)</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <f>SUMIFS(Master!N:N, Master!C:C,'Weekly Record'!B14)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <f t="shared" ref="E14" si="2">C14-D14</f>
-        <v>8</v>
-      </c>
-      <c r="F14" s="12">
+        <v>0</v>
+      </c>
+      <c r="F14" s="12" t="e">
         <f t="shared" ref="F14" si="3">D14/C14</f>
-        <v>0.5</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B15">
-        <v>17</v>
-      </c>
       <c r="C15">
         <f>COUNTIFS(Master!C:C,'Weekly Record'!B15)</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <f>SUMIFS(Master!N:N, Master!C:C,'Weekly Record'!B15)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <f t="shared" ref="E15" si="4">C15-D15</f>
-        <v>6</v>
-      </c>
-      <c r="F15" s="12">
+        <v>0</v>
+      </c>
+      <c r="F15" s="12" t="e">
         <f t="shared" ref="F15" si="5">D15/C15</f>
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B16">
-        <v>18</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.2">
@@ -32329,7 +33835,7 @@
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B19" cm="1">
-        <f t="array" ref="B19:B31">_xlfn.UNIQUE(_xlfn._xlws.FILTER(Master!C9:C1000,NOT(ISBLANK(Master!C9:C1000))))</f>
+        <f t="array" ref="B19:B32">_xlfn.UNIQUE(_xlfn._xlws.FILTER(Master!C9:C1000,NOT(ISBLANK(Master!C9:C1000))))</f>
         <v>6</v>
       </c>
       <c r="C19">
@@ -32585,6 +34091,11 @@
         <v>18</v>
       </c>
     </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B32">
+        <v>19</v>
+      </c>
+    </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" s="18" t="s">
         <v>146</v>
@@ -32609,7 +34120,7 @@
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" cm="1">
-        <f t="array" ref="B35:B47">_xlfn.UNIQUE(_xlfn._xlws.FILTER(Master!C9:C1000,NOT(ISBLANK(Master!C9:C1000))))</f>
+        <f t="array" ref="B35:B48">_xlfn.UNIQUE(_xlfn._xlws.FILTER(Master!C9:C1000,NOT(ISBLANK(Master!C9:C1000))))</f>
         <v>6</v>
       </c>
       <c r="C35">
@@ -32863,6 +34374,11 @@
     <row r="47" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B47">
         <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B48">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
